--- a/tabular/legacy-list.xlsx
+++ b/tabular/legacy-list.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rob/Projects/erv/ERVdb-HomoSapiens/tabular/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:40009_{F4AE04F0-9022-2546-9E89-6BDB604EA25F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45D58064-2631-CC46-A983-0284907EBB2A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1280" yWindow="1000" windowWidth="27140" windowHeight="16440"/>
+    <workbookView xWindow="1280" yWindow="1000" windowWidth="27140" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="legacy-list" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
@@ -1519,7 +1520,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
@@ -2361,9 +2362,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O152"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:O149"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="4" max="4" width="47.1640625" customWidth="1"/>
+    <col min="5" max="5" width="34" customWidth="1"/>
+    <col min="6" max="6" width="51.6640625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
@@ -2941,34 +2947,37 @@
         <v>17</v>
       </c>
       <c r="D15" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E15" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="F15" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="G15" t="s">
-        <v>65</v>
+        <v>19</v>
+      </c>
+      <c r="H15">
+        <v>16</v>
       </c>
       <c r="I15" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="J15">
-        <v>3272</v>
+        <v>100616411</v>
       </c>
       <c r="K15" t="s">
         <v>43</v>
       </c>
       <c r="L15" t="s">
-        <v>21</v>
+        <v>71</v>
       </c>
       <c r="M15">
-        <v>229406344</v>
+        <v>6866141</v>
       </c>
       <c r="N15">
-        <v>229408495</v>
+        <v>6875603</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.2">
@@ -2982,37 +2991,28 @@
         <v>17</v>
       </c>
       <c r="D16" t="s">
-        <v>67</v>
-      </c>
-      <c r="E16" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="F16" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="G16" t="s">
         <v>19</v>
       </c>
       <c r="H16">
-        <v>16</v>
-      </c>
-      <c r="I16" t="s">
-        <v>70</v>
-      </c>
-      <c r="J16">
-        <v>100616411</v>
+        <v>103</v>
       </c>
       <c r="K16" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="L16" t="s">
         <v>71</v>
       </c>
       <c r="M16">
-        <v>6866141</v>
+        <v>27182399</v>
       </c>
       <c r="N16">
-        <v>6875603</v>
+        <v>27183380</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.2">
@@ -3026,16 +3026,22 @@
         <v>17</v>
       </c>
       <c r="D17" t="s">
-        <v>72</v>
-      </c>
-      <c r="F17" t="s">
-        <v>73</v>
+        <v>74</v>
+      </c>
+      <c r="E17" t="s">
+        <v>75</v>
       </c>
       <c r="G17" t="s">
-        <v>19</v>
+        <v>76</v>
       </c>
       <c r="H17">
-        <v>103</v>
+        <v>5</v>
+      </c>
+      <c r="I17" t="s">
+        <v>77</v>
+      </c>
+      <c r="J17">
+        <v>100862699</v>
       </c>
       <c r="K17" t="s">
         <v>20</v>
@@ -3044,10 +3050,10 @@
         <v>71</v>
       </c>
       <c r="M17">
-        <v>27182399</v>
+        <v>27754712</v>
       </c>
       <c r="N17">
-        <v>27183380</v>
+        <v>27757008</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.2">
@@ -3061,22 +3067,25 @@
         <v>17</v>
       </c>
       <c r="D18" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="E18" t="s">
-        <v>75</v>
+        <v>79</v>
+      </c>
+      <c r="F18" t="s">
+        <v>80</v>
       </c>
       <c r="G18" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="H18">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I18" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="J18">
-        <v>100862699</v>
+        <v>100616200</v>
       </c>
       <c r="K18" t="s">
         <v>20</v>
@@ -3085,10 +3094,10 @@
         <v>71</v>
       </c>
       <c r="M18">
-        <v>27754712</v>
+        <v>38230496</v>
       </c>
       <c r="N18">
-        <v>27757008</v>
+        <v>38230791</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.2">
@@ -3102,37 +3111,37 @@
         <v>17</v>
       </c>
       <c r="D19" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="E19" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="F19" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="G19" t="s">
-        <v>81</v>
+        <v>19</v>
       </c>
       <c r="H19">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="I19" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="J19">
-        <v>100616200</v>
+        <v>100862686</v>
       </c>
       <c r="K19" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="L19" t="s">
         <v>71</v>
       </c>
       <c r="M19">
-        <v>38230496</v>
+        <v>101585489</v>
       </c>
       <c r="N19">
-        <v>38230791</v>
+        <v>101587716</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.2">
@@ -3146,37 +3155,25 @@
         <v>17</v>
       </c>
       <c r="D20" t="s">
-        <v>83</v>
-      </c>
-      <c r="E20" t="s">
-        <v>84</v>
-      </c>
-      <c r="F20" t="s">
-        <v>85</v>
+        <v>39</v>
       </c>
       <c r="G20" t="s">
         <v>19</v>
       </c>
       <c r="H20">
-        <v>17</v>
-      </c>
-      <c r="I20" t="s">
-        <v>86</v>
-      </c>
-      <c r="J20">
-        <v>100862686</v>
+        <v>7</v>
       </c>
       <c r="K20" t="s">
         <v>43</v>
       </c>
       <c r="L20" t="s">
-        <v>71</v>
+        <v>87</v>
       </c>
       <c r="M20">
-        <v>101585489</v>
+        <v>3468656</v>
       </c>
       <c r="N20">
-        <v>101587716</v>
+        <v>3478209</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.2">
@@ -3190,13 +3187,22 @@
         <v>17</v>
       </c>
       <c r="D21" t="s">
-        <v>39</v>
-      </c>
-      <c r="G21" t="s">
-        <v>19</v>
+        <v>88</v>
+      </c>
+      <c r="E21" t="s">
+        <v>89</v>
+      </c>
+      <c r="F21" t="s">
+        <v>90</v>
       </c>
       <c r="H21">
-        <v>7</v>
+        <v>4</v>
+      </c>
+      <c r="I21" t="s">
+        <v>91</v>
+      </c>
+      <c r="J21">
+        <v>100616106</v>
       </c>
       <c r="K21" t="s">
         <v>43</v>
@@ -3205,10 +3211,10 @@
         <v>87</v>
       </c>
       <c r="M21">
-        <v>3468656</v>
+        <v>7924011</v>
       </c>
       <c r="N21">
-        <v>3478209</v>
+        <v>7924334</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.2">
@@ -3222,22 +3228,22 @@
         <v>17</v>
       </c>
       <c r="D22" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="E22" t="s">
-        <v>89</v>
-      </c>
-      <c r="F22" t="s">
-        <v>90</v>
+        <v>93</v>
+      </c>
+      <c r="G22" t="s">
+        <v>19</v>
       </c>
       <c r="H22">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="I22" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="J22">
-        <v>100616106</v>
+        <v>106144566</v>
       </c>
       <c r="K22" t="s">
         <v>43</v>
@@ -3246,10 +3252,10 @@
         <v>87</v>
       </c>
       <c r="M22">
-        <v>7924011</v>
+        <v>62135963</v>
       </c>
       <c r="N22">
-        <v>7924334</v>
+        <v>62150563</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.2">
@@ -3263,34 +3269,34 @@
         <v>17</v>
       </c>
       <c r="D23" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="E23" t="s">
-        <v>93</v>
-      </c>
-      <c r="G23" t="s">
-        <v>19</v>
+        <v>96</v>
+      </c>
+      <c r="F23" t="s">
+        <v>97</v>
       </c>
       <c r="H23">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="I23" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="J23">
-        <v>106144566</v>
+        <v>100616497</v>
       </c>
       <c r="K23" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="L23" t="s">
         <v>87</v>
       </c>
       <c r="M23">
-        <v>62135963</v>
+        <v>67390298</v>
       </c>
       <c r="N23">
-        <v>62150563</v>
+        <v>67394204</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.2">
@@ -3304,34 +3310,31 @@
         <v>17</v>
       </c>
       <c r="D24" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="E24" t="s">
-        <v>96</v>
-      </c>
-      <c r="F24" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="H24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I24" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="J24">
-        <v>100616497</v>
+        <v>100862691</v>
       </c>
       <c r="K24" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="L24" t="s">
         <v>87</v>
       </c>
       <c r="M24">
-        <v>67390298</v>
+        <v>67612675</v>
       </c>
       <c r="N24">
-        <v>67394204</v>
+        <v>67615320</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.2">
@@ -3345,19 +3348,22 @@
         <v>17</v>
       </c>
       <c r="D25" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="E25" t="s">
-        <v>100</v>
+        <v>103</v>
+      </c>
+      <c r="G25" t="s">
+        <v>24</v>
       </c>
       <c r="H25">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I25" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="J25">
-        <v>100862691</v>
+        <v>100616198</v>
       </c>
       <c r="K25" t="s">
         <v>43</v>
@@ -3366,10 +3372,10 @@
         <v>87</v>
       </c>
       <c r="M25">
-        <v>67612675</v>
-      </c>
-      <c r="N25">
-        <v>67615320</v>
+        <v>77569259</v>
+      </c>
+      <c r="N25" s="1">
+        <v>77574524</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.2">
@@ -3383,34 +3389,37 @@
         <v>17</v>
       </c>
       <c r="D26" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="E26" t="s">
-        <v>103</v>
+        <v>106</v>
+      </c>
+      <c r="F26" t="s">
+        <v>107</v>
       </c>
       <c r="G26" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="H26">
-        <v>6</v>
+        <v>118</v>
       </c>
       <c r="I26" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="J26">
-        <v>100616198</v>
+        <v>100862683</v>
       </c>
       <c r="K26" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="L26" t="s">
         <v>87</v>
       </c>
       <c r="M26">
-        <v>77569259</v>
-      </c>
-      <c r="N26" s="1">
-        <v>77574524</v>
+        <v>101565794</v>
+      </c>
+      <c r="N26">
+        <v>101575259</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.2">
@@ -3424,37 +3433,37 @@
         <v>17</v>
       </c>
       <c r="D27" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="E27" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="F27" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="G27" t="s">
         <v>19</v>
       </c>
       <c r="H27">
-        <v>118</v>
+        <v>37</v>
       </c>
       <c r="I27" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="J27">
-        <v>100862683</v>
+        <v>100616444</v>
       </c>
       <c r="K27" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="L27" t="s">
         <v>87</v>
       </c>
       <c r="M27">
-        <v>101565794</v>
+        <v>118591724</v>
       </c>
       <c r="N27">
-        <v>101575259</v>
+        <v>118600883</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.2">
@@ -3468,37 +3477,34 @@
         <v>17</v>
       </c>
       <c r="D28" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="E28" t="s">
-        <v>110</v>
-      </c>
-      <c r="F28" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="G28" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="H28">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="I28" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="J28">
-        <v>100616444</v>
+        <v>106144603</v>
       </c>
       <c r="K28" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="L28" t="s">
-        <v>87</v>
+        <v>116</v>
       </c>
       <c r="M28">
-        <v>118591724</v>
+        <v>8914009</v>
       </c>
       <c r="N28">
-        <v>118600883</v>
+        <v>8921064</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.2">
@@ -3512,34 +3518,25 @@
         <v>17</v>
       </c>
       <c r="D29" t="s">
-        <v>113</v>
-      </c>
-      <c r="E29" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="G29" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="H29">
-        <v>23</v>
-      </c>
-      <c r="I29" t="s">
-        <v>115</v>
-      </c>
-      <c r="J29">
-        <v>106144603</v>
+        <v>50</v>
       </c>
       <c r="K29" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="L29" t="s">
         <v>116</v>
       </c>
       <c r="M29">
-        <v>8914009</v>
+        <v>34772555</v>
       </c>
       <c r="N29">
-        <v>8921064</v>
+        <v>34782217</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.2">
@@ -3553,25 +3550,34 @@
         <v>17</v>
       </c>
       <c r="D30" t="s">
-        <v>117</v>
+        <v>118</v>
+      </c>
+      <c r="E30" t="s">
+        <v>119</v>
       </c>
       <c r="G30" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="H30">
-        <v>50</v>
+        <v>24</v>
+      </c>
+      <c r="I30" t="s">
+        <v>120</v>
+      </c>
+      <c r="J30">
+        <v>106144564</v>
       </c>
       <c r="K30" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="L30" t="s">
         <v>116</v>
       </c>
       <c r="M30">
-        <v>34772555</v>
+        <v>51296258</v>
       </c>
       <c r="N30">
-        <v>34782217</v>
+        <v>51307150</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.2">
@@ -3585,34 +3591,37 @@
         <v>17</v>
       </c>
       <c r="D31" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="E31" t="s">
+        <v>122</v>
+      </c>
+      <c r="F31" t="s">
+        <v>123</v>
+      </c>
+      <c r="G31" t="s">
+        <v>19</v>
+      </c>
+      <c r="H31">
         <v>119</v>
       </c>
-      <c r="G31" t="s">
-        <v>24</v>
-      </c>
-      <c r="H31">
-        <v>24</v>
-      </c>
       <c r="I31" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="J31">
-        <v>106144564</v>
+        <v>100616103</v>
       </c>
       <c r="K31" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="L31" t="s">
         <v>116</v>
       </c>
       <c r="M31">
-        <v>51296258</v>
+        <v>58721242</v>
       </c>
       <c r="N31">
-        <v>51307150</v>
+        <v>58730698</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.2">
@@ -3626,25 +3635,22 @@
         <v>17</v>
       </c>
       <c r="D32" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="E32" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="F32" t="s">
-        <v>123</v>
-      </c>
-      <c r="G32" t="s">
-        <v>19</v>
+        <v>127</v>
       </c>
       <c r="H32">
-        <v>119</v>
+        <v>5</v>
       </c>
       <c r="I32" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="J32">
-        <v>100616103</v>
+        <v>100616412</v>
       </c>
       <c r="K32" t="s">
         <v>43</v>
@@ -3653,10 +3659,10 @@
         <v>116</v>
       </c>
       <c r="M32">
-        <v>58721242</v>
+        <v>112259651</v>
       </c>
       <c r="N32">
-        <v>58730698</v>
+        <v>112259984</v>
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.2">
@@ -3670,22 +3676,13 @@
         <v>17</v>
       </c>
       <c r="D33" t="s">
-        <v>125</v>
-      </c>
-      <c r="E33" t="s">
-        <v>126</v>
-      </c>
-      <c r="F33" t="s">
-        <v>127</v>
+        <v>129</v>
+      </c>
+      <c r="G33" t="s">
+        <v>19</v>
       </c>
       <c r="H33">
-        <v>5</v>
-      </c>
-      <c r="I33" t="s">
-        <v>128</v>
-      </c>
-      <c r="J33">
-        <v>100616412</v>
+        <v>42</v>
       </c>
       <c r="K33" t="s">
         <v>43</v>
@@ -3694,10 +3691,10 @@
         <v>116</v>
       </c>
       <c r="M33">
-        <v>112259651</v>
+        <v>133667120</v>
       </c>
       <c r="N33">
-        <v>112259984</v>
+        <v>133673132</v>
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.2">
@@ -3711,25 +3708,34 @@
         <v>17</v>
       </c>
       <c r="D34" t="s">
-        <v>129</v>
+        <v>130</v>
+      </c>
+      <c r="E34" t="s">
+        <v>131</v>
       </c>
       <c r="G34" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="H34">
-        <v>42</v>
+        <v>25</v>
+      </c>
+      <c r="I34" t="s">
+        <v>132</v>
+      </c>
+      <c r="J34">
+        <v>106144605</v>
       </c>
       <c r="K34" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="L34" t="s">
-        <v>116</v>
+        <v>133</v>
       </c>
       <c r="M34">
-        <v>133667120</v>
+        <v>37530786</v>
       </c>
       <c r="N34">
-        <v>133673132</v>
+        <v>37533118</v>
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.2">
@@ -3743,34 +3749,25 @@
         <v>17</v>
       </c>
       <c r="D35" t="s">
-        <v>130</v>
-      </c>
-      <c r="E35" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="G35" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="H35">
-        <v>25</v>
-      </c>
-      <c r="I35" t="s">
-        <v>132</v>
-      </c>
-      <c r="J35">
-        <v>106144605</v>
+        <v>71</v>
       </c>
       <c r="K35" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="L35" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="M35">
-        <v>37530786</v>
+        <v>24480625</v>
       </c>
       <c r="N35">
-        <v>37533118</v>
+        <v>24484121</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.2">
@@ -3784,25 +3781,34 @@
         <v>17</v>
       </c>
       <c r="D36" t="s">
-        <v>134</v>
+        <v>136</v>
+      </c>
+      <c r="E36" t="s">
+        <v>137</v>
       </c>
       <c r="G36" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="H36">
-        <v>71</v>
+        <v>26</v>
+      </c>
+      <c r="I36" t="s">
+        <v>138</v>
+      </c>
+      <c r="J36">
+        <v>106144572</v>
       </c>
       <c r="K36" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="L36" t="s">
         <v>135</v>
       </c>
       <c r="M36">
-        <v>24480625</v>
+        <v>45488688</v>
       </c>
       <c r="N36">
-        <v>24484121</v>
+        <v>45492897</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.2">
@@ -3816,22 +3822,22 @@
         <v>17</v>
       </c>
       <c r="D37" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E37" t="s">
-        <v>137</v>
-      </c>
-      <c r="G37" t="s">
-        <v>24</v>
+        <v>140</v>
+      </c>
+      <c r="F37" t="s">
+        <v>141</v>
       </c>
       <c r="H37">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="I37" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="J37">
-        <v>106144572</v>
+        <v>100862697</v>
       </c>
       <c r="K37" t="s">
         <v>20</v>
@@ -3840,10 +3846,10 @@
         <v>135</v>
       </c>
       <c r="M37">
-        <v>45488688</v>
+        <v>70279954</v>
       </c>
       <c r="N37">
-        <v>45492897</v>
+        <v>70282683</v>
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.2">
@@ -3857,22 +3863,22 @@
         <v>17</v>
       </c>
       <c r="D38" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="E38" t="s">
-        <v>140</v>
-      </c>
-      <c r="F38" t="s">
-        <v>141</v>
+        <v>144</v>
+      </c>
+      <c r="G38" t="s">
+        <v>24</v>
       </c>
       <c r="H38">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="I38" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="J38">
-        <v>100862697</v>
+        <v>106144565</v>
       </c>
       <c r="K38" t="s">
         <v>20</v>
@@ -3881,10 +3887,10 @@
         <v>135</v>
       </c>
       <c r="M38">
-        <v>70279954</v>
+        <v>91692008</v>
       </c>
       <c r="N38">
-        <v>70282683</v>
+        <v>91693212</v>
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.2">
@@ -3898,34 +3904,37 @@
         <v>17</v>
       </c>
       <c r="D39" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="E39" t="s">
-        <v>144</v>
+        <v>147</v>
+      </c>
+      <c r="F39" t="s">
+        <v>148</v>
       </c>
       <c r="G39" t="s">
-        <v>24</v>
+        <v>76</v>
       </c>
       <c r="H39">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="I39" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="J39">
-        <v>106144565</v>
+        <v>100862698</v>
       </c>
       <c r="K39" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="L39" t="s">
         <v>135</v>
       </c>
       <c r="M39">
-        <v>91692008</v>
+        <v>92511119</v>
       </c>
       <c r="N39">
-        <v>91693212</v>
+        <v>92516158</v>
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.2">
@@ -3939,37 +3948,37 @@
         <v>17</v>
       </c>
       <c r="D40" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="E40" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="F40" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G40" t="s">
         <v>76</v>
       </c>
       <c r="H40">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I40" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="J40">
-        <v>100862698</v>
+        <v>51359</v>
       </c>
       <c r="K40" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="L40" t="s">
         <v>135</v>
       </c>
       <c r="M40">
-        <v>92511119</v>
+        <v>99452044</v>
       </c>
       <c r="N40">
-        <v>92516158</v>
+        <v>99457077</v>
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.2">
@@ -3983,37 +3992,31 @@
         <v>17</v>
       </c>
       <c r="D41" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="E41" t="s">
-        <v>151</v>
-      </c>
-      <c r="F41" t="s">
-        <v>152</v>
-      </c>
-      <c r="G41" t="s">
-        <v>76</v>
+        <v>155</v>
       </c>
       <c r="H41">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I41" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="J41">
-        <v>51359</v>
+        <v>100133791</v>
       </c>
       <c r="K41" t="s">
         <v>20</v>
       </c>
       <c r="L41" t="s">
-        <v>135</v>
+        <v>157</v>
       </c>
       <c r="M41">
-        <v>99452044</v>
+        <v>54202966</v>
       </c>
       <c r="N41">
-        <v>99457077</v>
+        <v>54206909</v>
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.2">
@@ -4027,19 +4030,25 @@
         <v>17</v>
       </c>
       <c r="D42" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="E42" t="s">
-        <v>155</v>
+        <v>159</v>
+      </c>
+      <c r="F42" t="s">
+        <v>160</v>
+      </c>
+      <c r="G42" t="s">
+        <v>24</v>
       </c>
       <c r="H42">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I42" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="J42">
-        <v>100133791</v>
+        <v>100616496</v>
       </c>
       <c r="K42" t="s">
         <v>20</v>
@@ -4048,10 +4057,10 @@
         <v>157</v>
       </c>
       <c r="M42">
-        <v>54202966</v>
+        <v>55597079</v>
       </c>
       <c r="N42">
-        <v>54206909</v>
+        <v>55604574</v>
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.2">
@@ -4065,37 +4074,31 @@
         <v>17</v>
       </c>
       <c r="D43" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="E43" t="s">
-        <v>159</v>
-      </c>
-      <c r="F43" t="s">
-        <v>160</v>
-      </c>
-      <c r="G43" t="s">
-        <v>24</v>
+        <v>163</v>
       </c>
       <c r="H43">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I43" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="J43">
-        <v>100616496</v>
+        <v>100507321</v>
       </c>
       <c r="K43" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="L43" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="M43">
-        <v>55597079</v>
+        <v>2708390</v>
       </c>
       <c r="N43">
-        <v>55604574</v>
+        <v>2722572</v>
       </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.2">
@@ -4109,31 +4112,25 @@
         <v>17</v>
       </c>
       <c r="D44" t="s">
-        <v>162</v>
-      </c>
-      <c r="E44" t="s">
-        <v>163</v>
+        <v>166</v>
+      </c>
+      <c r="G44" t="s">
+        <v>19</v>
       </c>
       <c r="H44">
-        <v>1</v>
-      </c>
-      <c r="I44" t="s">
-        <v>164</v>
-      </c>
-      <c r="J44">
-        <v>100507321</v>
+        <v>4034</v>
       </c>
       <c r="K44" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="L44" t="s">
         <v>165</v>
       </c>
       <c r="M44">
-        <v>2708390</v>
+        <v>2976160</v>
       </c>
       <c r="N44">
-        <v>2722572</v>
+        <v>2977661</v>
       </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.2">
@@ -4147,25 +4144,37 @@
         <v>17</v>
       </c>
       <c r="D45" t="s">
-        <v>166</v>
-      </c>
-      <c r="G45" t="s">
-        <v>19</v>
+        <v>167</v>
+      </c>
+      <c r="E45" t="s">
+        <v>168</v>
+      </c>
+      <c r="F45" t="s">
+        <v>169</v>
+      </c>
+      <c r="G45">
+        <v>9</v>
       </c>
       <c r="H45">
-        <v>4034</v>
+        <v>9</v>
+      </c>
+      <c r="I45" t="s">
+        <v>170</v>
+      </c>
+      <c r="J45">
+        <v>111188137</v>
       </c>
       <c r="K45" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="L45" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="M45">
-        <v>2976160</v>
+        <v>6779397</v>
       </c>
       <c r="N45">
-        <v>2977661</v>
+        <v>6780027</v>
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.2">
@@ -4179,25 +4188,25 @@
         <v>17</v>
       </c>
       <c r="D46" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="E46" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="F46" t="s">
-        <v>169</v>
-      </c>
-      <c r="G46">
-        <v>9</v>
+        <v>174</v>
+      </c>
+      <c r="G46" t="s">
+        <v>175</v>
       </c>
       <c r="H46">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="I46" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="J46">
-        <v>111188137</v>
+        <v>85314</v>
       </c>
       <c r="K46" t="s">
         <v>43</v>
@@ -4206,10 +4215,10 @@
         <v>171</v>
       </c>
       <c r="M46">
-        <v>6779397</v>
+        <v>26557587</v>
       </c>
       <c r="N46">
-        <v>6780027</v>
+        <v>26559832</v>
       </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.2">
@@ -4223,37 +4232,34 @@
         <v>17</v>
       </c>
       <c r="D47" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="E47" t="s">
-        <v>173</v>
-      </c>
-      <c r="F47" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="G47" t="s">
-        <v>175</v>
+        <v>24</v>
       </c>
       <c r="H47">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="I47" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="J47">
-        <v>85314</v>
+        <v>105694156</v>
       </c>
       <c r="K47" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="L47" t="s">
         <v>171</v>
       </c>
       <c r="M47">
-        <v>26557587</v>
+        <v>35689889</v>
       </c>
       <c r="N47">
-        <v>26559832</v>
+        <v>35693622</v>
       </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.2">
@@ -4267,34 +4273,31 @@
         <v>17</v>
       </c>
       <c r="D48" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E48" t="s">
-        <v>178</v>
-      </c>
-      <c r="G48" t="s">
-        <v>24</v>
+        <v>181</v>
       </c>
       <c r="H48">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="I48" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="J48">
-        <v>105694156</v>
+        <v>111188144</v>
       </c>
       <c r="K48" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="L48" t="s">
         <v>171</v>
       </c>
       <c r="M48">
-        <v>35689889</v>
+        <v>47248932</v>
       </c>
       <c r="N48">
-        <v>35693622</v>
+        <v>47249567</v>
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.2">
@@ -4308,28 +4311,34 @@
         <v>17</v>
       </c>
       <c r="D49" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="E49" t="s">
-        <v>181</v>
+        <v>184</v>
+      </c>
+      <c r="G49" t="s">
+        <v>24</v>
+      </c>
+      <c r="H49">
+        <v>29</v>
       </c>
       <c r="I49" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="J49">
-        <v>111188144</v>
+        <v>106144583</v>
       </c>
       <c r="K49" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="L49" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
       <c r="M49">
-        <v>47248932</v>
+        <v>13656680</v>
       </c>
       <c r="N49">
-        <v>47249567</v>
+        <v>13657837</v>
       </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.2">
@@ -4343,34 +4352,37 @@
         <v>17</v>
       </c>
       <c r="D50" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="E50" t="s">
-        <v>184</v>
+        <v>188</v>
+      </c>
+      <c r="F50" t="s">
+        <v>189</v>
       </c>
       <c r="G50" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="H50">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="I50" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="J50">
-        <v>106144583</v>
+        <v>100616445</v>
       </c>
       <c r="K50" t="s">
         <v>20</v>
       </c>
       <c r="L50" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="M50">
-        <v>13656680</v>
+        <v>385095</v>
       </c>
       <c r="N50">
-        <v>13657837</v>
+        <v>387637</v>
       </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.2">
@@ -4384,37 +4396,34 @@
         <v>17</v>
       </c>
       <c r="D51" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="E51" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="F51" t="s">
-        <v>189</v>
-      </c>
-      <c r="G51" t="s">
-        <v>19</v>
+        <v>194</v>
       </c>
       <c r="H51">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="I51" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="J51">
-        <v>100616445</v>
+        <v>100616199</v>
       </c>
       <c r="K51" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="L51" t="s">
         <v>191</v>
       </c>
       <c r="M51">
-        <v>385095</v>
+        <v>9622047</v>
       </c>
       <c r="N51">
-        <v>387637</v>
+        <v>9622385</v>
       </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.2">
@@ -4428,34 +4437,25 @@
         <v>17</v>
       </c>
       <c r="D52" t="s">
-        <v>192</v>
-      </c>
-      <c r="E52" t="s">
-        <v>193</v>
-      </c>
-      <c r="F52" t="s">
-        <v>194</v>
+        <v>196</v>
+      </c>
+      <c r="G52" t="s">
+        <v>19</v>
       </c>
       <c r="H52">
-        <v>7</v>
-      </c>
-      <c r="I52" t="s">
-        <v>195</v>
-      </c>
-      <c r="J52">
-        <v>100616199</v>
+        <v>52</v>
       </c>
       <c r="K52" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="L52" t="s">
         <v>191</v>
       </c>
       <c r="M52">
-        <v>9622047</v>
+        <v>20387400</v>
       </c>
       <c r="N52">
-        <v>9622385</v>
+        <v>20397512</v>
       </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.2">
@@ -4469,13 +4469,25 @@
         <v>17</v>
       </c>
       <c r="D53" t="s">
-        <v>196</v>
+        <v>197</v>
+      </c>
+      <c r="E53" t="s">
+        <v>198</v>
+      </c>
+      <c r="F53" t="s">
+        <v>199</v>
       </c>
       <c r="G53" t="s">
-        <v>19</v>
+        <v>81</v>
       </c>
       <c r="H53">
-        <v>52</v>
+        <v>1</v>
+      </c>
+      <c r="I53" t="s">
+        <v>200</v>
+      </c>
+      <c r="J53">
+        <v>105372315</v>
       </c>
       <c r="K53" t="s">
         <v>20</v>
@@ -4484,10 +4496,10 @@
         <v>191</v>
       </c>
       <c r="M53">
-        <v>20387400</v>
+        <v>20480255</v>
       </c>
       <c r="N53">
-        <v>20397512</v>
+        <v>20481117</v>
       </c>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.2">
@@ -4501,37 +4513,25 @@
         <v>17</v>
       </c>
       <c r="D54" t="s">
-        <v>197</v>
-      </c>
-      <c r="E54" t="s">
-        <v>198</v>
-      </c>
-      <c r="F54" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="G54" t="s">
-        <v>81</v>
+        <v>19</v>
       </c>
       <c r="H54">
-        <v>1</v>
-      </c>
-      <c r="I54" t="s">
-        <v>200</v>
-      </c>
-      <c r="J54">
-        <v>105372315</v>
+        <v>113</v>
       </c>
       <c r="K54" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="L54" t="s">
         <v>191</v>
       </c>
       <c r="M54">
-        <v>20480255</v>
+        <v>21841536</v>
       </c>
       <c r="N54">
-        <v>20481117</v>
+        <v>21841542</v>
       </c>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.2">
@@ -4545,25 +4545,25 @@
         <v>17</v>
       </c>
       <c r="D55" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="G55" t="s">
         <v>19</v>
       </c>
       <c r="H55">
-        <v>113</v>
+        <v>51</v>
       </c>
       <c r="K55" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="L55" t="s">
         <v>191</v>
       </c>
       <c r="M55">
-        <v>21841536</v>
+        <v>22757824</v>
       </c>
       <c r="N55">
-        <v>21841542</v>
+        <v>22764561</v>
       </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.2">
@@ -4577,25 +4577,25 @@
         <v>17</v>
       </c>
       <c r="D56" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="G56" t="s">
         <v>19</v>
       </c>
       <c r="H56">
-        <v>51</v>
+        <v>19</v>
       </c>
       <c r="K56" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="L56" t="s">
         <v>191</v>
       </c>
       <c r="M56">
-        <v>22757824</v>
+        <v>28128498</v>
       </c>
       <c r="N56">
-        <v>22764561</v>
+        <v>28137361</v>
       </c>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.2">
@@ -4609,13 +4609,19 @@
         <v>17</v>
       </c>
       <c r="D57" t="s">
-        <v>203</v>
-      </c>
-      <c r="G57" t="s">
-        <v>19</v>
+        <v>204</v>
+      </c>
+      <c r="E57" t="s">
+        <v>205</v>
       </c>
       <c r="H57">
-        <v>19</v>
+        <v>28</v>
+      </c>
+      <c r="I57" t="s">
+        <v>206</v>
+      </c>
+      <c r="J57">
+        <v>106707175</v>
       </c>
       <c r="K57" t="s">
         <v>43</v>
@@ -4624,10 +4630,10 @@
         <v>191</v>
       </c>
       <c r="M57">
-        <v>28128498</v>
+        <v>28135954</v>
       </c>
       <c r="N57">
-        <v>28137361</v>
+        <v>28136531</v>
       </c>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.2">
@@ -4640,32 +4646,26 @@
       <c r="C58" t="s">
         <v>17</v>
       </c>
-      <c r="D58" t="s">
-        <v>204</v>
-      </c>
       <c r="E58" t="s">
-        <v>205</v>
+        <v>207</v>
+      </c>
+      <c r="F58" t="s">
+        <v>208</v>
       </c>
       <c r="H58">
-        <v>28</v>
-      </c>
-      <c r="I58" t="s">
-        <v>206</v>
-      </c>
-      <c r="J58">
-        <v>106707175</v>
+        <v>4700</v>
       </c>
       <c r="K58" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="L58" t="s">
         <v>191</v>
       </c>
       <c r="M58">
-        <v>28135954</v>
+        <v>29097595</v>
       </c>
       <c r="N58">
-        <v>28136531</v>
+        <v>29106136</v>
       </c>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.2">
@@ -4678,11 +4678,23 @@
       <c r="C59" t="s">
         <v>17</v>
       </c>
+      <c r="D59" t="s">
+        <v>209</v>
+      </c>
       <c r="E59" t="s">
-        <v>207</v>
-      </c>
-      <c r="F59" t="s">
-        <v>208</v>
+        <v>210</v>
+      </c>
+      <c r="G59" t="s">
+        <v>19</v>
+      </c>
+      <c r="H59">
+        <v>29</v>
+      </c>
+      <c r="I59" t="s">
+        <v>211</v>
+      </c>
+      <c r="J59">
+        <v>106144555</v>
       </c>
       <c r="K59" t="s">
         <v>20</v>
@@ -4691,10 +4703,10 @@
         <v>191</v>
       </c>
       <c r="M59">
-        <v>29097595</v>
+        <v>37597549</v>
       </c>
       <c r="N59">
-        <v>29106136</v>
+        <v>37607066</v>
       </c>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.2">
@@ -4708,34 +4720,31 @@
         <v>17</v>
       </c>
       <c r="D60" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="E60" t="s">
-        <v>210</v>
-      </c>
-      <c r="G60" t="s">
-        <v>19</v>
+        <v>213</v>
       </c>
       <c r="H60">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="I60" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="J60">
-        <v>106144555</v>
+        <v>111188141</v>
       </c>
       <c r="K60" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="L60" t="s">
         <v>191</v>
       </c>
       <c r="M60">
-        <v>37597549</v>
+        <v>39426730</v>
       </c>
       <c r="N60">
-        <v>37607066</v>
+        <v>39427348</v>
       </c>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.2">
@@ -4749,19 +4758,22 @@
         <v>17</v>
       </c>
       <c r="D61" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="E61" t="s">
-        <v>213</v>
+        <v>216</v>
+      </c>
+      <c r="F61" t="s">
+        <v>217</v>
       </c>
       <c r="H61">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="I61" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="J61">
-        <v>111188141</v>
+        <v>100616107</v>
       </c>
       <c r="K61" t="s">
         <v>43</v>
@@ -4770,10 +4782,10 @@
         <v>191</v>
       </c>
       <c r="M61">
-        <v>39426730</v>
+        <v>52311587</v>
       </c>
       <c r="N61">
-        <v>39427348</v>
+        <v>52311924</v>
       </c>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.2">
@@ -4787,34 +4799,37 @@
         <v>17</v>
       </c>
       <c r="D62" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="E62" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="F62" t="s">
-        <v>217</v>
+        <v>221</v>
+      </c>
+      <c r="G62" t="s">
+        <v>222</v>
       </c>
       <c r="H62">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I62" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="J62">
-        <v>100616107</v>
+        <v>107985332</v>
       </c>
       <c r="K62" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="L62" t="s">
         <v>191</v>
       </c>
       <c r="M62">
-        <v>52311587</v>
+        <v>53510765</v>
       </c>
       <c r="N62">
-        <v>52311924</v>
+        <v>53516433</v>
       </c>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.2">
@@ -4828,25 +4843,25 @@
         <v>17</v>
       </c>
       <c r="D63" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="E63" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="F63" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="G63" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="H63">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I63" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="J63">
-        <v>107985332</v>
+        <v>147664</v>
       </c>
       <c r="K63" t="s">
         <v>20</v>
@@ -4855,10 +4870,10 @@
         <v>191</v>
       </c>
       <c r="M63">
-        <v>53510765</v>
+        <v>53517174</v>
       </c>
       <c r="N63">
-        <v>53516433</v>
+        <v>53519376</v>
       </c>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.2">
@@ -4872,25 +4887,25 @@
         <v>17</v>
       </c>
       <c r="D64" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="E64" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="F64" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="G64" t="s">
         <v>227</v>
       </c>
       <c r="H64">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I64" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="J64">
-        <v>147664</v>
+        <v>100271846</v>
       </c>
       <c r="K64" t="s">
         <v>20</v>
@@ -4899,10 +4914,10 @@
         <v>191</v>
       </c>
       <c r="M64">
-        <v>53517174</v>
+        <v>53547993</v>
       </c>
       <c r="N64">
-        <v>53519376</v>
+        <v>53554933</v>
       </c>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.2">
@@ -4916,25 +4931,13 @@
         <v>17</v>
       </c>
       <c r="D65" t="s">
-        <v>229</v>
-      </c>
-      <c r="E65" t="s">
-        <v>230</v>
-      </c>
-      <c r="F65" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="G65" t="s">
-        <v>227</v>
+        <v>19</v>
       </c>
       <c r="H65">
-        <v>2</v>
-      </c>
-      <c r="I65" t="s">
-        <v>232</v>
-      </c>
-      <c r="J65">
-        <v>100271846</v>
+        <v>13</v>
       </c>
       <c r="K65" t="s">
         <v>20</v>
@@ -4943,10 +4946,10 @@
         <v>191</v>
       </c>
       <c r="M65">
-        <v>53547993</v>
+        <v>53862348</v>
       </c>
       <c r="N65">
-        <v>53554933</v>
+        <v>53868044</v>
       </c>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.2">
@@ -4960,13 +4963,22 @@
         <v>17</v>
       </c>
       <c r="D66" t="s">
-        <v>233</v>
-      </c>
-      <c r="G66" t="s">
-        <v>19</v>
+        <v>234</v>
+      </c>
+      <c r="E66" t="s">
+        <v>235</v>
+      </c>
+      <c r="F66" t="s">
+        <v>236</v>
       </c>
       <c r="H66">
-        <v>13</v>
+        <v>1</v>
+      </c>
+      <c r="I66" t="s">
+        <v>237</v>
+      </c>
+      <c r="J66">
+        <v>105372481</v>
       </c>
       <c r="K66" t="s">
         <v>20</v>
@@ -4975,10 +4987,10 @@
         <v>191</v>
       </c>
       <c r="M66">
-        <v>53862348</v>
+        <v>58816743</v>
       </c>
       <c r="N66">
-        <v>53868044</v>
+        <v>58828178</v>
       </c>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.2">
@@ -4992,34 +5004,31 @@
         <v>17</v>
       </c>
       <c r="D67" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="E67" t="s">
-        <v>235</v>
-      </c>
-      <c r="F67" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="H67">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I67" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="J67">
-        <v>105372481</v>
+        <v>111188149</v>
       </c>
       <c r="K67" t="s">
         <v>20</v>
       </c>
       <c r="L67" t="s">
-        <v>191</v>
+        <v>241</v>
       </c>
       <c r="M67">
-        <v>58816743</v>
+        <v>20126709</v>
       </c>
       <c r="N67">
-        <v>58828178</v>
+        <v>20127340</v>
       </c>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.2">
@@ -5033,19 +5042,22 @@
         <v>17</v>
       </c>
       <c r="D68" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="E68" t="s">
-        <v>239</v>
+        <v>243</v>
+      </c>
+      <c r="G68" t="s">
+        <v>24</v>
       </c>
       <c r="H68">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="I68" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="J68">
-        <v>111188149</v>
+        <v>106144580</v>
       </c>
       <c r="K68" t="s">
         <v>20</v>
@@ -5054,10 +5066,10 @@
         <v>241</v>
       </c>
       <c r="M68">
-        <v>20126709</v>
+        <v>53983779</v>
       </c>
       <c r="N68">
-        <v>20127340</v>
+        <v>53988562</v>
       </c>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.2">
@@ -5071,22 +5083,22 @@
         <v>17</v>
       </c>
       <c r="D69" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="E69" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="G69" t="s">
         <v>24</v>
       </c>
       <c r="H69">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I69" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="J69">
-        <v>106144580</v>
+        <v>106144576</v>
       </c>
       <c r="K69" t="s">
         <v>20</v>
@@ -5095,10 +5107,10 @@
         <v>241</v>
       </c>
       <c r="M69">
-        <v>53983779</v>
+        <v>112796922</v>
       </c>
       <c r="N69">
-        <v>53988562</v>
+        <v>112802566</v>
       </c>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.2">
@@ -5112,22 +5124,22 @@
         <v>17</v>
       </c>
       <c r="D70" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="E70" t="s">
-        <v>246</v>
+        <v>249</v>
+      </c>
+      <c r="F70" t="s">
+        <v>250</v>
       </c>
       <c r="G70" t="s">
-        <v>24</v>
+        <v>76</v>
       </c>
       <c r="H70">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="I70" t="s">
-        <v>247</v>
-      </c>
-      <c r="J70">
-        <v>106144576</v>
+        <v>251</v>
       </c>
       <c r="K70" t="s">
         <v>20</v>
@@ -5136,10 +5148,10 @@
         <v>241</v>
       </c>
       <c r="M70">
-        <v>112796922</v>
+        <v>155723544</v>
       </c>
       <c r="N70">
-        <v>112802566</v>
+        <v>155731248</v>
       </c>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.2">
@@ -5153,34 +5165,34 @@
         <v>17</v>
       </c>
       <c r="D71" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="E71" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="F71" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="G71" t="s">
         <v>76</v>
       </c>
       <c r="H71">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I71" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="K71" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="L71" t="s">
         <v>241</v>
       </c>
       <c r="M71">
-        <v>155723544</v>
+        <v>166563971</v>
       </c>
       <c r="N71">
-        <v>155731248</v>
+        <v>166572761</v>
       </c>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.2">
@@ -5194,34 +5206,34 @@
         <v>17</v>
       </c>
       <c r="D72" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="E72" t="s">
-        <v>253</v>
-      </c>
-      <c r="F72" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="G72" t="s">
-        <v>76</v>
+        <v>24</v>
       </c>
       <c r="H72">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="I72" t="s">
-        <v>255</v>
+        <v>258</v>
+      </c>
+      <c r="J72">
+        <v>106144561</v>
       </c>
       <c r="K72" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="L72" t="s">
         <v>241</v>
       </c>
       <c r="M72">
-        <v>166563971</v>
+        <v>178273972</v>
       </c>
       <c r="N72">
-        <v>166572761</v>
+        <v>178277886</v>
       </c>
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.2">
@@ -5235,22 +5247,22 @@
         <v>17</v>
       </c>
       <c r="D73" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="E73" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="G73" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="H73">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="I73" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="J73">
-        <v>106144561</v>
+        <v>106144591</v>
       </c>
       <c r="K73" t="s">
         <v>20</v>
@@ -5259,10 +5271,10 @@
         <v>241</v>
       </c>
       <c r="M73">
-        <v>178273972</v>
+        <v>187385634</v>
       </c>
       <c r="N73">
-        <v>178277886</v>
+        <v>187387099</v>
       </c>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.2">
@@ -5276,34 +5288,31 @@
         <v>17</v>
       </c>
       <c r="D74" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="E74" t="s">
-        <v>260</v>
-      </c>
-      <c r="G74" t="s">
-        <v>19</v>
+        <v>263</v>
       </c>
       <c r="H74">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="I74" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="J74">
-        <v>106144591</v>
+        <v>100616108</v>
       </c>
       <c r="K74" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="L74" t="s">
-        <v>241</v>
+        <v>265</v>
       </c>
       <c r="M74">
-        <v>187385634</v>
+        <v>25379489</v>
       </c>
       <c r="N74">
-        <v>187387099</v>
+        <v>25379824</v>
       </c>
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.2">
@@ -5317,31 +5326,25 @@
         <v>17</v>
       </c>
       <c r="D75" t="s">
-        <v>262</v>
-      </c>
-      <c r="E75" t="s">
-        <v>263</v>
+        <v>266</v>
+      </c>
+      <c r="G75" t="s">
+        <v>19</v>
       </c>
       <c r="H75">
-        <v>8</v>
-      </c>
-      <c r="I75" t="s">
-        <v>264</v>
-      </c>
-      <c r="J75">
-        <v>100616108</v>
+        <v>59</v>
       </c>
       <c r="K75" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="L75" t="s">
         <v>265</v>
       </c>
       <c r="M75">
-        <v>25379489</v>
+        <v>32714750</v>
       </c>
       <c r="N75">
-        <v>25379824</v>
+        <v>32724384</v>
       </c>
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.2">
@@ -5355,25 +5358,37 @@
         <v>17</v>
       </c>
       <c r="D76" t="s">
-        <v>266</v>
+        <v>267</v>
+      </c>
+      <c r="E76" t="s">
+        <v>268</v>
+      </c>
+      <c r="F76" t="s">
+        <v>269</v>
       </c>
       <c r="G76" t="s">
         <v>19</v>
       </c>
       <c r="H76">
-        <v>59</v>
+        <v>23</v>
+      </c>
+      <c r="I76" t="s">
+        <v>270</v>
+      </c>
+      <c r="J76">
+        <v>100616197</v>
       </c>
       <c r="K76" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="L76" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="M76">
-        <v>32714750</v>
+        <v>19933916</v>
       </c>
       <c r="N76">
-        <v>32724384</v>
+        <v>19934992</v>
       </c>
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.2">
@@ -5387,25 +5402,22 @@
         <v>17</v>
       </c>
       <c r="D77" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="E77" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="F77" t="s">
-        <v>269</v>
-      </c>
-      <c r="G77" t="s">
-        <v>19</v>
+        <v>274</v>
       </c>
       <c r="H77">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="I77" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="J77">
-        <v>100616197</v>
+        <v>90625</v>
       </c>
       <c r="K77" t="s">
         <v>43</v>
@@ -5414,10 +5426,10 @@
         <v>271</v>
       </c>
       <c r="M77">
-        <v>19933916</v>
+        <v>44336913</v>
       </c>
       <c r="N77">
-        <v>19934992</v>
+        <v>44345740</v>
       </c>
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.2">
@@ -5431,34 +5443,37 @@
         <v>17</v>
       </c>
       <c r="D78" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="E78" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="F78" t="s">
-        <v>274</v>
+        <v>278</v>
+      </c>
+      <c r="G78" t="s">
+        <v>19</v>
       </c>
       <c r="H78">
-        <v>1</v>
+        <v>101</v>
       </c>
       <c r="I78" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="J78">
-        <v>90625</v>
+        <v>100862684</v>
       </c>
       <c r="K78" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="L78" t="s">
-        <v>271</v>
+        <v>280</v>
       </c>
       <c r="M78">
-        <v>44336913</v>
+        <v>18926187</v>
       </c>
       <c r="N78">
-        <v>44345740</v>
+        <v>18934279</v>
       </c>
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.2">
@@ -5472,25 +5487,13 @@
         <v>17</v>
       </c>
       <c r="D79" t="s">
-        <v>276</v>
-      </c>
-      <c r="E79" t="s">
-        <v>277</v>
-      </c>
-      <c r="F79" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="G79" t="s">
         <v>19</v>
       </c>
       <c r="H79">
-        <v>101</v>
-      </c>
-      <c r="I79" t="s">
-        <v>279</v>
-      </c>
-      <c r="J79">
-        <v>100862684</v>
+        <v>345</v>
       </c>
       <c r="K79" t="s">
         <v>20</v>
@@ -5499,10 +5502,10 @@
         <v>280</v>
       </c>
       <c r="M79">
-        <v>18926187</v>
+        <v>23879930</v>
       </c>
       <c r="N79">
-        <v>18934279</v>
+        <v>23888810</v>
       </c>
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.2">
@@ -5516,25 +5519,37 @@
         <v>17</v>
       </c>
       <c r="D80" t="s">
-        <v>281</v>
+        <v>282</v>
+      </c>
+      <c r="E80" t="s">
+        <v>283</v>
+      </c>
+      <c r="F80" t="s">
+        <v>284</v>
       </c>
       <c r="G80" t="s">
         <v>19</v>
       </c>
       <c r="H80">
-        <v>345</v>
+        <v>2</v>
+      </c>
+      <c r="I80" t="s">
+        <v>285</v>
+      </c>
+      <c r="J80">
+        <v>100616100</v>
       </c>
       <c r="K80" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="L80" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="M80">
-        <v>23879930</v>
+        <v>9889346</v>
       </c>
       <c r="N80">
-        <v>23888810</v>
+        <v>9896236</v>
       </c>
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.2">
@@ -5548,25 +5563,22 @@
         <v>17</v>
       </c>
       <c r="D81" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="E81" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="F81" t="s">
-        <v>284</v>
-      </c>
-      <c r="G81" t="s">
-        <v>19</v>
+        <v>289</v>
       </c>
       <c r="H81">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I81" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="J81">
-        <v>100616100</v>
+        <v>100862693</v>
       </c>
       <c r="K81" t="s">
         <v>43</v>
@@ -5575,10 +5587,10 @@
         <v>286</v>
       </c>
       <c r="M81">
-        <v>9889346</v>
+        <v>16811648</v>
       </c>
       <c r="N81">
-        <v>9896236</v>
+        <v>16812243</v>
       </c>
     </row>
     <row r="82" spans="1:14" x14ac:dyDescent="0.2">
@@ -5592,34 +5604,37 @@
         <v>17</v>
       </c>
       <c r="D82" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="E82" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="F82" t="s">
-        <v>289</v>
+        <v>293</v>
+      </c>
+      <c r="G82" t="s">
+        <v>19</v>
       </c>
       <c r="H82">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I82" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="J82">
-        <v>100862693</v>
+        <v>60358</v>
       </c>
       <c r="K82" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="L82" t="s">
         <v>286</v>
       </c>
       <c r="M82">
-        <v>16811648</v>
+        <v>101409738</v>
       </c>
       <c r="N82">
-        <v>16812243</v>
+        <v>101420859</v>
       </c>
     </row>
     <row r="83" spans="1:14" x14ac:dyDescent="0.2">
@@ -5633,37 +5648,37 @@
         <v>17</v>
       </c>
       <c r="D83" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="E83" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="F83" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="G83" t="s">
         <v>19</v>
       </c>
       <c r="H83">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="I83" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="J83">
-        <v>60358</v>
+        <v>100862689</v>
       </c>
       <c r="K83" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="L83" t="s">
         <v>286</v>
       </c>
       <c r="M83">
-        <v>101409738</v>
+        <v>112743479</v>
       </c>
       <c r="N83">
-        <v>101420859</v>
+        <v>112752282</v>
       </c>
     </row>
     <row r="84" spans="1:14" x14ac:dyDescent="0.2">
@@ -5677,37 +5692,37 @@
         <v>17</v>
       </c>
       <c r="D84" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="E84" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="F84" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="G84" t="s">
         <v>19</v>
       </c>
       <c r="H84">
-        <v>106</v>
+        <v>4</v>
       </c>
       <c r="I84" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="J84">
-        <v>100862689</v>
+        <v>60359</v>
       </c>
       <c r="K84" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="L84" t="s">
         <v>286</v>
       </c>
       <c r="M84">
-        <v>112743479</v>
+        <v>125608304</v>
       </c>
       <c r="N84">
-        <v>112752282</v>
+        <v>125619438</v>
       </c>
     </row>
     <row r="85" spans="1:14" x14ac:dyDescent="0.2">
@@ -5721,25 +5736,25 @@
         <v>17</v>
       </c>
       <c r="D85" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="E85" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="F85" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="G85" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="H85">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I85" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="J85">
-        <v>60359</v>
+        <v>100862696</v>
       </c>
       <c r="K85" t="s">
         <v>20</v>
@@ -5748,10 +5763,10 @@
         <v>286</v>
       </c>
       <c r="M85">
-        <v>125608304</v>
+        <v>141538631</v>
       </c>
       <c r="N85">
-        <v>125619438</v>
+        <v>141540355</v>
       </c>
     </row>
     <row r="86" spans="1:14" x14ac:dyDescent="0.2">
@@ -5765,37 +5780,37 @@
         <v>17</v>
       </c>
       <c r="D86" t="s">
-        <v>303</v>
+        <v>233</v>
       </c>
       <c r="E86" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="F86" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="G86" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="H86">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="I86" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="J86">
-        <v>100862696</v>
+        <v>100861467</v>
       </c>
       <c r="K86" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="L86" t="s">
         <v>286</v>
       </c>
       <c r="M86">
-        <v>141538631</v>
+        <v>148281477</v>
       </c>
       <c r="N86">
-        <v>141540355</v>
+        <v>148285396</v>
       </c>
     </row>
     <row r="87" spans="1:14" x14ac:dyDescent="0.2">
@@ -5809,25 +5824,22 @@
         <v>17</v>
       </c>
       <c r="D87" t="s">
-        <v>233</v>
+        <v>310</v>
       </c>
       <c r="E87" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="F87" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="G87" t="s">
-        <v>19</v>
+        <v>76</v>
       </c>
       <c r="H87">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I87" t="s">
-        <v>309</v>
-      </c>
-      <c r="J87">
-        <v>100861467</v>
+        <v>313</v>
       </c>
       <c r="K87" t="s">
         <v>43</v>
@@ -5836,10 +5848,10 @@
         <v>286</v>
       </c>
       <c r="M87">
-        <v>148281477</v>
+        <v>166540223</v>
       </c>
       <c r="N87">
-        <v>148285396</v>
+        <v>166547792</v>
       </c>
     </row>
     <row r="88" spans="1:14" x14ac:dyDescent="0.2">
@@ -5853,34 +5865,37 @@
         <v>17</v>
       </c>
       <c r="D88" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="E88" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="F88" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="G88" t="s">
-        <v>76</v>
+        <v>24</v>
       </c>
       <c r="H88">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I88" t="s">
-        <v>313</v>
+        <v>317</v>
+      </c>
+      <c r="J88">
+        <v>100862695</v>
       </c>
       <c r="K88" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="L88" t="s">
         <v>286</v>
       </c>
       <c r="M88">
-        <v>166540223</v>
+        <v>178772378</v>
       </c>
       <c r="N88">
-        <v>166547792</v>
+        <v>178777943</v>
       </c>
     </row>
     <row r="89" spans="1:14" x14ac:dyDescent="0.2">
@@ -5894,37 +5909,31 @@
         <v>17</v>
       </c>
       <c r="D89" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="E89" t="s">
-        <v>315</v>
-      </c>
-      <c r="F89" t="s">
-        <v>316</v>
-      </c>
-      <c r="G89" t="s">
-        <v>24</v>
+        <v>319</v>
       </c>
       <c r="H89">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I89" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="J89">
-        <v>100862695</v>
+        <v>111188148</v>
       </c>
       <c r="K89" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="L89" t="s">
         <v>286</v>
       </c>
       <c r="M89">
-        <v>178772378</v>
+        <v>184731488</v>
       </c>
       <c r="N89">
-        <v>178777943</v>
+        <v>184732117</v>
       </c>
     </row>
     <row r="90" spans="1:14" x14ac:dyDescent="0.2">
@@ -5938,19 +5947,25 @@
         <v>17</v>
       </c>
       <c r="D90" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="E90" t="s">
-        <v>319</v>
+        <v>322</v>
+      </c>
+      <c r="F90" t="s">
+        <v>323</v>
+      </c>
+      <c r="G90" t="s">
+        <v>19</v>
       </c>
       <c r="H90">
-        <v>3</v>
+        <v>117</v>
       </c>
       <c r="I90" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="J90">
-        <v>111188148</v>
+        <v>100862688</v>
       </c>
       <c r="K90" t="s">
         <v>43</v>
@@ -5959,10 +5974,10 @@
         <v>286</v>
       </c>
       <c r="M90">
-        <v>184731488</v>
+        <v>185280336</v>
       </c>
       <c r="N90">
-        <v>184732117</v>
+        <v>185289515</v>
       </c>
     </row>
     <row r="91" spans="1:14" x14ac:dyDescent="0.2">
@@ -5976,37 +5991,25 @@
         <v>17</v>
       </c>
       <c r="D91" t="s">
-        <v>321</v>
-      </c>
-      <c r="E91" t="s">
-        <v>322</v>
-      </c>
-      <c r="F91" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="G91" t="s">
         <v>19</v>
       </c>
       <c r="H91">
-        <v>117</v>
-      </c>
-      <c r="I91" t="s">
-        <v>324</v>
-      </c>
-      <c r="J91">
-        <v>100862688</v>
+        <v>77</v>
       </c>
       <c r="K91" t="s">
         <v>43</v>
       </c>
       <c r="L91" t="s">
-        <v>286</v>
+        <v>326</v>
       </c>
       <c r="M91">
-        <v>185280336</v>
+        <v>3980069</v>
       </c>
       <c r="N91">
-        <v>185289515</v>
+        <v>3988631</v>
       </c>
     </row>
     <row r="92" spans="1:14" x14ac:dyDescent="0.2">
@@ -6020,25 +6023,34 @@
         <v>17</v>
       </c>
       <c r="D92" t="s">
-        <v>325</v>
+        <v>327</v>
+      </c>
+      <c r="E92" t="s">
+        <v>328</v>
       </c>
       <c r="G92" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="H92">
-        <v>77</v>
+        <v>15</v>
+      </c>
+      <c r="I92" t="s">
+        <v>329</v>
+      </c>
+      <c r="J92">
+        <v>106144597</v>
       </c>
       <c r="K92" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="L92" t="s">
         <v>326</v>
       </c>
       <c r="M92">
-        <v>3980069</v>
+        <v>8422091</v>
       </c>
       <c r="N92">
-        <v>3988631</v>
+        <v>8429492</v>
       </c>
     </row>
     <row r="93" spans="1:14" x14ac:dyDescent="0.2">
@@ -6052,22 +6064,13 @@
         <v>17</v>
       </c>
       <c r="D93" t="s">
-        <v>327</v>
-      </c>
-      <c r="E93" t="s">
-        <v>328</v>
+        <v>83</v>
       </c>
       <c r="G93" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="H93">
-        <v>15</v>
-      </c>
-      <c r="I93" t="s">
-        <v>329</v>
-      </c>
-      <c r="J93">
-        <v>106144597</v>
+        <v>17</v>
       </c>
       <c r="K93" t="s">
         <v>20</v>
@@ -6076,10 +6079,10 @@
         <v>326</v>
       </c>
       <c r="M93">
-        <v>8422091</v>
+        <v>9123515</v>
       </c>
       <c r="N93">
-        <v>8429492</v>
+        <v>9133075</v>
       </c>
     </row>
     <row r="94" spans="1:14" x14ac:dyDescent="0.2">
@@ -6093,13 +6096,13 @@
         <v>17</v>
       </c>
       <c r="D94" t="s">
-        <v>83</v>
+        <v>117</v>
       </c>
       <c r="G94" t="s">
         <v>19</v>
       </c>
       <c r="H94">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="K94" t="s">
         <v>20</v>
@@ -6108,10 +6111,10 @@
         <v>326</v>
       </c>
       <c r="M94">
-        <v>9123515</v>
+        <v>9659588</v>
       </c>
       <c r="N94">
-        <v>9133075</v>
+        <v>9668650</v>
       </c>
     </row>
     <row r="95" spans="1:14" x14ac:dyDescent="0.2">
@@ -6125,25 +6128,37 @@
         <v>17</v>
       </c>
       <c r="D95" t="s">
-        <v>117</v>
+        <v>330</v>
+      </c>
+      <c r="E95" t="s">
+        <v>331</v>
+      </c>
+      <c r="F95" t="s">
+        <v>332</v>
       </c>
       <c r="G95" t="s">
-        <v>19</v>
+        <v>76</v>
       </c>
       <c r="H95">
-        <v>50</v>
+        <v>1</v>
+      </c>
+      <c r="I95" t="s">
+        <v>333</v>
+      </c>
+      <c r="J95">
+        <v>100616446</v>
       </c>
       <c r="K95" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="L95" t="s">
         <v>326</v>
       </c>
       <c r="M95">
-        <v>9659588</v>
+        <v>23724532</v>
       </c>
       <c r="N95">
-        <v>9668650</v>
+        <v>23728952</v>
       </c>
     </row>
     <row r="96" spans="1:14" x14ac:dyDescent="0.2">
@@ -6157,25 +6172,22 @@
         <v>17</v>
       </c>
       <c r="D96" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="E96" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="F96" t="s">
-        <v>332</v>
-      </c>
-      <c r="G96" t="s">
-        <v>76</v>
+        <v>336</v>
       </c>
       <c r="H96">
         <v>1</v>
       </c>
       <c r="I96" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="J96">
-        <v>100616446</v>
+        <v>100288413</v>
       </c>
       <c r="K96" t="s">
         <v>43</v>
@@ -6184,10 +6196,10 @@
         <v>326</v>
       </c>
       <c r="M96">
-        <v>23724532</v>
+        <v>53608720</v>
       </c>
       <c r="N96">
-        <v>23728952</v>
+        <v>53617592</v>
       </c>
     </row>
     <row r="97" spans="1:14" x14ac:dyDescent="0.2">
@@ -6201,34 +6213,34 @@
         <v>17</v>
       </c>
       <c r="D97" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="E97" t="s">
-        <v>335</v>
-      </c>
-      <c r="F97" t="s">
-        <v>336</v>
+        <v>339</v>
+      </c>
+      <c r="G97" t="s">
+        <v>24</v>
       </c>
       <c r="H97">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="I97" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="J97">
-        <v>100288413</v>
+        <v>106144581</v>
       </c>
       <c r="K97" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="L97" t="s">
         <v>326</v>
       </c>
       <c r="M97">
-        <v>53608720</v>
+        <v>133803454</v>
       </c>
       <c r="N97">
-        <v>53617592</v>
+        <v>133810293</v>
       </c>
     </row>
     <row r="98" spans="1:14" x14ac:dyDescent="0.2">
@@ -6242,22 +6254,22 @@
         <v>17</v>
       </c>
       <c r="D98" t="s">
-        <v>338</v>
+        <v>48</v>
       </c>
       <c r="E98" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="G98" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="H98">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="I98" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="J98">
-        <v>106144581</v>
+        <v>100616442</v>
       </c>
       <c r="K98" t="s">
         <v>20</v>
@@ -6266,10 +6278,10 @@
         <v>326</v>
       </c>
       <c r="M98">
-        <v>133803454</v>
+        <v>165916840</v>
       </c>
       <c r="N98">
-        <v>133810293</v>
+        <v>165924068</v>
       </c>
     </row>
     <row r="99" spans="1:14" x14ac:dyDescent="0.2">
@@ -6283,34 +6295,31 @@
         <v>17</v>
       </c>
       <c r="D99" t="s">
-        <v>48</v>
+        <v>343</v>
       </c>
       <c r="E99" t="s">
-        <v>341</v>
-      </c>
-      <c r="G99" t="s">
-        <v>19</v>
+        <v>344</v>
       </c>
       <c r="H99">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="I99" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="J99">
-        <v>100616442</v>
+        <v>111188147</v>
       </c>
       <c r="K99" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="L99" t="s">
-        <v>326</v>
+        <v>346</v>
       </c>
       <c r="M99">
-        <v>165916840</v>
+        <v>1578855</v>
       </c>
       <c r="N99">
-        <v>165924068</v>
+        <v>1579485</v>
       </c>
     </row>
     <row r="100" spans="1:14" x14ac:dyDescent="0.2">
@@ -6324,19 +6333,13 @@
         <v>17</v>
       </c>
       <c r="D100" t="s">
-        <v>343</v>
-      </c>
-      <c r="E100" t="s">
-        <v>344</v>
+        <v>347</v>
+      </c>
+      <c r="G100" t="s">
+        <v>19</v>
       </c>
       <c r="H100">
-        <v>5</v>
-      </c>
-      <c r="I100" t="s">
-        <v>345</v>
-      </c>
-      <c r="J100">
-        <v>111188147</v>
+        <v>104</v>
       </c>
       <c r="K100" t="s">
         <v>43</v>
@@ -6345,10 +6348,10 @@
         <v>346</v>
       </c>
       <c r="M100">
-        <v>1578855</v>
+        <v>30487114</v>
       </c>
       <c r="N100">
-        <v>1579485</v>
+        <v>30496205</v>
       </c>
     </row>
     <row r="101" spans="1:14" x14ac:dyDescent="0.2">
@@ -6362,13 +6365,19 @@
         <v>17</v>
       </c>
       <c r="D101" t="s">
-        <v>347</v>
-      </c>
-      <c r="G101" t="s">
-        <v>19</v>
+        <v>348</v>
+      </c>
+      <c r="E101" t="s">
+        <v>349</v>
       </c>
       <c r="H101">
-        <v>104</v>
+        <v>4</v>
+      </c>
+      <c r="I101" t="s">
+        <v>350</v>
+      </c>
+      <c r="J101">
+        <v>111188143</v>
       </c>
       <c r="K101" t="s">
         <v>43</v>
@@ -6377,10 +6386,10 @@
         <v>346</v>
       </c>
       <c r="M101">
-        <v>30487114</v>
+        <v>34782791</v>
       </c>
       <c r="N101">
-        <v>30496205</v>
+        <v>34783397</v>
       </c>
     </row>
     <row r="102" spans="1:14" x14ac:dyDescent="0.2">
@@ -6394,31 +6403,34 @@
         <v>17</v>
       </c>
       <c r="D102" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="E102" t="s">
-        <v>349</v>
+        <v>352</v>
+      </c>
+      <c r="F102" t="s">
+        <v>353</v>
       </c>
       <c r="H102">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I102" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="J102">
-        <v>111188143</v>
+        <v>100616462</v>
       </c>
       <c r="K102" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="L102" t="s">
         <v>346</v>
       </c>
       <c r="M102">
-        <v>34782791</v>
+        <v>70871465</v>
       </c>
       <c r="N102">
-        <v>34783397</v>
+        <v>70871802</v>
       </c>
     </row>
     <row r="103" spans="1:14" x14ac:dyDescent="0.2">
@@ -6432,22 +6444,22 @@
         <v>17</v>
       </c>
       <c r="D103" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="E103" t="s">
-        <v>352</v>
-      </c>
-      <c r="F103" t="s">
-        <v>353</v>
+        <v>356</v>
+      </c>
+      <c r="G103" t="s">
+        <v>19</v>
       </c>
       <c r="H103">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="I103" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="J103">
-        <v>100616462</v>
+        <v>106144590</v>
       </c>
       <c r="K103" t="s">
         <v>20</v>
@@ -6456,10 +6468,10 @@
         <v>346</v>
       </c>
       <c r="M103">
-        <v>70871465</v>
+        <v>92792380</v>
       </c>
       <c r="N103">
-        <v>70871802</v>
+        <v>92793912</v>
       </c>
     </row>
     <row r="104" spans="1:14" x14ac:dyDescent="0.2">
@@ -6473,34 +6485,25 @@
         <v>17</v>
       </c>
       <c r="D104" t="s">
-        <v>355</v>
-      </c>
-      <c r="E104" t="s">
-        <v>356</v>
+        <v>44</v>
       </c>
       <c r="G104" t="s">
         <v>19</v>
       </c>
       <c r="H104">
-        <v>31</v>
-      </c>
-      <c r="I104" t="s">
-        <v>357</v>
-      </c>
-      <c r="J104">
-        <v>106144590</v>
+        <v>18</v>
       </c>
       <c r="K104" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="L104" t="s">
         <v>346</v>
       </c>
       <c r="M104">
-        <v>92792380</v>
+        <v>154016502</v>
       </c>
       <c r="N104">
-        <v>92793912</v>
+        <v>154024214</v>
       </c>
     </row>
     <row r="105" spans="1:14" x14ac:dyDescent="0.2">
@@ -6514,13 +6517,22 @@
         <v>17</v>
       </c>
       <c r="D105" t="s">
-        <v>44</v>
+        <v>358</v>
+      </c>
+      <c r="E105" t="s">
+        <v>359</v>
       </c>
       <c r="G105" t="s">
         <v>19</v>
       </c>
       <c r="H105">
-        <v>18</v>
+        <v>107</v>
+      </c>
+      <c r="I105" t="s">
+        <v>360</v>
+      </c>
+      <c r="J105">
+        <v>100616101</v>
       </c>
       <c r="K105" t="s">
         <v>43</v>
@@ -6529,10 +6541,10 @@
         <v>346</v>
       </c>
       <c r="M105">
-        <v>154016502</v>
+        <v>156084717</v>
       </c>
       <c r="N105">
-        <v>154024214</v>
+        <v>156093896</v>
       </c>
     </row>
     <row r="106" spans="1:14" x14ac:dyDescent="0.2">
@@ -6546,34 +6558,37 @@
         <v>17</v>
       </c>
       <c r="D106" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="E106" t="s">
-        <v>359</v>
+        <v>362</v>
+      </c>
+      <c r="F106" t="s">
+        <v>363</v>
       </c>
       <c r="G106" t="s">
-        <v>19</v>
+        <v>222</v>
       </c>
       <c r="H106">
-        <v>107</v>
+        <v>1</v>
       </c>
       <c r="I106" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="J106">
-        <v>100616101</v>
+        <v>405754</v>
       </c>
       <c r="K106" t="s">
         <v>43</v>
       </c>
       <c r="L106" t="s">
-        <v>346</v>
+        <v>365</v>
       </c>
       <c r="M106">
-        <v>156084717</v>
+        <v>11102722</v>
       </c>
       <c r="N106">
-        <v>156093896</v>
+        <v>11105864</v>
       </c>
     </row>
     <row r="107" spans="1:14" x14ac:dyDescent="0.2">
@@ -6587,37 +6602,25 @@
         <v>17</v>
       </c>
       <c r="D107" t="s">
-        <v>361</v>
-      </c>
-      <c r="E107" t="s">
-        <v>362</v>
-      </c>
-      <c r="F107" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="G107" t="s">
-        <v>222</v>
+        <v>19</v>
       </c>
       <c r="H107">
-        <v>1</v>
-      </c>
-      <c r="I107" t="s">
-        <v>364</v>
-      </c>
-      <c r="J107">
-        <v>405754</v>
+        <v>69</v>
       </c>
       <c r="K107" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="L107" t="s">
         <v>365</v>
       </c>
       <c r="M107">
-        <v>11102722</v>
+        <v>28650367</v>
       </c>
       <c r="N107">
-        <v>11105864</v>
+        <v>28660735</v>
       </c>
     </row>
     <row r="108" spans="1:14" x14ac:dyDescent="0.2">
@@ -6631,13 +6634,19 @@
         <v>17</v>
       </c>
       <c r="D108" t="s">
-        <v>366</v>
-      </c>
-      <c r="G108" t="s">
-        <v>19</v>
+        <v>367</v>
+      </c>
+      <c r="E108" t="s">
+        <v>368</v>
       </c>
       <c r="H108">
-        <v>69</v>
+        <v>12</v>
+      </c>
+      <c r="I108" t="s">
+        <v>369</v>
+      </c>
+      <c r="J108">
+        <v>105375011</v>
       </c>
       <c r="K108" t="s">
         <v>20</v>
@@ -6646,10 +6655,10 @@
         <v>365</v>
       </c>
       <c r="M108">
-        <v>28650367</v>
+        <v>29843501</v>
       </c>
       <c r="N108">
-        <v>28660735</v>
+        <v>29844033</v>
       </c>
     </row>
     <row r="109" spans="1:14" x14ac:dyDescent="0.2">
@@ -6663,31 +6672,25 @@
         <v>17</v>
       </c>
       <c r="D109" t="s">
-        <v>367</v>
-      </c>
-      <c r="E109" t="s">
-        <v>368</v>
+        <v>370</v>
+      </c>
+      <c r="G109" t="s">
+        <v>19</v>
       </c>
       <c r="H109">
-        <v>12</v>
-      </c>
-      <c r="I109" t="s">
-        <v>369</v>
-      </c>
-      <c r="J109">
-        <v>105375011</v>
+        <v>35587</v>
       </c>
       <c r="K109" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="L109" t="s">
         <v>365</v>
       </c>
       <c r="M109">
-        <v>29843501</v>
+        <v>42861409</v>
       </c>
       <c r="N109">
-        <v>29844033</v>
+        <v>42871367</v>
       </c>
     </row>
     <row r="110" spans="1:14" x14ac:dyDescent="0.2">
@@ -6701,25 +6704,25 @@
         <v>17</v>
       </c>
       <c r="D110" t="s">
-        <v>370</v>
+        <v>267</v>
       </c>
       <c r="G110" t="s">
         <v>19</v>
       </c>
       <c r="H110">
-        <v>35587</v>
+        <v>23</v>
       </c>
       <c r="K110" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="L110" t="s">
         <v>365</v>
       </c>
       <c r="M110">
-        <v>42861409</v>
+        <v>57623896</v>
       </c>
       <c r="N110">
-        <v>42871367</v>
+        <v>57628704</v>
       </c>
     </row>
     <row r="111" spans="1:14" x14ac:dyDescent="0.2">
@@ -6733,25 +6736,37 @@
         <v>17</v>
       </c>
       <c r="D111" t="s">
-        <v>267</v>
+        <v>371</v>
+      </c>
+      <c r="E111" t="s">
+        <v>372</v>
+      </c>
+      <c r="F111" t="s">
+        <v>373</v>
       </c>
       <c r="G111" t="s">
-        <v>19</v>
+        <v>76</v>
       </c>
       <c r="H111">
-        <v>23</v>
+        <v>3</v>
+      </c>
+      <c r="I111" t="s">
+        <v>374</v>
+      </c>
+      <c r="J111">
+        <v>100289683</v>
       </c>
       <c r="K111" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="L111" t="s">
         <v>365</v>
       </c>
       <c r="M111">
-        <v>57623896</v>
+        <v>68591209</v>
       </c>
       <c r="N111">
-        <v>57628704</v>
+        <v>68599037</v>
       </c>
     </row>
     <row r="112" spans="1:14" x14ac:dyDescent="0.2">
@@ -6765,37 +6780,34 @@
         <v>17</v>
       </c>
       <c r="D112" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="E112" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="F112" t="s">
-        <v>373</v>
-      </c>
-      <c r="G112" t="s">
-        <v>76</v>
+        <v>377</v>
       </c>
       <c r="H112">
-        <v>3</v>
+        <v>1610</v>
       </c>
       <c r="I112" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="J112">
-        <v>100289683</v>
+        <v>101928353</v>
       </c>
       <c r="K112" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="L112" t="s">
         <v>365</v>
       </c>
       <c r="M112">
-        <v>68591209</v>
+        <v>71103905</v>
       </c>
       <c r="N112">
-        <v>68599037</v>
+        <v>71109120</v>
       </c>
     </row>
     <row r="113" spans="1:15" x14ac:dyDescent="0.2">
@@ -6809,34 +6821,34 @@
         <v>17</v>
       </c>
       <c r="D113" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="E113" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="F113" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="H113">
-        <v>1610</v>
+        <v>109</v>
       </c>
       <c r="I113" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="J113">
-        <v>101928353</v>
+        <v>110006328</v>
       </c>
       <c r="K113" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="L113" t="s">
         <v>365</v>
       </c>
       <c r="M113">
-        <v>71103905</v>
+        <v>78426662</v>
       </c>
       <c r="N113">
-        <v>71109120</v>
+        <v>78436083</v>
       </c>
     </row>
     <row r="114" spans="1:15" x14ac:dyDescent="0.2">
@@ -6850,22 +6862,25 @@
         <v>17</v>
       </c>
       <c r="D114" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="E114" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="F114" t="s">
-        <v>381</v>
+        <v>385</v>
+      </c>
+      <c r="G114" t="s">
+        <v>19</v>
       </c>
       <c r="H114">
-        <v>109</v>
+        <v>19</v>
       </c>
       <c r="I114" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="J114">
-        <v>110006328</v>
+        <v>105376906</v>
       </c>
       <c r="K114" t="s">
         <v>43</v>
@@ -6874,7 +6889,7 @@
         <v>365</v>
       </c>
       <c r="M114">
-        <v>78426662</v>
+        <v>78427019</v>
       </c>
       <c r="N114">
         <v>78436083</v>
@@ -6891,25 +6906,19 @@
         <v>17</v>
       </c>
       <c r="D115" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="E115" t="s">
-        <v>384</v>
-      </c>
-      <c r="F115" t="s">
-        <v>385</v>
-      </c>
-      <c r="G115" t="s">
-        <v>19</v>
+        <v>388</v>
       </c>
       <c r="H115">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="I115" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="J115">
-        <v>105376906</v>
+        <v>100616102</v>
       </c>
       <c r="K115" t="s">
         <v>43</v>
@@ -6918,10 +6927,10 @@
         <v>365</v>
       </c>
       <c r="M115">
-        <v>78427019</v>
+        <v>78430450</v>
       </c>
       <c r="N115">
-        <v>78436083</v>
+        <v>78432161</v>
       </c>
     </row>
     <row r="116" spans="1:15" x14ac:dyDescent="0.2">
@@ -6935,31 +6944,34 @@
         <v>17</v>
       </c>
       <c r="D116" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="E116" t="s">
-        <v>388</v>
+        <v>391</v>
+      </c>
+      <c r="G116" t="s">
+        <v>175</v>
       </c>
       <c r="H116">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I116" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="J116">
-        <v>100616102</v>
+        <v>100616105</v>
       </c>
       <c r="K116" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="L116" t="s">
         <v>365</v>
       </c>
       <c r="M116">
-        <v>78430450</v>
+        <v>89372192</v>
       </c>
       <c r="N116">
-        <v>78432161</v>
+        <v>89380624</v>
       </c>
     </row>
     <row r="117" spans="1:15" x14ac:dyDescent="0.2">
@@ -6973,22 +6985,22 @@
         <v>17</v>
       </c>
       <c r="D117" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="E117" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="G117" t="s">
-        <v>175</v>
+        <v>24</v>
       </c>
       <c r="H117">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="I117" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="J117">
-        <v>100616105</v>
+        <v>106144567</v>
       </c>
       <c r="K117" t="s">
         <v>20</v>
@@ -6997,10 +7009,10 @@
         <v>365</v>
       </c>
       <c r="M117">
-        <v>89372192</v>
+        <v>106676011</v>
       </c>
       <c r="N117">
-        <v>89380624</v>
+        <v>106683689</v>
       </c>
     </row>
     <row r="118" spans="1:15" x14ac:dyDescent="0.2">
@@ -7014,16 +7026,19 @@
         <v>17</v>
       </c>
       <c r="D118" t="s">
-        <v>390</v>
+        <v>397</v>
       </c>
       <c r="E118" t="s">
-        <v>391</v>
-      </c>
-      <c r="F118" t="s">
-        <v>393</v>
-      </c>
-      <c r="G118" t="s">
-        <v>175</v>
+        <v>398</v>
+      </c>
+      <c r="H118">
+        <v>6</v>
+      </c>
+      <c r="I118" t="s">
+        <v>399</v>
+      </c>
+      <c r="J118">
+        <v>111188146</v>
       </c>
       <c r="K118" t="s">
         <v>20</v>
@@ -7032,10 +7047,10 @@
         <v>365</v>
       </c>
       <c r="M118">
-        <v>89372203</v>
+        <v>111242742</v>
       </c>
       <c r="N118">
-        <v>89375974</v>
+        <v>111243387</v>
       </c>
     </row>
     <row r="119" spans="1:15" x14ac:dyDescent="0.2">
@@ -7049,22 +7064,22 @@
         <v>17</v>
       </c>
       <c r="D119" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="E119" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
       <c r="G119" t="s">
         <v>24</v>
       </c>
       <c r="H119">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I119" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="J119">
-        <v>106144567</v>
+        <v>106144562</v>
       </c>
       <c r="K119" t="s">
         <v>20</v>
@@ -7073,10 +7088,10 @@
         <v>365</v>
       </c>
       <c r="M119">
-        <v>106676011</v>
+        <v>143400937</v>
       </c>
       <c r="N119">
-        <v>106683689</v>
+        <v>143408849</v>
       </c>
     </row>
     <row r="120" spans="1:15" x14ac:dyDescent="0.2">
@@ -7090,16 +7105,22 @@
         <v>17</v>
       </c>
       <c r="D120" t="s">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="E120" t="s">
-        <v>398</v>
+        <v>404</v>
+      </c>
+      <c r="G120" t="s">
+        <v>24</v>
+      </c>
+      <c r="H120">
+        <v>19</v>
       </c>
       <c r="I120" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="J120">
-        <v>111188146</v>
+        <v>106144571</v>
       </c>
       <c r="K120" t="s">
         <v>20</v>
@@ -7108,10 +7129,10 @@
         <v>365</v>
       </c>
       <c r="M120">
-        <v>111242742</v>
+        <v>167304567</v>
       </c>
       <c r="N120">
-        <v>111243387</v>
+        <v>167311741</v>
       </c>
     </row>
     <row r="121" spans="1:15" x14ac:dyDescent="0.2">
@@ -7125,34 +7146,40 @@
         <v>17</v>
       </c>
       <c r="D121" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="E121" t="s">
-        <v>401</v>
+        <v>407</v>
+      </c>
+      <c r="F121" t="s">
+        <v>408</v>
       </c>
       <c r="G121" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="H121">
-        <v>18</v>
+        <v>108</v>
       </c>
       <c r="I121" t="s">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="J121">
-        <v>106144562</v>
+        <v>64006</v>
       </c>
       <c r="K121" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="L121" t="s">
-        <v>365</v>
+        <v>410</v>
       </c>
       <c r="M121">
-        <v>143400937</v>
+        <v>4620811</v>
       </c>
       <c r="N121">
-        <v>143408849</v>
+        <v>4631528</v>
+      </c>
+      <c r="O121" t="s">
+        <v>411</v>
       </c>
     </row>
     <row r="122" spans="1:15" x14ac:dyDescent="0.2">
@@ -7166,34 +7193,40 @@
         <v>17</v>
       </c>
       <c r="D122" t="s">
-        <v>403</v>
+        <v>412</v>
       </c>
       <c r="E122" t="s">
-        <v>404</v>
+        <v>407</v>
+      </c>
+      <c r="F122" t="s">
+        <v>408</v>
       </c>
       <c r="G122" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="H122">
-        <v>19</v>
+        <v>108</v>
       </c>
       <c r="I122" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="J122">
-        <v>106144571</v>
+        <v>64006</v>
       </c>
       <c r="K122" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="L122" t="s">
-        <v>365</v>
+        <v>410</v>
       </c>
       <c r="M122">
-        <v>167304567</v>
+        <v>4630561</v>
       </c>
       <c r="N122">
-        <v>167311741</v>
+        <v>4640031</v>
+      </c>
+      <c r="O122" t="s">
+        <v>413</v>
       </c>
     </row>
     <row r="123" spans="1:15" x14ac:dyDescent="0.2">
@@ -7207,25 +7240,25 @@
         <v>17</v>
       </c>
       <c r="D123" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
       <c r="E123" t="s">
-        <v>407</v>
+        <v>415</v>
       </c>
       <c r="F123" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="G123" t="s">
-        <v>19</v>
+        <v>417</v>
       </c>
       <c r="H123">
-        <v>108</v>
+        <v>21</v>
       </c>
       <c r="I123" t="s">
-        <v>409</v>
+        <v>418</v>
       </c>
       <c r="J123">
-        <v>64006</v>
+        <v>100616104</v>
       </c>
       <c r="K123" t="s">
         <v>43</v>
@@ -7234,13 +7267,10 @@
         <v>410</v>
       </c>
       <c r="M123">
-        <v>4620811</v>
+        <v>12628860</v>
       </c>
       <c r="N123">
-        <v>4631528</v>
-      </c>
-      <c r="O123" t="s">
-        <v>411</v>
+        <v>12633987</v>
       </c>
     </row>
     <row r="124" spans="1:15" x14ac:dyDescent="0.2">
@@ -7254,40 +7284,31 @@
         <v>17</v>
       </c>
       <c r="D124" t="s">
-        <v>412</v>
+        <v>419</v>
       </c>
       <c r="E124" t="s">
-        <v>407</v>
-      </c>
-      <c r="F124" t="s">
-        <v>408</v>
-      </c>
-      <c r="G124" t="s">
-        <v>19</v>
+        <v>420</v>
       </c>
       <c r="H124">
-        <v>108</v>
+        <v>7</v>
       </c>
       <c r="I124" t="s">
-        <v>409</v>
+        <v>421</v>
       </c>
       <c r="J124">
-        <v>64006</v>
+        <v>111188142</v>
       </c>
       <c r="K124" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="L124" t="s">
         <v>410</v>
       </c>
       <c r="M124">
-        <v>4630561</v>
+        <v>35950680</v>
       </c>
       <c r="N124">
-        <v>4640031</v>
-      </c>
-      <c r="O124" t="s">
-        <v>413</v>
+        <v>35951312</v>
       </c>
     </row>
     <row r="125" spans="1:15" x14ac:dyDescent="0.2">
@@ -7301,22 +7322,25 @@
         <v>17</v>
       </c>
       <c r="D125" t="s">
-        <v>414</v>
+        <v>422</v>
       </c>
       <c r="E125" t="s">
-        <v>415</v>
+        <v>423</v>
       </c>
       <c r="F125" t="s">
-        <v>416</v>
+        <v>424</v>
       </c>
       <c r="G125" t="s">
-        <v>417</v>
+        <v>425</v>
+      </c>
+      <c r="H125">
+        <v>1</v>
       </c>
       <c r="I125" t="s">
-        <v>418</v>
+        <v>426</v>
       </c>
       <c r="J125">
-        <v>100616104</v>
+        <v>2086</v>
       </c>
       <c r="K125" t="s">
         <v>43</v>
@@ -7325,10 +7349,10 @@
         <v>410</v>
       </c>
       <c r="M125">
-        <v>12628860</v>
+        <v>64450734</v>
       </c>
       <c r="N125">
-        <v>12633987</v>
+        <v>64467065</v>
       </c>
     </row>
     <row r="126" spans="1:15" x14ac:dyDescent="0.2">
@@ -7342,16 +7366,25 @@
         <v>17</v>
       </c>
       <c r="D126" t="s">
-        <v>419</v>
+        <v>427</v>
       </c>
       <c r="E126" t="s">
-        <v>420</v>
+        <v>428</v>
+      </c>
+      <c r="F126" t="s">
+        <v>429</v>
+      </c>
+      <c r="G126" t="s">
+        <v>24</v>
+      </c>
+      <c r="H126">
+        <v>1</v>
       </c>
       <c r="I126" t="s">
-        <v>421</v>
+        <v>430</v>
       </c>
       <c r="J126">
-        <v>111188142</v>
+        <v>30816</v>
       </c>
       <c r="K126" t="s">
         <v>20</v>
@@ -7360,10 +7393,10 @@
         <v>410</v>
       </c>
       <c r="M126">
-        <v>35950680</v>
+        <v>92097312</v>
       </c>
       <c r="N126">
-        <v>35951312</v>
+        <v>92107506</v>
       </c>
     </row>
     <row r="127" spans="1:15" x14ac:dyDescent="0.2">
@@ -7377,22 +7410,25 @@
         <v>17</v>
       </c>
       <c r="D127" t="s">
-        <v>422</v>
+        <v>431</v>
       </c>
       <c r="E127" t="s">
-        <v>423</v>
+        <v>432</v>
       </c>
       <c r="F127" t="s">
-        <v>424</v>
+        <v>433</v>
       </c>
       <c r="G127" t="s">
-        <v>425</v>
+        <v>19</v>
+      </c>
+      <c r="H127">
+        <v>14</v>
       </c>
       <c r="I127" t="s">
-        <v>426</v>
+        <v>434</v>
       </c>
       <c r="J127">
-        <v>2086</v>
+        <v>100862687</v>
       </c>
       <c r="K127" t="s">
         <v>43</v>
@@ -7401,10 +7437,10 @@
         <v>410</v>
       </c>
       <c r="M127">
-        <v>64450734</v>
+        <v>104388369</v>
       </c>
       <c r="N127">
-        <v>64467065</v>
+        <v>104393266</v>
       </c>
     </row>
     <row r="128" spans="1:15" x14ac:dyDescent="0.2">
@@ -7418,25 +7454,22 @@
         <v>17</v>
       </c>
       <c r="D128" t="s">
-        <v>427</v>
+        <v>435</v>
       </c>
       <c r="E128" t="s">
-        <v>428</v>
+        <v>436</v>
       </c>
       <c r="F128" t="s">
-        <v>429</v>
-      </c>
-      <c r="G128" t="s">
-        <v>24</v>
+        <v>437</v>
       </c>
       <c r="H128">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I128" t="s">
-        <v>430</v>
+        <v>438</v>
       </c>
       <c r="J128">
-        <v>30816</v>
+        <v>57612</v>
       </c>
       <c r="K128" t="s">
         <v>20</v>
@@ -7445,10 +7478,10 @@
         <v>410</v>
       </c>
       <c r="M128">
-        <v>92097312</v>
+        <v>134862422</v>
       </c>
       <c r="N128">
-        <v>92107506</v>
+        <v>134866711</v>
       </c>
     </row>
     <row r="129" spans="1:14" x14ac:dyDescent="0.2">
@@ -7462,25 +7495,25 @@
         <v>17</v>
       </c>
       <c r="D129" t="s">
-        <v>431</v>
+        <v>439</v>
       </c>
       <c r="E129" t="s">
-        <v>432</v>
+        <v>440</v>
       </c>
       <c r="F129" t="s">
-        <v>433</v>
+        <v>441</v>
       </c>
       <c r="G129" t="s">
         <v>19</v>
       </c>
       <c r="H129">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I129" t="s">
-        <v>434</v>
+        <v>442</v>
       </c>
       <c r="J129">
-        <v>100862687</v>
+        <v>100616443</v>
       </c>
       <c r="K129" t="s">
         <v>43</v>
@@ -7489,10 +7522,10 @@
         <v>410</v>
       </c>
       <c r="M129">
-        <v>104388369</v>
+        <v>141450926</v>
       </c>
       <c r="N129">
-        <v>104393266</v>
+        <v>141455903</v>
       </c>
     </row>
     <row r="130" spans="1:14" x14ac:dyDescent="0.2">
@@ -7506,31 +7539,37 @@
         <v>17</v>
       </c>
       <c r="D130" t="s">
-        <v>435</v>
+        <v>443</v>
       </c>
       <c r="E130" t="s">
-        <v>436</v>
+        <v>444</v>
       </c>
       <c r="F130" t="s">
-        <v>437</v>
+        <v>445</v>
+      </c>
+      <c r="G130" t="s">
+        <v>446</v>
+      </c>
+      <c r="H130">
+        <v>1</v>
       </c>
       <c r="I130" t="s">
-        <v>438</v>
+        <v>447</v>
       </c>
       <c r="J130">
-        <v>57612</v>
+        <v>346547</v>
       </c>
       <c r="K130" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="L130" t="s">
         <v>410</v>
       </c>
       <c r="M130">
-        <v>134862422</v>
+        <v>153108319</v>
       </c>
       <c r="N130">
-        <v>134866711</v>
+        <v>153111048</v>
       </c>
     </row>
     <row r="131" spans="1:14" x14ac:dyDescent="0.2">
@@ -7544,37 +7583,37 @@
         <v>17</v>
       </c>
       <c r="D131" t="s">
-        <v>439</v>
+        <v>448</v>
       </c>
       <c r="E131" t="s">
-        <v>440</v>
+        <v>449</v>
       </c>
       <c r="F131" t="s">
-        <v>441</v>
+        <v>450</v>
       </c>
       <c r="G131" t="s">
         <v>19</v>
       </c>
       <c r="H131">
-        <v>15</v>
+        <v>115</v>
       </c>
       <c r="I131" t="s">
-        <v>442</v>
+        <v>451</v>
       </c>
       <c r="J131">
-        <v>100616443</v>
+        <v>619465</v>
       </c>
       <c r="K131" t="s">
         <v>43</v>
       </c>
       <c r="L131" t="s">
-        <v>410</v>
+        <v>452</v>
       </c>
       <c r="M131">
-        <v>141450926</v>
+        <v>7355397</v>
       </c>
       <c r="N131">
-        <v>141455903</v>
+        <v>7364859</v>
       </c>
     </row>
     <row r="132" spans="1:14" x14ac:dyDescent="0.2">
@@ -7588,37 +7627,25 @@
         <v>17</v>
       </c>
       <c r="D132" t="s">
-        <v>443</v>
-      </c>
-      <c r="E132" t="s">
-        <v>444</v>
-      </c>
-      <c r="F132" t="s">
-        <v>445</v>
+        <v>92</v>
       </c>
       <c r="G132" t="s">
-        <v>446</v>
+        <v>19</v>
       </c>
       <c r="H132">
-        <v>1</v>
-      </c>
-      <c r="I132" t="s">
-        <v>447</v>
-      </c>
-      <c r="J132">
-        <v>346547</v>
+        <v>27</v>
       </c>
       <c r="K132" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="L132" t="s">
-        <v>410</v>
+        <v>452</v>
       </c>
       <c r="M132">
-        <v>153108319</v>
+        <v>8054700</v>
       </c>
       <c r="N132">
-        <v>153111048</v>
+        <v>8055725</v>
       </c>
     </row>
     <row r="133" spans="1:14" x14ac:dyDescent="0.2">
@@ -7632,25 +7659,22 @@
         <v>17</v>
       </c>
       <c r="D133" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="E133" t="s">
-        <v>449</v>
-      </c>
-      <c r="F133" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="G133" t="s">
         <v>19</v>
       </c>
       <c r="H133">
-        <v>115</v>
+        <v>26</v>
       </c>
       <c r="I133" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="J133">
-        <v>619465</v>
+        <v>103539957</v>
       </c>
       <c r="K133" t="s">
         <v>43</v>
@@ -7659,10 +7683,10 @@
         <v>452</v>
       </c>
       <c r="M133">
-        <v>7355397</v>
+        <v>12081113</v>
       </c>
       <c r="N133">
-        <v>7364859</v>
+        <v>12081622</v>
       </c>
     </row>
     <row r="134" spans="1:14" x14ac:dyDescent="0.2">
@@ -7676,25 +7700,34 @@
         <v>17</v>
       </c>
       <c r="D134" t="s">
-        <v>92</v>
+        <v>458</v>
+      </c>
+      <c r="E134" t="s">
+        <v>459</v>
       </c>
       <c r="G134" t="s">
-        <v>19</v>
+        <v>175</v>
       </c>
       <c r="H134">
-        <v>27</v>
+        <v>3</v>
+      </c>
+      <c r="I134" t="s">
+        <v>460</v>
+      </c>
+      <c r="J134">
+        <v>100862700</v>
       </c>
       <c r="K134" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="L134" t="s">
         <v>452</v>
       </c>
       <c r="M134">
-        <v>8054700</v>
+        <v>12343258</v>
       </c>
       <c r="N134">
-        <v>8055725</v>
+        <v>12350376</v>
       </c>
     </row>
     <row r="135" spans="1:14" x14ac:dyDescent="0.2">
@@ -7708,22 +7741,13 @@
         <v>17</v>
       </c>
       <c r="D135" t="s">
-        <v>453</v>
-      </c>
-      <c r="E135" t="s">
-        <v>454</v>
+        <v>461</v>
       </c>
       <c r="G135" t="s">
         <v>19</v>
       </c>
       <c r="H135">
-        <v>26</v>
-      </c>
-      <c r="I135" t="s">
-        <v>455</v>
-      </c>
-      <c r="J135">
-        <v>103539957</v>
+        <v>70</v>
       </c>
       <c r="K135" t="s">
         <v>43</v>
@@ -7732,10 +7756,10 @@
         <v>452</v>
       </c>
       <c r="M135">
-        <v>12081113</v>
+        <v>47175650</v>
       </c>
       <c r="N135">
-        <v>12081622</v>
+        <v>47183661</v>
       </c>
     </row>
     <row r="136" spans="1:14" x14ac:dyDescent="0.2">
@@ -7749,13 +7773,19 @@
         <v>17</v>
       </c>
       <c r="D136" t="s">
-        <v>456</v>
-      </c>
-      <c r="F136" t="s">
-        <v>457</v>
-      </c>
-      <c r="G136" t="s">
-        <v>19</v>
+        <v>462</v>
+      </c>
+      <c r="E136" t="s">
+        <v>463</v>
+      </c>
+      <c r="H136">
+        <v>8</v>
+      </c>
+      <c r="I136" t="s">
+        <v>464</v>
+      </c>
+      <c r="J136">
+        <v>111188145</v>
       </c>
       <c r="K136" t="s">
         <v>20</v>
@@ -7764,10 +7794,10 @@
         <v>452</v>
       </c>
       <c r="M136">
-        <v>12316492</v>
+        <v>54988029</v>
       </c>
       <c r="N136">
-        <v>12326007</v>
+        <v>54988656</v>
       </c>
     </row>
     <row r="137" spans="1:14" x14ac:dyDescent="0.2">
@@ -7781,34 +7811,34 @@
         <v>17</v>
       </c>
       <c r="D137" t="s">
-        <v>458</v>
+        <v>465</v>
       </c>
       <c r="E137" t="s">
-        <v>459</v>
+        <v>466</v>
       </c>
       <c r="G137" t="s">
-        <v>175</v>
+        <v>24</v>
       </c>
       <c r="H137">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="I137" t="s">
-        <v>460</v>
+        <v>467</v>
       </c>
       <c r="J137">
-        <v>100862700</v>
+        <v>106144604</v>
       </c>
       <c r="K137" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="L137" t="s">
         <v>452</v>
       </c>
       <c r="M137">
-        <v>12343258</v>
+        <v>74734099</v>
       </c>
       <c r="N137">
-        <v>12350376</v>
+        <v>74734838</v>
       </c>
     </row>
     <row r="138" spans="1:14" x14ac:dyDescent="0.2">
@@ -7822,25 +7852,34 @@
         <v>17</v>
       </c>
       <c r="D138" t="s">
-        <v>461</v>
+        <v>468</v>
+      </c>
+      <c r="E138" t="s">
+        <v>469</v>
       </c>
       <c r="G138" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="H138">
-        <v>70</v>
+        <v>21</v>
+      </c>
+      <c r="I138" t="s">
+        <v>470</v>
+      </c>
+      <c r="J138">
+        <v>106144587</v>
       </c>
       <c r="K138" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="L138" t="s">
         <v>452</v>
       </c>
       <c r="M138">
-        <v>47175650</v>
+        <v>81651950</v>
       </c>
       <c r="N138">
-        <v>47183661</v>
+        <v>81655427</v>
       </c>
     </row>
     <row r="139" spans="1:14" x14ac:dyDescent="0.2">
@@ -7854,31 +7893,25 @@
         <v>17</v>
       </c>
       <c r="D139" t="s">
-        <v>462</v>
-      </c>
-      <c r="E139" t="s">
-        <v>463</v>
+        <v>209</v>
+      </c>
+      <c r="G139" t="s">
+        <v>19</v>
       </c>
       <c r="H139">
-        <v>8</v>
-      </c>
-      <c r="I139" t="s">
-        <v>464</v>
-      </c>
-      <c r="J139">
-        <v>111188145</v>
+        <v>29</v>
       </c>
       <c r="K139" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="L139" t="s">
         <v>452</v>
       </c>
       <c r="M139">
-        <v>54988029</v>
+        <v>146246648</v>
       </c>
       <c r="N139">
-        <v>54988656</v>
+        <v>146254211</v>
       </c>
     </row>
     <row r="140" spans="1:14" x14ac:dyDescent="0.2">
@@ -7892,34 +7925,34 @@
         <v>17</v>
       </c>
       <c r="D140" t="s">
-        <v>465</v>
+        <v>471</v>
       </c>
       <c r="E140" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
       <c r="G140" t="s">
-        <v>24</v>
+        <v>222</v>
       </c>
       <c r="H140">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="I140" t="s">
-        <v>467</v>
+        <v>473</v>
       </c>
       <c r="J140">
-        <v>106144604</v>
+        <v>100533725</v>
       </c>
       <c r="K140" t="s">
         <v>20</v>
       </c>
       <c r="L140" t="s">
-        <v>452</v>
+        <v>474</v>
       </c>
       <c r="M140">
-        <v>74734099</v>
+        <v>21930389</v>
       </c>
       <c r="N140">
-        <v>74734838</v>
+        <v>21932738</v>
       </c>
     </row>
     <row r="141" spans="1:14" x14ac:dyDescent="0.2">
@@ -7933,34 +7966,34 @@
         <v>17</v>
       </c>
       <c r="D141" t="s">
-        <v>468</v>
+        <v>475</v>
       </c>
       <c r="E141" t="s">
-        <v>469</v>
+        <v>476</v>
       </c>
       <c r="G141" t="s">
         <v>24</v>
       </c>
       <c r="H141">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I141" t="s">
-        <v>470</v>
+        <v>477</v>
       </c>
       <c r="J141">
-        <v>106144587</v>
+        <v>106144563</v>
       </c>
       <c r="K141" t="s">
         <v>20</v>
       </c>
       <c r="L141" t="s">
-        <v>452</v>
+        <v>474</v>
       </c>
       <c r="M141">
-        <v>81651950</v>
+        <v>35640301</v>
       </c>
       <c r="N141">
-        <v>81655427</v>
+        <v>35642824</v>
       </c>
     </row>
     <row r="142" spans="1:14" x14ac:dyDescent="0.2">
@@ -7974,25 +8007,34 @@
         <v>17</v>
       </c>
       <c r="D142" t="s">
-        <v>209</v>
+        <v>478</v>
+      </c>
+      <c r="E142" t="s">
+        <v>479</v>
       </c>
       <c r="G142" t="s">
-        <v>19</v>
+        <v>480</v>
       </c>
       <c r="H142">
-        <v>29</v>
+        <v>1</v>
+      </c>
+      <c r="I142" t="s">
+        <v>481</v>
+      </c>
+      <c r="J142">
+        <v>100131068</v>
       </c>
       <c r="K142" t="s">
         <v>43</v>
       </c>
       <c r="L142" t="s">
-        <v>452</v>
+        <v>474</v>
       </c>
       <c r="M142">
-        <v>146246648</v>
+        <v>90652790</v>
       </c>
       <c r="N142">
-        <v>146254211</v>
+        <v>90659200</v>
       </c>
     </row>
     <row r="143" spans="1:14" x14ac:dyDescent="0.2">
@@ -8006,22 +8048,13 @@
         <v>17</v>
       </c>
       <c r="D143" t="s">
-        <v>471</v>
-      </c>
-      <c r="E143" t="s">
-        <v>472</v>
+        <v>355</v>
       </c>
       <c r="G143" t="s">
-        <v>222</v>
+        <v>19</v>
       </c>
       <c r="H143">
-        <v>3</v>
-      </c>
-      <c r="I143" t="s">
-        <v>473</v>
-      </c>
-      <c r="J143">
-        <v>100533725</v>
+        <v>31</v>
       </c>
       <c r="K143" t="s">
         <v>20</v>
@@ -8030,10 +8063,10 @@
         <v>474</v>
       </c>
       <c r="M143">
-        <v>21930389</v>
+        <v>131612515</v>
       </c>
       <c r="N143">
-        <v>21932738</v>
+        <v>131619736</v>
       </c>
     </row>
     <row r="144" spans="1:14" x14ac:dyDescent="0.2">
@@ -8047,34 +8080,25 @@
         <v>17</v>
       </c>
       <c r="D144" t="s">
-        <v>475</v>
-      </c>
-      <c r="E144" t="s">
-        <v>476</v>
+        <v>259</v>
       </c>
       <c r="G144" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="H144">
-        <v>22</v>
-      </c>
-      <c r="I144" t="s">
-        <v>477</v>
-      </c>
-      <c r="J144">
-        <v>106144563</v>
+        <v>30</v>
       </c>
       <c r="K144" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="L144" t="s">
         <v>474</v>
       </c>
       <c r="M144">
-        <v>35640301</v>
+        <v>139674766</v>
       </c>
       <c r="N144">
-        <v>35642824</v>
+        <v>139684228</v>
       </c>
     </row>
     <row r="145" spans="1:14" x14ac:dyDescent="0.2">
@@ -8088,34 +8112,25 @@
         <v>17</v>
       </c>
       <c r="D145" t="s">
-        <v>478</v>
-      </c>
-      <c r="E145" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="G145" t="s">
-        <v>480</v>
+        <v>19</v>
       </c>
       <c r="H145">
-        <v>1</v>
-      </c>
-      <c r="I145" t="s">
-        <v>481</v>
-      </c>
-      <c r="J145">
-        <v>100131068</v>
+        <v>105</v>
       </c>
       <c r="K145" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="L145" t="s">
-        <v>474</v>
+        <v>483</v>
       </c>
       <c r="M145">
-        <v>90652790</v>
+        <v>175210</v>
       </c>
       <c r="N145">
-        <v>90659200</v>
+        <v>176178</v>
       </c>
     </row>
     <row r="146" spans="1:14" x14ac:dyDescent="0.2">
@@ -8129,25 +8144,37 @@
         <v>17</v>
       </c>
       <c r="D146" t="s">
-        <v>355</v>
+        <v>484</v>
+      </c>
+      <c r="E146" t="s">
+        <v>485</v>
+      </c>
+      <c r="F146" t="s">
+        <v>486</v>
       </c>
       <c r="G146" t="s">
-        <v>19</v>
+        <v>76</v>
       </c>
       <c r="H146">
-        <v>31</v>
+        <v>2</v>
+      </c>
+      <c r="I146" t="s">
+        <v>487</v>
+      </c>
+      <c r="J146">
+        <v>100616461</v>
       </c>
       <c r="K146" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="L146" t="s">
-        <v>474</v>
+        <v>488</v>
       </c>
       <c r="M146">
-        <v>131612515</v>
+        <v>4462210</v>
       </c>
       <c r="N146">
-        <v>131619736</v>
+        <v>4463549</v>
       </c>
     </row>
     <row r="147" spans="1:14" x14ac:dyDescent="0.2">
@@ -8161,25 +8188,37 @@
         <v>17</v>
       </c>
       <c r="D147" t="s">
-        <v>259</v>
+        <v>489</v>
+      </c>
+      <c r="E147" t="s">
+        <v>490</v>
+      </c>
+      <c r="F147" t="s">
+        <v>491</v>
       </c>
       <c r="G147" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="H147">
-        <v>30</v>
+        <v>2</v>
+      </c>
+      <c r="I147" t="s">
+        <v>492</v>
+      </c>
+      <c r="J147">
+        <v>100379323</v>
       </c>
       <c r="K147" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="L147" t="s">
-        <v>474</v>
+        <v>488</v>
       </c>
       <c r="M147">
-        <v>139674766</v>
+        <v>106295360</v>
       </c>
       <c r="N147">
-        <v>139684228</v>
+        <v>106298101</v>
       </c>
     </row>
     <row r="148" spans="1:14" x14ac:dyDescent="0.2">
@@ -8193,25 +8232,25 @@
         <v>17</v>
       </c>
       <c r="D148" t="s">
-        <v>482</v>
+        <v>493</v>
       </c>
       <c r="G148" t="s">
         <v>19</v>
       </c>
       <c r="H148">
-        <v>105</v>
+        <v>63</v>
       </c>
       <c r="K148" t="s">
         <v>20</v>
       </c>
       <c r="L148" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="M148">
-        <v>175210</v>
+        <v>153817163</v>
       </c>
       <c r="N148">
-        <v>176178</v>
+        <v>153819562</v>
       </c>
     </row>
     <row r="149" spans="1:14" x14ac:dyDescent="0.2">
@@ -8225,157 +8264,158 @@
         <v>17</v>
       </c>
       <c r="D149" t="s">
-        <v>484</v>
+        <v>494</v>
       </c>
       <c r="E149" t="s">
-        <v>485</v>
-      </c>
-      <c r="F149" t="s">
-        <v>486</v>
+        <v>495</v>
       </c>
       <c r="G149" t="s">
         <v>76</v>
       </c>
       <c r="H149">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I149" t="s">
-        <v>487</v>
+        <v>496</v>
       </c>
       <c r="J149">
-        <v>100616461</v>
+        <v>51581</v>
       </c>
       <c r="K149" t="s">
         <v>43</v>
       </c>
       <c r="L149" t="s">
-        <v>488</v>
+        <v>497</v>
       </c>
       <c r="M149">
-        <v>4462210</v>
+        <v>23200175</v>
       </c>
       <c r="N149">
-        <v>4463549</v>
-      </c>
-    </row>
-    <row r="150" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A150" t="s">
-        <v>15</v>
-      </c>
-      <c r="B150" t="s">
-        <v>16</v>
-      </c>
-      <c r="C150" t="s">
-        <v>17</v>
-      </c>
-      <c r="D150" t="s">
-        <v>489</v>
-      </c>
-      <c r="E150" t="s">
-        <v>490</v>
-      </c>
-      <c r="F150" t="s">
-        <v>491</v>
-      </c>
-      <c r="G150" t="s">
-        <v>24</v>
-      </c>
-      <c r="H150">
-        <v>2</v>
-      </c>
-      <c r="I150" t="s">
-        <v>492</v>
-      </c>
-      <c r="J150">
-        <v>100379323</v>
-      </c>
-      <c r="K150" t="s">
-        <v>20</v>
-      </c>
-      <c r="L150" t="s">
-        <v>488</v>
-      </c>
-      <c r="M150">
-        <v>106295360</v>
-      </c>
-      <c r="N150">
-        <v>106298101</v>
-      </c>
-    </row>
-    <row r="151" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A151" t="s">
-        <v>15</v>
-      </c>
-      <c r="B151" t="s">
-        <v>16</v>
-      </c>
-      <c r="C151" t="s">
-        <v>17</v>
-      </c>
-      <c r="D151" t="s">
-        <v>493</v>
-      </c>
-      <c r="G151" t="s">
-        <v>19</v>
-      </c>
-      <c r="H151">
-        <v>63</v>
-      </c>
-      <c r="K151" t="s">
-        <v>20</v>
-      </c>
-      <c r="L151" t="s">
-        <v>488</v>
-      </c>
-      <c r="M151">
-        <v>153817163</v>
-      </c>
-      <c r="N151">
-        <v>153819562</v>
-      </c>
-    </row>
-    <row r="152" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A152" t="s">
-        <v>15</v>
-      </c>
-      <c r="B152" t="s">
-        <v>16</v>
-      </c>
-      <c r="C152" t="s">
-        <v>17</v>
-      </c>
-      <c r="D152" t="s">
-        <v>494</v>
-      </c>
-      <c r="E152" t="s">
-        <v>495</v>
-      </c>
-      <c r="G152" t="s">
-        <v>76</v>
-      </c>
-      <c r="H152">
-        <v>6</v>
-      </c>
-      <c r="I152" t="s">
-        <v>496</v>
-      </c>
-      <c r="J152">
-        <v>51581</v>
-      </c>
-      <c r="K152" t="s">
-        <v>43</v>
-      </c>
-      <c r="L152" t="s">
-        <v>497</v>
-      </c>
-      <c r="M152">
-        <v>23200175</v>
-      </c>
-      <c r="N152">
         <v>23206610</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCBE97ED-1BA3-824F-A08D-55E4843F8392}">
+  <dimension ref="A1:N3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F1" t="s">
+        <v>64</v>
+      </c>
+      <c r="G1" t="s">
+        <v>65</v>
+      </c>
+      <c r="I1" t="s">
+        <v>66</v>
+      </c>
+      <c r="J1">
+        <v>3272</v>
+      </c>
+      <c r="K1" t="s">
+        <v>43</v>
+      </c>
+      <c r="L1" t="s">
+        <v>21</v>
+      </c>
+      <c r="M1">
+        <v>229406344</v>
+      </c>
+      <c r="N1">
+        <v>229408495</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" t="s">
+        <v>390</v>
+      </c>
+      <c r="E2" t="s">
+        <v>391</v>
+      </c>
+      <c r="F2" t="s">
+        <v>393</v>
+      </c>
+      <c r="G2" t="s">
+        <v>175</v>
+      </c>
+      <c r="H2">
+        <v>4</v>
+      </c>
+      <c r="K2" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2" t="s">
+        <v>365</v>
+      </c>
+      <c r="M2">
+        <v>89372203</v>
+      </c>
+      <c r="N2">
+        <v>89375974</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" t="s">
+        <v>456</v>
+      </c>
+      <c r="F3" t="s">
+        <v>457</v>
+      </c>
+      <c r="G3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L3" t="s">
+        <v>452</v>
+      </c>
+      <c r="M3">
+        <v>12316492</v>
+      </c>
+      <c r="N3">
+        <v>12326007</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/tabular/legacy-list.xlsx
+++ b/tabular/legacy-list.xlsx
@@ -8,20 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rob/Projects/erv/ERVdb-HomoSapiens/tabular/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45D58064-2631-CC46-A983-0284907EBB2A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78FF3E04-AFE8-F84C-A0D0-FAAEBD36B583}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1280" yWindow="1000" windowWidth="27140" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="legacy-list" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
+    <sheet name="not found" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1343" uniqueCount="498">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1360" uniqueCount="500">
   <si>
     <t>organism</t>
   </si>
@@ -1515,6 +1515,12 @@
   </si>
   <si>
     <t>chrY</t>
+  </si>
+  <si>
+    <t>HERV-K 105</t>
+  </si>
+  <si>
+    <t>HERV-K 113</t>
   </si>
 </sst>
 </file>
@@ -1657,7 +1663,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1843,6 +1849,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="10">
     <border>
@@ -2004,10 +2016,11 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -2363,7 +2376,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O149"/>
+  <dimension ref="A1:O143"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="4" max="4" width="47.1640625" customWidth="1"/>
@@ -2824,22 +2837,22 @@
         <v>17</v>
       </c>
       <c r="D12" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="E12" t="s">
-        <v>53</v>
-      </c>
-      <c r="F12" t="s">
-        <v>54</v>
+        <v>57</v>
+      </c>
+      <c r="G12" t="s">
+        <v>24</v>
       </c>
       <c r="H12">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I12" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J12">
-        <v>339476</v>
+        <v>106144579</v>
       </c>
       <c r="K12" t="s">
         <v>20</v>
@@ -2848,10 +2861,10 @@
         <v>21</v>
       </c>
       <c r="M12">
-        <v>187610358</v>
+        <v>205835459</v>
       </c>
       <c r="N12">
-        <v>187612992</v>
+        <v>205844935</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.2">
@@ -2865,22 +2878,22 @@
         <v>17</v>
       </c>
       <c r="D13" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="E13" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G13" t="s">
         <v>24</v>
       </c>
       <c r="H13">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I13" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="J13">
-        <v>106144579</v>
+        <v>106144560</v>
       </c>
       <c r="K13" t="s">
         <v>20</v>
@@ -2889,10 +2902,10 @@
         <v>21</v>
       </c>
       <c r="M13">
-        <v>205835459</v>
+        <v>227812214</v>
       </c>
       <c r="N13">
-        <v>205844935</v>
+        <v>227821260</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.2">
@@ -2906,34 +2919,37 @@
         <v>17</v>
       </c>
       <c r="D14" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="E14" t="s">
-        <v>60</v>
+        <v>68</v>
+      </c>
+      <c r="F14" t="s">
+        <v>69</v>
       </c>
       <c r="G14" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="H14">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="I14" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="J14">
-        <v>106144560</v>
+        <v>100616411</v>
       </c>
       <c r="K14" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="L14" t="s">
-        <v>21</v>
+        <v>71</v>
       </c>
       <c r="M14">
-        <v>227812214</v>
+        <v>6866141</v>
       </c>
       <c r="N14">
-        <v>227821260</v>
+        <v>6875603</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.2">
@@ -2947,37 +2963,28 @@
         <v>17</v>
       </c>
       <c r="D15" t="s">
-        <v>67</v>
-      </c>
-      <c r="E15" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="F15" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="G15" t="s">
         <v>19</v>
       </c>
       <c r="H15">
-        <v>16</v>
-      </c>
-      <c r="I15" t="s">
-        <v>70</v>
-      </c>
-      <c r="J15">
-        <v>100616411</v>
+        <v>103</v>
       </c>
       <c r="K15" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="L15" t="s">
         <v>71</v>
       </c>
       <c r="M15">
-        <v>6866141</v>
+        <v>27182399</v>
       </c>
       <c r="N15">
-        <v>6875603</v>
+        <v>27183380</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.2">
@@ -2991,16 +2998,22 @@
         <v>17</v>
       </c>
       <c r="D16" t="s">
-        <v>72</v>
-      </c>
-      <c r="F16" t="s">
-        <v>73</v>
+        <v>74</v>
+      </c>
+      <c r="E16" t="s">
+        <v>75</v>
       </c>
       <c r="G16" t="s">
-        <v>19</v>
+        <v>76</v>
       </c>
       <c r="H16">
-        <v>103</v>
+        <v>5</v>
+      </c>
+      <c r="I16" t="s">
+        <v>77</v>
+      </c>
+      <c r="J16">
+        <v>100862699</v>
       </c>
       <c r="K16" t="s">
         <v>20</v>
@@ -3009,10 +3022,10 @@
         <v>71</v>
       </c>
       <c r="M16">
-        <v>27182399</v>
+        <v>27754712</v>
       </c>
       <c r="N16">
-        <v>27183380</v>
+        <v>27757008</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.2">
@@ -3026,22 +3039,25 @@
         <v>17</v>
       </c>
       <c r="D17" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="E17" t="s">
-        <v>75</v>
+        <v>79</v>
+      </c>
+      <c r="F17" t="s">
+        <v>80</v>
       </c>
       <c r="G17" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="H17">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I17" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="J17">
-        <v>100862699</v>
+        <v>100616200</v>
       </c>
       <c r="K17" t="s">
         <v>20</v>
@@ -3050,10 +3066,10 @@
         <v>71</v>
       </c>
       <c r="M17">
-        <v>27754712</v>
+        <v>38230496</v>
       </c>
       <c r="N17">
-        <v>27757008</v>
+        <v>38230791</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.2">
@@ -3067,37 +3083,37 @@
         <v>17</v>
       </c>
       <c r="D18" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="E18" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="F18" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="G18" t="s">
-        <v>81</v>
+        <v>19</v>
       </c>
       <c r="H18">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="I18" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="J18">
-        <v>100616200</v>
+        <v>100862686</v>
       </c>
       <c r="K18" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="L18" t="s">
         <v>71</v>
       </c>
       <c r="M18">
-        <v>38230496</v>
+        <v>101585489</v>
       </c>
       <c r="N18">
-        <v>38230791</v>
+        <v>101587716</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.2">
@@ -3111,37 +3127,25 @@
         <v>17</v>
       </c>
       <c r="D19" t="s">
-        <v>83</v>
-      </c>
-      <c r="E19" t="s">
-        <v>84</v>
-      </c>
-      <c r="F19" t="s">
-        <v>85</v>
+        <v>39</v>
       </c>
       <c r="G19" t="s">
         <v>19</v>
       </c>
       <c r="H19">
-        <v>17</v>
-      </c>
-      <c r="I19" t="s">
-        <v>86</v>
-      </c>
-      <c r="J19">
-        <v>100862686</v>
+        <v>7</v>
       </c>
       <c r="K19" t="s">
         <v>43</v>
       </c>
       <c r="L19" t="s">
-        <v>71</v>
+        <v>87</v>
       </c>
       <c r="M19">
-        <v>101585489</v>
+        <v>3468656</v>
       </c>
       <c r="N19">
-        <v>101587716</v>
+        <v>3478209</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.2">
@@ -3155,13 +3159,22 @@
         <v>17</v>
       </c>
       <c r="D20" t="s">
-        <v>39</v>
-      </c>
-      <c r="G20" t="s">
-        <v>19</v>
+        <v>88</v>
+      </c>
+      <c r="E20" t="s">
+        <v>89</v>
+      </c>
+      <c r="F20" t="s">
+        <v>90</v>
       </c>
       <c r="H20">
-        <v>7</v>
+        <v>4</v>
+      </c>
+      <c r="I20" t="s">
+        <v>91</v>
+      </c>
+      <c r="J20">
+        <v>100616106</v>
       </c>
       <c r="K20" t="s">
         <v>43</v>
@@ -3170,10 +3183,10 @@
         <v>87</v>
       </c>
       <c r="M20">
-        <v>3468656</v>
+        <v>7924011</v>
       </c>
       <c r="N20">
-        <v>3478209</v>
+        <v>7924334</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.2">
@@ -3187,22 +3200,22 @@
         <v>17</v>
       </c>
       <c r="D21" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="E21" t="s">
-        <v>89</v>
-      </c>
-      <c r="F21" t="s">
-        <v>90</v>
+        <v>93</v>
+      </c>
+      <c r="G21" t="s">
+        <v>19</v>
       </c>
       <c r="H21">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="I21" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="J21">
-        <v>100616106</v>
+        <v>106144566</v>
       </c>
       <c r="K21" t="s">
         <v>43</v>
@@ -3211,10 +3224,10 @@
         <v>87</v>
       </c>
       <c r="M21">
-        <v>7924011</v>
+        <v>62135963</v>
       </c>
       <c r="N21">
-        <v>7924334</v>
+        <v>62150563</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.2">
@@ -3228,34 +3241,34 @@
         <v>17</v>
       </c>
       <c r="D22" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="E22" t="s">
-        <v>93</v>
-      </c>
-      <c r="G22" t="s">
-        <v>19</v>
+        <v>96</v>
+      </c>
+      <c r="F22" t="s">
+        <v>97</v>
       </c>
       <c r="H22">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="I22" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="J22">
-        <v>106144566</v>
+        <v>100616497</v>
       </c>
       <c r="K22" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="L22" t="s">
         <v>87</v>
       </c>
       <c r="M22">
-        <v>62135963</v>
+        <v>67390298</v>
       </c>
       <c r="N22">
-        <v>62150563</v>
+        <v>67394204</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.2">
@@ -3269,34 +3282,31 @@
         <v>17</v>
       </c>
       <c r="D23" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="E23" t="s">
-        <v>96</v>
-      </c>
-      <c r="F23" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="H23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I23" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="J23">
-        <v>100616497</v>
+        <v>100862691</v>
       </c>
       <c r="K23" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="L23" t="s">
         <v>87</v>
       </c>
       <c r="M23">
-        <v>67390298</v>
+        <v>67612675</v>
       </c>
       <c r="N23">
-        <v>67394204</v>
+        <v>67615320</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.2">
@@ -3310,19 +3320,22 @@
         <v>17</v>
       </c>
       <c r="D24" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="E24" t="s">
-        <v>100</v>
+        <v>103</v>
+      </c>
+      <c r="G24" t="s">
+        <v>24</v>
       </c>
       <c r="H24">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I24" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="J24">
-        <v>100862691</v>
+        <v>100616198</v>
       </c>
       <c r="K24" t="s">
         <v>43</v>
@@ -3331,10 +3344,10 @@
         <v>87</v>
       </c>
       <c r="M24">
-        <v>67612675</v>
-      </c>
-      <c r="N24">
-        <v>67615320</v>
+        <v>77569259</v>
+      </c>
+      <c r="N24" s="1">
+        <v>77574524</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.2">
@@ -3348,34 +3361,37 @@
         <v>17</v>
       </c>
       <c r="D25" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="E25" t="s">
-        <v>103</v>
+        <v>106</v>
+      </c>
+      <c r="F25" t="s">
+        <v>107</v>
       </c>
       <c r="G25" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="H25">
-        <v>6</v>
+        <v>118</v>
       </c>
       <c r="I25" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="J25">
-        <v>100616198</v>
+        <v>100862683</v>
       </c>
       <c r="K25" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="L25" t="s">
         <v>87</v>
       </c>
       <c r="M25">
-        <v>77569259</v>
-      </c>
-      <c r="N25" s="1">
-        <v>77574524</v>
+        <v>101565794</v>
+      </c>
+      <c r="N25">
+        <v>101575259</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.2">
@@ -3389,37 +3405,37 @@
         <v>17</v>
       </c>
       <c r="D26" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="E26" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="F26" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="G26" t="s">
         <v>19</v>
       </c>
       <c r="H26">
-        <v>118</v>
+        <v>37</v>
       </c>
       <c r="I26" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="J26">
-        <v>100862683</v>
+        <v>100616444</v>
       </c>
       <c r="K26" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="L26" t="s">
         <v>87</v>
       </c>
       <c r="M26">
-        <v>101565794</v>
+        <v>118591724</v>
       </c>
       <c r="N26">
-        <v>101575259</v>
+        <v>118600883</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.2">
@@ -3433,37 +3449,34 @@
         <v>17</v>
       </c>
       <c r="D27" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="E27" t="s">
-        <v>110</v>
-      </c>
-      <c r="F27" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="G27" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="H27">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="I27" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="J27">
-        <v>100616444</v>
+        <v>106144603</v>
       </c>
       <c r="K27" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="L27" t="s">
-        <v>87</v>
+        <v>116</v>
       </c>
       <c r="M27">
-        <v>118591724</v>
+        <v>8914009</v>
       </c>
       <c r="N27">
-        <v>118600883</v>
+        <v>8921064</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.2">
@@ -3477,34 +3490,25 @@
         <v>17</v>
       </c>
       <c r="D28" t="s">
-        <v>113</v>
-      </c>
-      <c r="E28" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="G28" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="H28">
-        <v>23</v>
-      </c>
-      <c r="I28" t="s">
-        <v>115</v>
-      </c>
-      <c r="J28">
-        <v>106144603</v>
+        <v>50</v>
       </c>
       <c r="K28" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="L28" t="s">
         <v>116</v>
       </c>
       <c r="M28">
-        <v>8914009</v>
+        <v>34772555</v>
       </c>
       <c r="N28">
-        <v>8921064</v>
+        <v>34782217</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.2">
@@ -3518,25 +3522,34 @@
         <v>17</v>
       </c>
       <c r="D29" t="s">
-        <v>117</v>
+        <v>118</v>
+      </c>
+      <c r="E29" t="s">
+        <v>119</v>
       </c>
       <c r="G29" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="H29">
-        <v>50</v>
+        <v>24</v>
+      </c>
+      <c r="I29" t="s">
+        <v>120</v>
+      </c>
+      <c r="J29">
+        <v>106144564</v>
       </c>
       <c r="K29" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="L29" t="s">
         <v>116</v>
       </c>
       <c r="M29">
-        <v>34772555</v>
+        <v>51296258</v>
       </c>
       <c r="N29">
-        <v>34782217</v>
+        <v>51307150</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.2">
@@ -3550,34 +3563,37 @@
         <v>17</v>
       </c>
       <c r="D30" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="E30" t="s">
+        <v>122</v>
+      </c>
+      <c r="F30" t="s">
+        <v>123</v>
+      </c>
+      <c r="G30" t="s">
+        <v>19</v>
+      </c>
+      <c r="H30">
         <v>119</v>
       </c>
-      <c r="G30" t="s">
-        <v>24</v>
-      </c>
-      <c r="H30">
-        <v>24</v>
-      </c>
       <c r="I30" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="J30">
-        <v>106144564</v>
+        <v>100616103</v>
       </c>
       <c r="K30" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="L30" t="s">
         <v>116</v>
       </c>
       <c r="M30">
-        <v>51296258</v>
+        <v>58721242</v>
       </c>
       <c r="N30">
-        <v>51307150</v>
+        <v>58730698</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.2">
@@ -3591,25 +3607,22 @@
         <v>17</v>
       </c>
       <c r="D31" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="E31" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="F31" t="s">
-        <v>123</v>
-      </c>
-      <c r="G31" t="s">
-        <v>19</v>
+        <v>127</v>
       </c>
       <c r="H31">
-        <v>119</v>
+        <v>5</v>
       </c>
       <c r="I31" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="J31">
-        <v>100616103</v>
+        <v>100616412</v>
       </c>
       <c r="K31" t="s">
         <v>43</v>
@@ -3618,10 +3631,10 @@
         <v>116</v>
       </c>
       <c r="M31">
-        <v>58721242</v>
+        <v>112259651</v>
       </c>
       <c r="N31">
-        <v>58730698</v>
+        <v>112259984</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.2">
@@ -3635,22 +3648,13 @@
         <v>17</v>
       </c>
       <c r="D32" t="s">
-        <v>125</v>
-      </c>
-      <c r="E32" t="s">
-        <v>126</v>
-      </c>
-      <c r="F32" t="s">
-        <v>127</v>
+        <v>129</v>
+      </c>
+      <c r="G32" t="s">
+        <v>19</v>
       </c>
       <c r="H32">
-        <v>5</v>
-      </c>
-      <c r="I32" t="s">
-        <v>128</v>
-      </c>
-      <c r="J32">
-        <v>100616412</v>
+        <v>42</v>
       </c>
       <c r="K32" t="s">
         <v>43</v>
@@ -3659,10 +3663,10 @@
         <v>116</v>
       </c>
       <c r="M32">
-        <v>112259651</v>
+        <v>133667120</v>
       </c>
       <c r="N32">
-        <v>112259984</v>
+        <v>133673132</v>
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.2">
@@ -3676,25 +3680,34 @@
         <v>17</v>
       </c>
       <c r="D33" t="s">
-        <v>129</v>
+        <v>130</v>
+      </c>
+      <c r="E33" t="s">
+        <v>131</v>
       </c>
       <c r="G33" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="H33">
-        <v>42</v>
+        <v>25</v>
+      </c>
+      <c r="I33" t="s">
+        <v>132</v>
+      </c>
+      <c r="J33">
+        <v>106144605</v>
       </c>
       <c r="K33" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="L33" t="s">
-        <v>116</v>
+        <v>133</v>
       </c>
       <c r="M33">
-        <v>133667120</v>
+        <v>37530786</v>
       </c>
       <c r="N33">
-        <v>133673132</v>
+        <v>37533118</v>
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.2">
@@ -3708,34 +3721,25 @@
         <v>17</v>
       </c>
       <c r="D34" t="s">
-        <v>130</v>
-      </c>
-      <c r="E34" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="G34" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="H34">
-        <v>25</v>
-      </c>
-      <c r="I34" t="s">
-        <v>132</v>
-      </c>
-      <c r="J34">
-        <v>106144605</v>
+        <v>71</v>
       </c>
       <c r="K34" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="L34" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="M34">
-        <v>37530786</v>
+        <v>24480625</v>
       </c>
       <c r="N34">
-        <v>37533118</v>
+        <v>24484121</v>
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.2">
@@ -3749,25 +3753,34 @@
         <v>17</v>
       </c>
       <c r="D35" t="s">
-        <v>134</v>
+        <v>136</v>
+      </c>
+      <c r="E35" t="s">
+        <v>137</v>
       </c>
       <c r="G35" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="H35">
-        <v>71</v>
+        <v>26</v>
+      </c>
+      <c r="I35" t="s">
+        <v>138</v>
+      </c>
+      <c r="J35">
+        <v>106144572</v>
       </c>
       <c r="K35" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="L35" t="s">
         <v>135</v>
       </c>
       <c r="M35">
-        <v>24480625</v>
+        <v>45488688</v>
       </c>
       <c r="N35">
-        <v>24484121</v>
+        <v>45492897</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.2">
@@ -3781,22 +3794,22 @@
         <v>17</v>
       </c>
       <c r="D36" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E36" t="s">
-        <v>137</v>
-      </c>
-      <c r="G36" t="s">
-        <v>24</v>
+        <v>140</v>
+      </c>
+      <c r="F36" t="s">
+        <v>141</v>
       </c>
       <c r="H36">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="I36" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="J36">
-        <v>106144572</v>
+        <v>100862697</v>
       </c>
       <c r="K36" t="s">
         <v>20</v>
@@ -3805,10 +3818,10 @@
         <v>135</v>
       </c>
       <c r="M36">
-        <v>45488688</v>
+        <v>70279954</v>
       </c>
       <c r="N36">
-        <v>45492897</v>
+        <v>70282683</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.2">
@@ -3822,22 +3835,22 @@
         <v>17</v>
       </c>
       <c r="D37" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="E37" t="s">
-        <v>140</v>
-      </c>
-      <c r="F37" t="s">
-        <v>141</v>
+        <v>144</v>
+      </c>
+      <c r="G37" t="s">
+        <v>24</v>
       </c>
       <c r="H37">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="I37" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="J37">
-        <v>100862697</v>
+        <v>106144565</v>
       </c>
       <c r="K37" t="s">
         <v>20</v>
@@ -3846,10 +3859,10 @@
         <v>135</v>
       </c>
       <c r="M37">
-        <v>70279954</v>
+        <v>91692008</v>
       </c>
       <c r="N37">
-        <v>70282683</v>
+        <v>91693212</v>
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.2">
@@ -3863,34 +3876,37 @@
         <v>17</v>
       </c>
       <c r="D38" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="E38" t="s">
-        <v>144</v>
+        <v>147</v>
+      </c>
+      <c r="F38" t="s">
+        <v>148</v>
       </c>
       <c r="G38" t="s">
-        <v>24</v>
+        <v>76</v>
       </c>
       <c r="H38">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="I38" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="J38">
-        <v>106144565</v>
+        <v>100862698</v>
       </c>
       <c r="K38" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="L38" t="s">
         <v>135</v>
       </c>
       <c r="M38">
-        <v>91692008</v>
+        <v>92511119</v>
       </c>
       <c r="N38">
-        <v>91693212</v>
+        <v>92516158</v>
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.2">
@@ -3904,37 +3920,37 @@
         <v>17</v>
       </c>
       <c r="D39" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="E39" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="F39" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G39" t="s">
         <v>76</v>
       </c>
       <c r="H39">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I39" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="J39">
-        <v>100862698</v>
+        <v>51359</v>
       </c>
       <c r="K39" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="L39" t="s">
         <v>135</v>
       </c>
       <c r="M39">
-        <v>92511119</v>
+        <v>99452044</v>
       </c>
       <c r="N39">
-        <v>92516158</v>
+        <v>99457077</v>
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.2">
@@ -3948,37 +3964,31 @@
         <v>17</v>
       </c>
       <c r="D40" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="E40" t="s">
-        <v>151</v>
-      </c>
-      <c r="F40" t="s">
-        <v>152</v>
-      </c>
-      <c r="G40" t="s">
-        <v>76</v>
+        <v>155</v>
       </c>
       <c r="H40">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I40" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="J40">
-        <v>51359</v>
+        <v>100133791</v>
       </c>
       <c r="K40" t="s">
         <v>20</v>
       </c>
       <c r="L40" t="s">
-        <v>135</v>
+        <v>157</v>
       </c>
       <c r="M40">
-        <v>99452044</v>
+        <v>54202966</v>
       </c>
       <c r="N40">
-        <v>99457077</v>
+        <v>54206909</v>
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.2">
@@ -3992,19 +4002,25 @@
         <v>17</v>
       </c>
       <c r="D41" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="E41" t="s">
-        <v>155</v>
+        <v>159</v>
+      </c>
+      <c r="F41" t="s">
+        <v>160</v>
+      </c>
+      <c r="G41" t="s">
+        <v>24</v>
       </c>
       <c r="H41">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I41" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="J41">
-        <v>100133791</v>
+        <v>100616496</v>
       </c>
       <c r="K41" t="s">
         <v>20</v>
@@ -4013,10 +4029,10 @@
         <v>157</v>
       </c>
       <c r="M41">
-        <v>54202966</v>
+        <v>55597079</v>
       </c>
       <c r="N41">
-        <v>54206909</v>
+        <v>55604574</v>
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.2">
@@ -4030,37 +4046,31 @@
         <v>17</v>
       </c>
       <c r="D42" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="E42" t="s">
-        <v>159</v>
-      </c>
-      <c r="F42" t="s">
-        <v>160</v>
-      </c>
-      <c r="G42" t="s">
-        <v>24</v>
+        <v>163</v>
       </c>
       <c r="H42">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I42" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="J42">
-        <v>100616496</v>
+        <v>100507321</v>
       </c>
       <c r="K42" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="L42" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="M42">
-        <v>55597079</v>
+        <v>2708390</v>
       </c>
       <c r="N42">
-        <v>55604574</v>
+        <v>2722572</v>
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.2">
@@ -4074,31 +4084,25 @@
         <v>17</v>
       </c>
       <c r="D43" t="s">
-        <v>162</v>
-      </c>
-      <c r="E43" t="s">
-        <v>163</v>
+        <v>166</v>
+      </c>
+      <c r="G43" t="s">
+        <v>19</v>
       </c>
       <c r="H43">
-        <v>1</v>
-      </c>
-      <c r="I43" t="s">
-        <v>164</v>
-      </c>
-      <c r="J43">
-        <v>100507321</v>
+        <v>4034</v>
       </c>
       <c r="K43" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="L43" t="s">
         <v>165</v>
       </c>
       <c r="M43">
-        <v>2708390</v>
+        <v>2976160</v>
       </c>
       <c r="N43">
-        <v>2722572</v>
+        <v>2977661</v>
       </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.2">
@@ -4112,25 +4116,37 @@
         <v>17</v>
       </c>
       <c r="D44" t="s">
-        <v>166</v>
-      </c>
-      <c r="G44" t="s">
-        <v>19</v>
+        <v>167</v>
+      </c>
+      <c r="E44" t="s">
+        <v>168</v>
+      </c>
+      <c r="F44" t="s">
+        <v>169</v>
+      </c>
+      <c r="G44">
+        <v>9</v>
       </c>
       <c r="H44">
-        <v>4034</v>
+        <v>9</v>
+      </c>
+      <c r="I44" t="s">
+        <v>170</v>
+      </c>
+      <c r="J44">
+        <v>111188137</v>
       </c>
       <c r="K44" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="L44" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="M44">
-        <v>2976160</v>
+        <v>6779397</v>
       </c>
       <c r="N44">
-        <v>2977661</v>
+        <v>6780027</v>
       </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.2">
@@ -4144,25 +4160,25 @@
         <v>17</v>
       </c>
       <c r="D45" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="E45" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="F45" t="s">
-        <v>169</v>
-      </c>
-      <c r="G45">
-        <v>9</v>
+        <v>174</v>
+      </c>
+      <c r="G45" t="s">
+        <v>175</v>
       </c>
       <c r="H45">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="I45" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="J45">
-        <v>111188137</v>
+        <v>85314</v>
       </c>
       <c r="K45" t="s">
         <v>43</v>
@@ -4171,10 +4187,10 @@
         <v>171</v>
       </c>
       <c r="M45">
-        <v>6779397</v>
+        <v>26557587</v>
       </c>
       <c r="N45">
-        <v>6780027</v>
+        <v>26559832</v>
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.2">
@@ -4188,37 +4204,34 @@
         <v>17</v>
       </c>
       <c r="D46" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="E46" t="s">
-        <v>173</v>
-      </c>
-      <c r="F46" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="G46" t="s">
-        <v>175</v>
+        <v>24</v>
       </c>
       <c r="H46">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="I46" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="J46">
-        <v>85314</v>
+        <v>105694156</v>
       </c>
       <c r="K46" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="L46" t="s">
         <v>171</v>
       </c>
       <c r="M46">
-        <v>26557587</v>
+        <v>35689889</v>
       </c>
       <c r="N46">
-        <v>26559832</v>
+        <v>35693622</v>
       </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.2">
@@ -4232,34 +4245,31 @@
         <v>17</v>
       </c>
       <c r="D47" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E47" t="s">
-        <v>178</v>
-      </c>
-      <c r="G47" t="s">
-        <v>24</v>
+        <v>181</v>
       </c>
       <c r="H47">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="I47" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="J47">
-        <v>105694156</v>
+        <v>111188144</v>
       </c>
       <c r="K47" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="L47" t="s">
         <v>171</v>
       </c>
       <c r="M47">
-        <v>35689889</v>
+        <v>47248932</v>
       </c>
       <c r="N47">
-        <v>35693622</v>
+        <v>47249567</v>
       </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.2">
@@ -4273,31 +4283,34 @@
         <v>17</v>
       </c>
       <c r="D48" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="E48" t="s">
-        <v>181</v>
+        <v>184</v>
+      </c>
+      <c r="G48" t="s">
+        <v>24</v>
       </c>
       <c r="H48">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="I48" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="J48">
-        <v>111188144</v>
+        <v>106144583</v>
       </c>
       <c r="K48" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="L48" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
       <c r="M48">
-        <v>47248932</v>
+        <v>13656680</v>
       </c>
       <c r="N48">
-        <v>47249567</v>
+        <v>13657837</v>
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.2">
@@ -4311,34 +4324,37 @@
         <v>17</v>
       </c>
       <c r="D49" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="E49" t="s">
-        <v>184</v>
+        <v>188</v>
+      </c>
+      <c r="F49" t="s">
+        <v>189</v>
       </c>
       <c r="G49" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="H49">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="I49" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="J49">
-        <v>106144583</v>
+        <v>100616445</v>
       </c>
       <c r="K49" t="s">
         <v>20</v>
       </c>
       <c r="L49" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="M49">
-        <v>13656680</v>
+        <v>385095</v>
       </c>
       <c r="N49">
-        <v>13657837</v>
+        <v>387637</v>
       </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.2">
@@ -4352,37 +4368,34 @@
         <v>17</v>
       </c>
       <c r="D50" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="E50" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="F50" t="s">
-        <v>189</v>
-      </c>
-      <c r="G50" t="s">
-        <v>19</v>
+        <v>194</v>
       </c>
       <c r="H50">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="I50" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="J50">
-        <v>100616445</v>
+        <v>100616199</v>
       </c>
       <c r="K50" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="L50" t="s">
         <v>191</v>
       </c>
       <c r="M50">
-        <v>385095</v>
+        <v>9622047</v>
       </c>
       <c r="N50">
-        <v>387637</v>
+        <v>9622385</v>
       </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.2">
@@ -4396,34 +4409,25 @@
         <v>17</v>
       </c>
       <c r="D51" t="s">
-        <v>192</v>
-      </c>
-      <c r="E51" t="s">
-        <v>193</v>
-      </c>
-      <c r="F51" t="s">
-        <v>194</v>
+        <v>196</v>
+      </c>
+      <c r="G51" t="s">
+        <v>19</v>
       </c>
       <c r="H51">
-        <v>7</v>
-      </c>
-      <c r="I51" t="s">
-        <v>195</v>
-      </c>
-      <c r="J51">
-        <v>100616199</v>
+        <v>52</v>
       </c>
       <c r="K51" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="L51" t="s">
         <v>191</v>
       </c>
       <c r="M51">
-        <v>9622047</v>
+        <v>20387400</v>
       </c>
       <c r="N51">
-        <v>9622385</v>
+        <v>20397512</v>
       </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.2">
@@ -4437,13 +4441,25 @@
         <v>17</v>
       </c>
       <c r="D52" t="s">
-        <v>196</v>
+        <v>197</v>
+      </c>
+      <c r="E52" t="s">
+        <v>198</v>
+      </c>
+      <c r="F52" t="s">
+        <v>199</v>
       </c>
       <c r="G52" t="s">
-        <v>19</v>
+        <v>81</v>
       </c>
       <c r="H52">
-        <v>52</v>
+        <v>1</v>
+      </c>
+      <c r="I52" t="s">
+        <v>200</v>
+      </c>
+      <c r="J52">
+        <v>105372315</v>
       </c>
       <c r="K52" t="s">
         <v>20</v>
@@ -4452,10 +4468,10 @@
         <v>191</v>
       </c>
       <c r="M52">
-        <v>20387400</v>
+        <v>20480255</v>
       </c>
       <c r="N52">
-        <v>20397512</v>
+        <v>20481117</v>
       </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.2">
@@ -4469,25 +4485,13 @@
         <v>17</v>
       </c>
       <c r="D53" t="s">
-        <v>197</v>
-      </c>
-      <c r="E53" t="s">
-        <v>198</v>
-      </c>
-      <c r="F53" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="G53" t="s">
-        <v>81</v>
+        <v>19</v>
       </c>
       <c r="H53">
-        <v>1</v>
-      </c>
-      <c r="I53" t="s">
-        <v>200</v>
-      </c>
-      <c r="J53">
-        <v>105372315</v>
+        <v>51</v>
       </c>
       <c r="K53" t="s">
         <v>20</v>
@@ -4496,10 +4500,10 @@
         <v>191</v>
       </c>
       <c r="M53">
-        <v>20480255</v>
+        <v>22757824</v>
       </c>
       <c r="N53">
-        <v>20481117</v>
+        <v>22764561</v>
       </c>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.2">
@@ -4513,13 +4517,13 @@
         <v>17</v>
       </c>
       <c r="D54" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="G54" t="s">
         <v>19</v>
       </c>
       <c r="H54">
-        <v>113</v>
+        <v>19</v>
       </c>
       <c r="K54" t="s">
         <v>43</v>
@@ -4528,10 +4532,10 @@
         <v>191</v>
       </c>
       <c r="M54">
-        <v>21841536</v>
+        <v>28128498</v>
       </c>
       <c r="N54">
-        <v>21841542</v>
+        <v>28137361</v>
       </c>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.2">
@@ -4545,25 +4549,31 @@
         <v>17</v>
       </c>
       <c r="D55" t="s">
-        <v>202</v>
-      </c>
-      <c r="G55" t="s">
-        <v>19</v>
+        <v>204</v>
+      </c>
+      <c r="E55" t="s">
+        <v>205</v>
       </c>
       <c r="H55">
-        <v>51</v>
+        <v>28</v>
+      </c>
+      <c r="I55" t="s">
+        <v>206</v>
+      </c>
+      <c r="J55">
+        <v>106707175</v>
       </c>
       <c r="K55" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="L55" t="s">
         <v>191</v>
       </c>
       <c r="M55">
-        <v>22757824</v>
+        <v>28135954</v>
       </c>
       <c r="N55">
-        <v>22764561</v>
+        <v>28136531</v>
       </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.2">
@@ -4576,26 +4586,26 @@
       <c r="C56" t="s">
         <v>17</v>
       </c>
-      <c r="D56" t="s">
-        <v>203</v>
-      </c>
-      <c r="G56" t="s">
-        <v>19</v>
+      <c r="E56" t="s">
+        <v>207</v>
+      </c>
+      <c r="F56" t="s">
+        <v>208</v>
       </c>
       <c r="H56">
-        <v>19</v>
+        <v>4700</v>
       </c>
       <c r="K56" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="L56" t="s">
         <v>191</v>
       </c>
       <c r="M56">
-        <v>28128498</v>
+        <v>29097595</v>
       </c>
       <c r="N56">
-        <v>28137361</v>
+        <v>29106136</v>
       </c>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.2">
@@ -4609,31 +4619,34 @@
         <v>17</v>
       </c>
       <c r="D57" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="E57" t="s">
-        <v>205</v>
+        <v>210</v>
+      </c>
+      <c r="G57" t="s">
+        <v>19</v>
       </c>
       <c r="H57">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I57" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="J57">
-        <v>106707175</v>
+        <v>106144555</v>
       </c>
       <c r="K57" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="L57" t="s">
         <v>191</v>
       </c>
       <c r="M57">
-        <v>28135954</v>
+        <v>37597549</v>
       </c>
       <c r="N57">
-        <v>28136531</v>
+        <v>37607066</v>
       </c>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.2">
@@ -4646,26 +4659,32 @@
       <c r="C58" t="s">
         <v>17</v>
       </c>
+      <c r="D58" t="s">
+        <v>212</v>
+      </c>
       <c r="E58" t="s">
-        <v>207</v>
-      </c>
-      <c r="F58" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="H58">
-        <v>4700</v>
+        <v>11</v>
+      </c>
+      <c r="I58" t="s">
+        <v>214</v>
+      </c>
+      <c r="J58">
+        <v>111188141</v>
       </c>
       <c r="K58" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="L58" t="s">
         <v>191</v>
       </c>
       <c r="M58">
-        <v>29097595</v>
+        <v>39426730</v>
       </c>
       <c r="N58">
-        <v>29106136</v>
+        <v>39427348</v>
       </c>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.2">
@@ -4679,34 +4698,34 @@
         <v>17</v>
       </c>
       <c r="D59" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="E59" t="s">
-        <v>210</v>
-      </c>
-      <c r="G59" t="s">
-        <v>19</v>
+        <v>216</v>
+      </c>
+      <c r="F59" t="s">
+        <v>217</v>
       </c>
       <c r="H59">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="I59" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="J59">
-        <v>106144555</v>
+        <v>100616107</v>
       </c>
       <c r="K59" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="L59" t="s">
         <v>191</v>
       </c>
       <c r="M59">
-        <v>37597549</v>
+        <v>52311587</v>
       </c>
       <c r="N59">
-        <v>37607066</v>
+        <v>52311924</v>
       </c>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.2">
@@ -4720,31 +4739,37 @@
         <v>17</v>
       </c>
       <c r="D60" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="E60" t="s">
-        <v>213</v>
+        <v>220</v>
+      </c>
+      <c r="F60" t="s">
+        <v>221</v>
+      </c>
+      <c r="G60" t="s">
+        <v>222</v>
       </c>
       <c r="H60">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="I60" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="J60">
-        <v>111188141</v>
+        <v>107985332</v>
       </c>
       <c r="K60" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="L60" t="s">
         <v>191</v>
       </c>
       <c r="M60">
-        <v>39426730</v>
+        <v>53510765</v>
       </c>
       <c r="N60">
-        <v>39427348</v>
+        <v>53516433</v>
       </c>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.2">
@@ -4758,34 +4783,37 @@
         <v>17</v>
       </c>
       <c r="D61" t="s">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="E61" t="s">
-        <v>216</v>
+        <v>225</v>
       </c>
       <c r="F61" t="s">
-        <v>217</v>
+        <v>226</v>
+      </c>
+      <c r="G61" t="s">
+        <v>227</v>
       </c>
       <c r="H61">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I61" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="J61">
-        <v>100616107</v>
+        <v>147664</v>
       </c>
       <c r="K61" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="L61" t="s">
         <v>191</v>
       </c>
       <c r="M61">
-        <v>52311587</v>
+        <v>53517174</v>
       </c>
       <c r="N61">
-        <v>52311924</v>
+        <v>53519376</v>
       </c>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.2">
@@ -4799,25 +4827,25 @@
         <v>17</v>
       </c>
       <c r="D62" t="s">
-        <v>219</v>
+        <v>229</v>
       </c>
       <c r="E62" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="F62" t="s">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="G62" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="H62">
         <v>2</v>
       </c>
       <c r="I62" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="J62">
-        <v>107985332</v>
+        <v>100271846</v>
       </c>
       <c r="K62" t="s">
         <v>20</v>
@@ -4826,10 +4854,10 @@
         <v>191</v>
       </c>
       <c r="M62">
-        <v>53510765</v>
+        <v>53547993</v>
       </c>
       <c r="N62">
-        <v>53516433</v>
+        <v>53554933</v>
       </c>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.2">
@@ -4843,25 +4871,13 @@
         <v>17</v>
       </c>
       <c r="D63" t="s">
-        <v>224</v>
-      </c>
-      <c r="E63" t="s">
-        <v>225</v>
-      </c>
-      <c r="F63" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="G63" t="s">
-        <v>227</v>
+        <v>19</v>
       </c>
       <c r="H63">
-        <v>1</v>
-      </c>
-      <c r="I63" t="s">
-        <v>228</v>
-      </c>
-      <c r="J63">
-        <v>147664</v>
+        <v>13</v>
       </c>
       <c r="K63" t="s">
         <v>20</v>
@@ -4870,10 +4886,10 @@
         <v>191</v>
       </c>
       <c r="M63">
-        <v>53517174</v>
+        <v>53862348</v>
       </c>
       <c r="N63">
-        <v>53519376</v>
+        <v>53868044</v>
       </c>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.2">
@@ -4887,25 +4903,22 @@
         <v>17</v>
       </c>
       <c r="D64" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="E64" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="F64" t="s">
-        <v>231</v>
-      </c>
-      <c r="G64" t="s">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="H64">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I64" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="J64">
-        <v>100271846</v>
+        <v>105372481</v>
       </c>
       <c r="K64" t="s">
         <v>20</v>
@@ -4914,10 +4927,10 @@
         <v>191</v>
       </c>
       <c r="M64">
-        <v>53547993</v>
+        <v>58816743</v>
       </c>
       <c r="N64">
-        <v>53554933</v>
+        <v>58828178</v>
       </c>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.2">
@@ -4931,25 +4944,31 @@
         <v>17</v>
       </c>
       <c r="D65" t="s">
-        <v>233</v>
-      </c>
-      <c r="G65" t="s">
-        <v>19</v>
+        <v>238</v>
+      </c>
+      <c r="E65" t="s">
+        <v>239</v>
       </c>
       <c r="H65">
-        <v>13</v>
+        <v>2</v>
+      </c>
+      <c r="I65" t="s">
+        <v>240</v>
+      </c>
+      <c r="J65">
+        <v>111188149</v>
       </c>
       <c r="K65" t="s">
         <v>20</v>
       </c>
       <c r="L65" t="s">
-        <v>191</v>
+        <v>241</v>
       </c>
       <c r="M65">
-        <v>53862348</v>
+        <v>20126709</v>
       </c>
       <c r="N65">
-        <v>53868044</v>
+        <v>20127340</v>
       </c>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.2">
@@ -4963,34 +4982,34 @@
         <v>17</v>
       </c>
       <c r="D66" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="E66" t="s">
-        <v>235</v>
-      </c>
-      <c r="F66" t="s">
-        <v>236</v>
+        <v>243</v>
+      </c>
+      <c r="G66" t="s">
+        <v>24</v>
       </c>
       <c r="H66">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I66" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="J66">
-        <v>105372481</v>
+        <v>106144580</v>
       </c>
       <c r="K66" t="s">
         <v>20</v>
       </c>
       <c r="L66" t="s">
-        <v>191</v>
+        <v>241</v>
       </c>
       <c r="M66">
-        <v>58816743</v>
+        <v>53983779</v>
       </c>
       <c r="N66">
-        <v>58828178</v>
+        <v>53988562</v>
       </c>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.2">
@@ -5004,19 +5023,22 @@
         <v>17</v>
       </c>
       <c r="D67" t="s">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="E67" t="s">
-        <v>239</v>
+        <v>246</v>
+      </c>
+      <c r="G67" t="s">
+        <v>24</v>
       </c>
       <c r="H67">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="I67" t="s">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="J67">
-        <v>111188149</v>
+        <v>106144576</v>
       </c>
       <c r="K67" t="s">
         <v>20</v>
@@ -5025,10 +5047,10 @@
         <v>241</v>
       </c>
       <c r="M67">
-        <v>20126709</v>
+        <v>112796922</v>
       </c>
       <c r="N67">
-        <v>20127340</v>
+        <v>112802566</v>
       </c>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.2">
@@ -5042,22 +5064,22 @@
         <v>17</v>
       </c>
       <c r="D68" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="E68" t="s">
-        <v>243</v>
+        <v>249</v>
+      </c>
+      <c r="F68" t="s">
+        <v>250</v>
       </c>
       <c r="G68" t="s">
-        <v>24</v>
+        <v>76</v>
       </c>
       <c r="H68">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I68" t="s">
-        <v>244</v>
-      </c>
-      <c r="J68">
-        <v>106144580</v>
+        <v>251</v>
       </c>
       <c r="K68" t="s">
         <v>20</v>
@@ -5066,10 +5088,10 @@
         <v>241</v>
       </c>
       <c r="M68">
-        <v>53983779</v>
+        <v>155723544</v>
       </c>
       <c r="N68">
-        <v>53988562</v>
+        <v>155731248</v>
       </c>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.2">
@@ -5083,34 +5105,34 @@
         <v>17</v>
       </c>
       <c r="D69" t="s">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="E69" t="s">
-        <v>246</v>
+        <v>253</v>
+      </c>
+      <c r="F69" t="s">
+        <v>254</v>
       </c>
       <c r="G69" t="s">
-        <v>24</v>
+        <v>76</v>
       </c>
       <c r="H69">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="I69" t="s">
-        <v>247</v>
-      </c>
-      <c r="J69">
-        <v>106144576</v>
+        <v>255</v>
       </c>
       <c r="K69" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="L69" t="s">
         <v>241</v>
       </c>
       <c r="M69">
-        <v>112796922</v>
+        <v>166563971</v>
       </c>
       <c r="N69">
-        <v>112802566</v>
+        <v>166572761</v>
       </c>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.2">
@@ -5124,22 +5146,22 @@
         <v>17</v>
       </c>
       <c r="D70" t="s">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="E70" t="s">
-        <v>249</v>
-      </c>
-      <c r="F70" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="G70" t="s">
-        <v>76</v>
+        <v>24</v>
       </c>
       <c r="H70">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="I70" t="s">
-        <v>251</v>
+        <v>258</v>
+      </c>
+      <c r="J70">
+        <v>106144561</v>
       </c>
       <c r="K70" t="s">
         <v>20</v>
@@ -5148,10 +5170,10 @@
         <v>241</v>
       </c>
       <c r="M70">
-        <v>155723544</v>
+        <v>178273972</v>
       </c>
       <c r="N70">
-        <v>155731248</v>
+        <v>178277886</v>
       </c>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.2">
@@ -5165,34 +5187,31 @@
         <v>17</v>
       </c>
       <c r="D71" t="s">
-        <v>252</v>
+        <v>262</v>
       </c>
       <c r="E71" t="s">
-        <v>253</v>
-      </c>
-      <c r="F71" t="s">
-        <v>254</v>
-      </c>
-      <c r="G71" t="s">
-        <v>76</v>
+        <v>263</v>
       </c>
       <c r="H71">
         <v>8</v>
       </c>
       <c r="I71" t="s">
-        <v>255</v>
+        <v>264</v>
+      </c>
+      <c r="J71">
+        <v>100616108</v>
       </c>
       <c r="K71" t="s">
         <v>43</v>
       </c>
       <c r="L71" t="s">
-        <v>241</v>
+        <v>265</v>
       </c>
       <c r="M71">
-        <v>166563971</v>
+        <v>25379489</v>
       </c>
       <c r="N71">
-        <v>166572761</v>
+        <v>25379824</v>
       </c>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.2">
@@ -5206,34 +5225,25 @@
         <v>17</v>
       </c>
       <c r="D72" t="s">
-        <v>256</v>
-      </c>
-      <c r="E72" t="s">
-        <v>257</v>
+        <v>266</v>
       </c>
       <c r="G72" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="H72">
-        <v>14</v>
-      </c>
-      <c r="I72" t="s">
-        <v>258</v>
-      </c>
-      <c r="J72">
-        <v>106144561</v>
+        <v>59</v>
       </c>
       <c r="K72" t="s">
         <v>20</v>
       </c>
       <c r="L72" t="s">
-        <v>241</v>
+        <v>265</v>
       </c>
       <c r="M72">
-        <v>178273972</v>
+        <v>32714750</v>
       </c>
       <c r="N72">
-        <v>178277886</v>
+        <v>32724384</v>
       </c>
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.2">
@@ -5247,34 +5257,37 @@
         <v>17</v>
       </c>
       <c r="D73" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="E73" t="s">
-        <v>260</v>
+        <v>268</v>
+      </c>
+      <c r="F73" t="s">
+        <v>269</v>
       </c>
       <c r="G73" t="s">
         <v>19</v>
       </c>
       <c r="H73">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="I73" t="s">
-        <v>261</v>
+        <v>270</v>
       </c>
       <c r="J73">
-        <v>106144591</v>
+        <v>100616197</v>
       </c>
       <c r="K73" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="L73" t="s">
-        <v>241</v>
+        <v>271</v>
       </c>
       <c r="M73">
-        <v>187385634</v>
+        <v>19933916</v>
       </c>
       <c r="N73">
-        <v>187387099</v>
+        <v>19934992</v>
       </c>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.2">
@@ -5288,31 +5301,34 @@
         <v>17</v>
       </c>
       <c r="D74" t="s">
-        <v>262</v>
+        <v>272</v>
       </c>
       <c r="E74" t="s">
-        <v>263</v>
+        <v>273</v>
+      </c>
+      <c r="F74" t="s">
+        <v>274</v>
       </c>
       <c r="H74">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I74" t="s">
-        <v>264</v>
+        <v>275</v>
       </c>
       <c r="J74">
-        <v>100616108</v>
+        <v>90625</v>
       </c>
       <c r="K74" t="s">
         <v>43</v>
       </c>
       <c r="L74" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="M74">
-        <v>25379489</v>
+        <v>44336913</v>
       </c>
       <c r="N74">
-        <v>25379824</v>
+        <v>44345740</v>
       </c>
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.2">
@@ -5326,25 +5342,37 @@
         <v>17</v>
       </c>
       <c r="D75" t="s">
-        <v>266</v>
+        <v>276</v>
+      </c>
+      <c r="E75" t="s">
+        <v>277</v>
+      </c>
+      <c r="F75" t="s">
+        <v>278</v>
       </c>
       <c r="G75" t="s">
         <v>19</v>
       </c>
       <c r="H75">
-        <v>59</v>
+        <v>101</v>
+      </c>
+      <c r="I75" t="s">
+        <v>279</v>
+      </c>
+      <c r="J75">
+        <v>100862684</v>
       </c>
       <c r="K75" t="s">
         <v>20</v>
       </c>
       <c r="L75" t="s">
-        <v>265</v>
+        <v>280</v>
       </c>
       <c r="M75">
-        <v>32714750</v>
+        <v>18926187</v>
       </c>
       <c r="N75">
-        <v>32724384</v>
+        <v>18934279</v>
       </c>
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.2">
@@ -5358,37 +5386,25 @@
         <v>17</v>
       </c>
       <c r="D76" t="s">
-        <v>267</v>
-      </c>
-      <c r="E76" t="s">
-        <v>268</v>
-      </c>
-      <c r="F76" t="s">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="G76" t="s">
         <v>19</v>
       </c>
       <c r="H76">
-        <v>23</v>
-      </c>
-      <c r="I76" t="s">
-        <v>270</v>
-      </c>
-      <c r="J76">
-        <v>100616197</v>
+        <v>345</v>
       </c>
       <c r="K76" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="L76" t="s">
-        <v>271</v>
+        <v>280</v>
       </c>
       <c r="M76">
-        <v>19933916</v>
+        <v>23879930</v>
       </c>
       <c r="N76">
-        <v>19934992</v>
+        <v>23888810</v>
       </c>
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.2">
@@ -5402,34 +5418,37 @@
         <v>17</v>
       </c>
       <c r="D77" t="s">
-        <v>272</v>
+        <v>282</v>
       </c>
       <c r="E77" t="s">
-        <v>273</v>
+        <v>283</v>
       </c>
       <c r="F77" t="s">
-        <v>274</v>
+        <v>284</v>
+      </c>
+      <c r="G77" t="s">
+        <v>19</v>
       </c>
       <c r="H77">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I77" t="s">
-        <v>275</v>
+        <v>285</v>
       </c>
       <c r="J77">
-        <v>90625</v>
+        <v>100616100</v>
       </c>
       <c r="K77" t="s">
         <v>43</v>
       </c>
       <c r="L77" t="s">
-        <v>271</v>
+        <v>286</v>
       </c>
       <c r="M77">
-        <v>44336913</v>
+        <v>9889346</v>
       </c>
       <c r="N77">
-        <v>44345740</v>
+        <v>9896236</v>
       </c>
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.2">
@@ -5443,37 +5462,34 @@
         <v>17</v>
       </c>
       <c r="D78" t="s">
-        <v>276</v>
+        <v>287</v>
       </c>
       <c r="E78" t="s">
-        <v>277</v>
+        <v>288</v>
       </c>
       <c r="F78" t="s">
-        <v>278</v>
-      </c>
-      <c r="G78" t="s">
-        <v>19</v>
+        <v>289</v>
       </c>
       <c r="H78">
-        <v>101</v>
+        <v>1</v>
       </c>
       <c r="I78" t="s">
-        <v>279</v>
+        <v>290</v>
       </c>
       <c r="J78">
-        <v>100862684</v>
+        <v>100862693</v>
       </c>
       <c r="K78" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="L78" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="M78">
-        <v>18926187</v>
+        <v>16811648</v>
       </c>
       <c r="N78">
-        <v>18934279</v>
+        <v>16812243</v>
       </c>
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.2">
@@ -5487,25 +5503,37 @@
         <v>17</v>
       </c>
       <c r="D79" t="s">
-        <v>281</v>
+        <v>291</v>
+      </c>
+      <c r="E79" t="s">
+        <v>292</v>
+      </c>
+      <c r="F79" t="s">
+        <v>293</v>
       </c>
       <c r="G79" t="s">
         <v>19</v>
       </c>
       <c r="H79">
-        <v>345</v>
+        <v>5</v>
+      </c>
+      <c r="I79" t="s">
+        <v>294</v>
+      </c>
+      <c r="J79">
+        <v>60358</v>
       </c>
       <c r="K79" t="s">
         <v>20</v>
       </c>
       <c r="L79" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="M79">
-        <v>23879930</v>
+        <v>101409738</v>
       </c>
       <c r="N79">
-        <v>23888810</v>
+        <v>101420859</v>
       </c>
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.2">
@@ -5519,25 +5547,25 @@
         <v>17</v>
       </c>
       <c r="D80" t="s">
-        <v>282</v>
+        <v>295</v>
       </c>
       <c r="E80" t="s">
-        <v>283</v>
+        <v>296</v>
       </c>
       <c r="F80" t="s">
-        <v>284</v>
+        <v>297</v>
       </c>
       <c r="G80" t="s">
         <v>19</v>
       </c>
       <c r="H80">
-        <v>2</v>
+        <v>106</v>
       </c>
       <c r="I80" t="s">
-        <v>285</v>
+        <v>298</v>
       </c>
       <c r="J80">
-        <v>100616100</v>
+        <v>100862689</v>
       </c>
       <c r="K80" t="s">
         <v>43</v>
@@ -5546,10 +5574,10 @@
         <v>286</v>
       </c>
       <c r="M80">
-        <v>9889346</v>
+        <v>112743479</v>
       </c>
       <c r="N80">
-        <v>9896236</v>
+        <v>112752282</v>
       </c>
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.2">
@@ -5563,34 +5591,37 @@
         <v>17</v>
       </c>
       <c r="D81" t="s">
-        <v>287</v>
+        <v>299</v>
       </c>
       <c r="E81" t="s">
-        <v>288</v>
+        <v>300</v>
       </c>
       <c r="F81" t="s">
-        <v>289</v>
+        <v>301</v>
+      </c>
+      <c r="G81" t="s">
+        <v>19</v>
       </c>
       <c r="H81">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I81" t="s">
-        <v>290</v>
+        <v>302</v>
       </c>
       <c r="J81">
-        <v>100862693</v>
+        <v>60359</v>
       </c>
       <c r="K81" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="L81" t="s">
         <v>286</v>
       </c>
       <c r="M81">
-        <v>16811648</v>
+        <v>125608304</v>
       </c>
       <c r="N81">
-        <v>16812243</v>
+        <v>125619438</v>
       </c>
     </row>
     <row r="82" spans="1:14" x14ac:dyDescent="0.2">
@@ -5604,25 +5635,25 @@
         <v>17</v>
       </c>
       <c r="D82" t="s">
-        <v>291</v>
+        <v>303</v>
       </c>
       <c r="E82" t="s">
-        <v>292</v>
+        <v>304</v>
       </c>
       <c r="F82" t="s">
-        <v>293</v>
+        <v>305</v>
       </c>
       <c r="G82" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="H82">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I82" t="s">
-        <v>294</v>
+        <v>306</v>
       </c>
       <c r="J82">
-        <v>60358</v>
+        <v>100862696</v>
       </c>
       <c r="K82" t="s">
         <v>20</v>
@@ -5631,10 +5662,10 @@
         <v>286</v>
       </c>
       <c r="M82">
-        <v>101409738</v>
+        <v>141538631</v>
       </c>
       <c r="N82">
-        <v>101420859</v>
+        <v>141540355</v>
       </c>
     </row>
     <row r="83" spans="1:14" x14ac:dyDescent="0.2">
@@ -5648,25 +5679,25 @@
         <v>17</v>
       </c>
       <c r="D83" t="s">
-        <v>295</v>
+        <v>233</v>
       </c>
       <c r="E83" t="s">
-        <v>296</v>
+        <v>307</v>
       </c>
       <c r="F83" t="s">
-        <v>297</v>
+        <v>308</v>
       </c>
       <c r="G83" t="s">
         <v>19</v>
       </c>
       <c r="H83">
-        <v>106</v>
+        <v>13</v>
       </c>
       <c r="I83" t="s">
-        <v>298</v>
+        <v>309</v>
       </c>
       <c r="J83">
-        <v>100862689</v>
+        <v>100861467</v>
       </c>
       <c r="K83" t="s">
         <v>43</v>
@@ -5675,10 +5706,10 @@
         <v>286</v>
       </c>
       <c r="M83">
-        <v>112743479</v>
+        <v>148281477</v>
       </c>
       <c r="N83">
-        <v>112752282</v>
+        <v>148285396</v>
       </c>
     </row>
     <row r="84" spans="1:14" x14ac:dyDescent="0.2">
@@ -5692,37 +5723,34 @@
         <v>17</v>
       </c>
       <c r="D84" t="s">
-        <v>299</v>
+        <v>310</v>
       </c>
       <c r="E84" t="s">
-        <v>300</v>
+        <v>311</v>
       </c>
       <c r="F84" t="s">
-        <v>301</v>
+        <v>312</v>
       </c>
       <c r="G84" t="s">
-        <v>19</v>
+        <v>76</v>
       </c>
       <c r="H84">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I84" t="s">
-        <v>302</v>
-      </c>
-      <c r="J84">
-        <v>60359</v>
+        <v>313</v>
       </c>
       <c r="K84" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="L84" t="s">
         <v>286</v>
       </c>
       <c r="M84">
-        <v>125608304</v>
+        <v>166540223</v>
       </c>
       <c r="N84">
-        <v>125619438</v>
+        <v>166547792</v>
       </c>
     </row>
     <row r="85" spans="1:14" x14ac:dyDescent="0.2">
@@ -5736,25 +5764,25 @@
         <v>17</v>
       </c>
       <c r="D85" t="s">
-        <v>303</v>
+        <v>314</v>
       </c>
       <c r="E85" t="s">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c r="F85" t="s">
-        <v>305</v>
+        <v>316</v>
       </c>
       <c r="G85" t="s">
         <v>24</v>
       </c>
       <c r="H85">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I85" t="s">
-        <v>306</v>
+        <v>317</v>
       </c>
       <c r="J85">
-        <v>100862696</v>
+        <v>100862695</v>
       </c>
       <c r="K85" t="s">
         <v>20</v>
@@ -5763,10 +5791,10 @@
         <v>286</v>
       </c>
       <c r="M85">
-        <v>141538631</v>
+        <v>178772378</v>
       </c>
       <c r="N85">
-        <v>141540355</v>
+        <v>178777943</v>
       </c>
     </row>
     <row r="86" spans="1:14" x14ac:dyDescent="0.2">
@@ -5780,25 +5808,19 @@
         <v>17</v>
       </c>
       <c r="D86" t="s">
-        <v>233</v>
+        <v>318</v>
       </c>
       <c r="E86" t="s">
-        <v>307</v>
-      </c>
-      <c r="F86" t="s">
-        <v>308</v>
-      </c>
-      <c r="G86" t="s">
-        <v>19</v>
+        <v>319</v>
       </c>
       <c r="H86">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="I86" t="s">
-        <v>309</v>
+        <v>320</v>
       </c>
       <c r="J86">
-        <v>100861467</v>
+        <v>111188148</v>
       </c>
       <c r="K86" t="s">
         <v>43</v>
@@ -5807,10 +5829,10 @@
         <v>286</v>
       </c>
       <c r="M86">
-        <v>148281477</v>
+        <v>184731488</v>
       </c>
       <c r="N86">
-        <v>148285396</v>
+        <v>184732117</v>
       </c>
     </row>
     <row r="87" spans="1:14" x14ac:dyDescent="0.2">
@@ -5824,22 +5846,25 @@
         <v>17</v>
       </c>
       <c r="D87" t="s">
-        <v>310</v>
+        <v>321</v>
       </c>
       <c r="E87" t="s">
-        <v>311</v>
+        <v>322</v>
       </c>
       <c r="F87" t="s">
-        <v>312</v>
+        <v>323</v>
       </c>
       <c r="G87" t="s">
-        <v>76</v>
+        <v>19</v>
       </c>
       <c r="H87">
-        <v>9</v>
+        <v>117</v>
       </c>
       <c r="I87" t="s">
-        <v>313</v>
+        <v>324</v>
+      </c>
+      <c r="J87">
+        <v>100862688</v>
       </c>
       <c r="K87" t="s">
         <v>43</v>
@@ -5848,10 +5873,10 @@
         <v>286</v>
       </c>
       <c r="M87">
-        <v>166540223</v>
+        <v>185280336</v>
       </c>
       <c r="N87">
-        <v>166547792</v>
+        <v>185289515</v>
       </c>
     </row>
     <row r="88" spans="1:14" x14ac:dyDescent="0.2">
@@ -5865,37 +5890,25 @@
         <v>17</v>
       </c>
       <c r="D88" t="s">
-        <v>314</v>
-      </c>
-      <c r="E88" t="s">
-        <v>315</v>
-      </c>
-      <c r="F88" t="s">
-        <v>316</v>
+        <v>325</v>
       </c>
       <c r="G88" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="H88">
-        <v>5</v>
-      </c>
-      <c r="I88" t="s">
-        <v>317</v>
-      </c>
-      <c r="J88">
-        <v>100862695</v>
+        <v>77</v>
       </c>
       <c r="K88" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="L88" t="s">
-        <v>286</v>
+        <v>326</v>
       </c>
       <c r="M88">
-        <v>178772378</v>
+        <v>3980069</v>
       </c>
       <c r="N88">
-        <v>178777943</v>
+        <v>3988631</v>
       </c>
     </row>
     <row r="89" spans="1:14" x14ac:dyDescent="0.2">
@@ -5909,31 +5922,34 @@
         <v>17</v>
       </c>
       <c r="D89" t="s">
-        <v>318</v>
+        <v>327</v>
       </c>
       <c r="E89" t="s">
-        <v>319</v>
+        <v>328</v>
+      </c>
+      <c r="G89" t="s">
+        <v>24</v>
       </c>
       <c r="H89">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="I89" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="J89">
-        <v>111188148</v>
+        <v>106144597</v>
       </c>
       <c r="K89" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="L89" t="s">
-        <v>286</v>
+        <v>326</v>
       </c>
       <c r="M89">
-        <v>184731488</v>
+        <v>8422091</v>
       </c>
       <c r="N89">
-        <v>184732117</v>
+        <v>8429492</v>
       </c>
     </row>
     <row r="90" spans="1:14" x14ac:dyDescent="0.2">
@@ -5947,37 +5963,25 @@
         <v>17</v>
       </c>
       <c r="D90" t="s">
-        <v>321</v>
-      </c>
-      <c r="E90" t="s">
-        <v>322</v>
-      </c>
-      <c r="F90" t="s">
-        <v>323</v>
+        <v>83</v>
       </c>
       <c r="G90" t="s">
         <v>19</v>
       </c>
       <c r="H90">
-        <v>117</v>
-      </c>
-      <c r="I90" t="s">
-        <v>324</v>
-      </c>
-      <c r="J90">
-        <v>100862688</v>
+        <v>17</v>
       </c>
       <c r="K90" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="L90" t="s">
-        <v>286</v>
+        <v>326</v>
       </c>
       <c r="M90">
-        <v>185280336</v>
+        <v>9123515</v>
       </c>
       <c r="N90">
-        <v>185289515</v>
+        <v>9133075</v>
       </c>
     </row>
     <row r="91" spans="1:14" x14ac:dyDescent="0.2">
@@ -5991,25 +5995,25 @@
         <v>17</v>
       </c>
       <c r="D91" t="s">
-        <v>325</v>
+        <v>117</v>
       </c>
       <c r="G91" t="s">
         <v>19</v>
       </c>
       <c r="H91">
-        <v>77</v>
+        <v>50</v>
       </c>
       <c r="K91" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="L91" t="s">
         <v>326</v>
       </c>
       <c r="M91">
-        <v>3980069</v>
+        <v>9659588</v>
       </c>
       <c r="N91">
-        <v>3988631</v>
+        <v>9668650</v>
       </c>
     </row>
     <row r="92" spans="1:14" x14ac:dyDescent="0.2">
@@ -6023,34 +6027,37 @@
         <v>17</v>
       </c>
       <c r="D92" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="E92" t="s">
-        <v>328</v>
+        <v>331</v>
+      </c>
+      <c r="F92" t="s">
+        <v>332</v>
       </c>
       <c r="G92" t="s">
-        <v>24</v>
+        <v>76</v>
       </c>
       <c r="H92">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="I92" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="J92">
-        <v>106144597</v>
+        <v>100616446</v>
       </c>
       <c r="K92" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="L92" t="s">
         <v>326</v>
       </c>
       <c r="M92">
-        <v>8422091</v>
+        <v>23724532</v>
       </c>
       <c r="N92">
-        <v>8429492</v>
+        <v>23728952</v>
       </c>
     </row>
     <row r="93" spans="1:14" x14ac:dyDescent="0.2">
@@ -6064,25 +6071,34 @@
         <v>17</v>
       </c>
       <c r="D93" t="s">
-        <v>83</v>
-      </c>
-      <c r="G93" t="s">
-        <v>19</v>
+        <v>334</v>
+      </c>
+      <c r="E93" t="s">
+        <v>335</v>
+      </c>
+      <c r="F93" t="s">
+        <v>336</v>
       </c>
       <c r="H93">
-        <v>17</v>
+        <v>1</v>
+      </c>
+      <c r="I93" t="s">
+        <v>337</v>
+      </c>
+      <c r="J93">
+        <v>100288413</v>
       </c>
       <c r="K93" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="L93" t="s">
         <v>326</v>
       </c>
       <c r="M93">
-        <v>9123515</v>
+        <v>53608720</v>
       </c>
       <c r="N93">
-        <v>9133075</v>
+        <v>53617592</v>
       </c>
     </row>
     <row r="94" spans="1:14" x14ac:dyDescent="0.2">
@@ -6096,13 +6112,22 @@
         <v>17</v>
       </c>
       <c r="D94" t="s">
-        <v>117</v>
+        <v>338</v>
+      </c>
+      <c r="E94" t="s">
+        <v>339</v>
       </c>
       <c r="G94" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="H94">
-        <v>50</v>
+        <v>16</v>
+      </c>
+      <c r="I94" t="s">
+        <v>340</v>
+      </c>
+      <c r="J94">
+        <v>106144581</v>
       </c>
       <c r="K94" t="s">
         <v>20</v>
@@ -6111,10 +6136,10 @@
         <v>326</v>
       </c>
       <c r="M94">
-        <v>9659588</v>
+        <v>133803454</v>
       </c>
       <c r="N94">
-        <v>9668650</v>
+        <v>133810293</v>
       </c>
     </row>
     <row r="95" spans="1:14" x14ac:dyDescent="0.2">
@@ -6128,37 +6153,34 @@
         <v>17</v>
       </c>
       <c r="D95" t="s">
-        <v>330</v>
+        <v>48</v>
       </c>
       <c r="E95" t="s">
-        <v>331</v>
-      </c>
-      <c r="F95" t="s">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="G95" t="s">
-        <v>76</v>
+        <v>19</v>
       </c>
       <c r="H95">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I95" t="s">
-        <v>333</v>
+        <v>342</v>
       </c>
       <c r="J95">
-        <v>100616446</v>
+        <v>100616442</v>
       </c>
       <c r="K95" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="L95" t="s">
         <v>326</v>
       </c>
       <c r="M95">
-        <v>23724532</v>
+        <v>165916840</v>
       </c>
       <c r="N95">
-        <v>23728952</v>
+        <v>165924068</v>
       </c>
     </row>
     <row r="96" spans="1:14" x14ac:dyDescent="0.2">
@@ -6172,34 +6194,31 @@
         <v>17</v>
       </c>
       <c r="D96" t="s">
-        <v>334</v>
+        <v>343</v>
       </c>
       <c r="E96" t="s">
-        <v>335</v>
-      </c>
-      <c r="F96" t="s">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="H96">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I96" t="s">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="J96">
-        <v>100288413</v>
+        <v>111188147</v>
       </c>
       <c r="K96" t="s">
         <v>43</v>
       </c>
       <c r="L96" t="s">
-        <v>326</v>
+        <v>346</v>
       </c>
       <c r="M96">
-        <v>53608720</v>
+        <v>1578855</v>
       </c>
       <c r="N96">
-        <v>53617592</v>
+        <v>1579485</v>
       </c>
     </row>
     <row r="97" spans="1:14" x14ac:dyDescent="0.2">
@@ -6213,34 +6232,25 @@
         <v>17</v>
       </c>
       <c r="D97" t="s">
-        <v>338</v>
-      </c>
-      <c r="E97" t="s">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="G97" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="H97">
-        <v>16</v>
-      </c>
-      <c r="I97" t="s">
-        <v>340</v>
-      </c>
-      <c r="J97">
-        <v>106144581</v>
+        <v>104</v>
       </c>
       <c r="K97" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="L97" t="s">
-        <v>326</v>
+        <v>346</v>
       </c>
       <c r="M97">
-        <v>133803454</v>
+        <v>30487114</v>
       </c>
       <c r="N97">
-        <v>133810293</v>
+        <v>30496205</v>
       </c>
     </row>
     <row r="98" spans="1:14" x14ac:dyDescent="0.2">
@@ -6254,34 +6264,31 @@
         <v>17</v>
       </c>
       <c r="D98" t="s">
-        <v>48</v>
+        <v>348</v>
       </c>
       <c r="E98" t="s">
-        <v>341</v>
-      </c>
-      <c r="G98" t="s">
-        <v>19</v>
+        <v>349</v>
       </c>
       <c r="H98">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I98" t="s">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c r="J98">
-        <v>100616442</v>
+        <v>111188143</v>
       </c>
       <c r="K98" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="L98" t="s">
-        <v>326</v>
+        <v>346</v>
       </c>
       <c r="M98">
-        <v>165916840</v>
+        <v>34782791</v>
       </c>
       <c r="N98">
-        <v>165924068</v>
+        <v>34783397</v>
       </c>
     </row>
     <row r="99" spans="1:14" x14ac:dyDescent="0.2">
@@ -6295,31 +6302,34 @@
         <v>17</v>
       </c>
       <c r="D99" t="s">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="E99" t="s">
-        <v>344</v>
+        <v>352</v>
+      </c>
+      <c r="F99" t="s">
+        <v>353</v>
       </c>
       <c r="H99">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I99" t="s">
-        <v>345</v>
+        <v>354</v>
       </c>
       <c r="J99">
-        <v>111188147</v>
+        <v>100616462</v>
       </c>
       <c r="K99" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="L99" t="s">
         <v>346</v>
       </c>
       <c r="M99">
-        <v>1578855</v>
+        <v>70871465</v>
       </c>
       <c r="N99">
-        <v>1579485</v>
+        <v>70871802</v>
       </c>
     </row>
     <row r="100" spans="1:14" x14ac:dyDescent="0.2">
@@ -6333,25 +6343,34 @@
         <v>17</v>
       </c>
       <c r="D100" t="s">
-        <v>347</v>
+        <v>355</v>
+      </c>
+      <c r="E100" t="s">
+        <v>356</v>
       </c>
       <c r="G100" t="s">
         <v>19</v>
       </c>
       <c r="H100">
-        <v>104</v>
+        <v>31</v>
+      </c>
+      <c r="I100" t="s">
+        <v>357</v>
+      </c>
+      <c r="J100">
+        <v>106144590</v>
       </c>
       <c r="K100" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="L100" t="s">
         <v>346</v>
       </c>
       <c r="M100">
-        <v>30487114</v>
+        <v>92792380</v>
       </c>
       <c r="N100">
-        <v>30496205</v>
+        <v>92793912</v>
       </c>
     </row>
     <row r="101" spans="1:14" x14ac:dyDescent="0.2">
@@ -6365,19 +6384,13 @@
         <v>17</v>
       </c>
       <c r="D101" t="s">
-        <v>348</v>
-      </c>
-      <c r="E101" t="s">
-        <v>349</v>
+        <v>44</v>
+      </c>
+      <c r="G101" t="s">
+        <v>19</v>
       </c>
       <c r="H101">
-        <v>4</v>
-      </c>
-      <c r="I101" t="s">
-        <v>350</v>
-      </c>
-      <c r="J101">
-        <v>111188143</v>
+        <v>18</v>
       </c>
       <c r="K101" t="s">
         <v>43</v>
@@ -6386,10 +6399,10 @@
         <v>346</v>
       </c>
       <c r="M101">
-        <v>34782791</v>
+        <v>154016502</v>
       </c>
       <c r="N101">
-        <v>34783397</v>
+        <v>154024214</v>
       </c>
     </row>
     <row r="102" spans="1:14" x14ac:dyDescent="0.2">
@@ -6403,34 +6416,34 @@
         <v>17</v>
       </c>
       <c r="D102" t="s">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="E102" t="s">
-        <v>352</v>
-      </c>
-      <c r="F102" t="s">
-        <v>353</v>
+        <v>359</v>
+      </c>
+      <c r="G102" t="s">
+        <v>19</v>
       </c>
       <c r="H102">
-        <v>3</v>
+        <v>107</v>
       </c>
       <c r="I102" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="J102">
-        <v>100616462</v>
+        <v>100616101</v>
       </c>
       <c r="K102" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="L102" t="s">
         <v>346</v>
       </c>
       <c r="M102">
-        <v>70871465</v>
+        <v>156084717</v>
       </c>
       <c r="N102">
-        <v>70871802</v>
+        <v>156093896</v>
       </c>
     </row>
     <row r="103" spans="1:14" x14ac:dyDescent="0.2">
@@ -6444,34 +6457,37 @@
         <v>17</v>
       </c>
       <c r="D103" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="E103" t="s">
-        <v>356</v>
+        <v>362</v>
+      </c>
+      <c r="F103" t="s">
+        <v>363</v>
       </c>
       <c r="G103" t="s">
-        <v>19</v>
+        <v>222</v>
       </c>
       <c r="H103">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="I103" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="J103">
-        <v>106144590</v>
+        <v>405754</v>
       </c>
       <c r="K103" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="L103" t="s">
-        <v>346</v>
+        <v>365</v>
       </c>
       <c r="M103">
-        <v>92792380</v>
+        <v>11102722</v>
       </c>
       <c r="N103">
-        <v>92793912</v>
+        <v>11105864</v>
       </c>
     </row>
     <row r="104" spans="1:14" x14ac:dyDescent="0.2">
@@ -6485,25 +6501,25 @@
         <v>17</v>
       </c>
       <c r="D104" t="s">
-        <v>44</v>
+        <v>366</v>
       </c>
       <c r="G104" t="s">
         <v>19</v>
       </c>
       <c r="H104">
-        <v>18</v>
+        <v>69</v>
       </c>
       <c r="K104" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="L104" t="s">
-        <v>346</v>
+        <v>365</v>
       </c>
       <c r="M104">
-        <v>154016502</v>
+        <v>28650367</v>
       </c>
       <c r="N104">
-        <v>154024214</v>
+        <v>28660735</v>
       </c>
     </row>
     <row r="105" spans="1:14" x14ac:dyDescent="0.2">
@@ -6517,34 +6533,31 @@
         <v>17</v>
       </c>
       <c r="D105" t="s">
-        <v>358</v>
+        <v>367</v>
       </c>
       <c r="E105" t="s">
-        <v>359</v>
-      </c>
-      <c r="G105" t="s">
-        <v>19</v>
+        <v>368</v>
       </c>
       <c r="H105">
-        <v>107</v>
+        <v>12</v>
       </c>
       <c r="I105" t="s">
-        <v>360</v>
+        <v>369</v>
       </c>
       <c r="J105">
-        <v>100616101</v>
+        <v>105375011</v>
       </c>
       <c r="K105" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="L105" t="s">
-        <v>346</v>
+        <v>365</v>
       </c>
       <c r="M105">
-        <v>156084717</v>
+        <v>29843501</v>
       </c>
       <c r="N105">
-        <v>156093896</v>
+        <v>29844033</v>
       </c>
     </row>
     <row r="106" spans="1:14" x14ac:dyDescent="0.2">
@@ -6558,25 +6571,13 @@
         <v>17</v>
       </c>
       <c r="D106" t="s">
-        <v>361</v>
-      </c>
-      <c r="E106" t="s">
-        <v>362</v>
-      </c>
-      <c r="F106" t="s">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="G106" t="s">
-        <v>222</v>
+        <v>19</v>
       </c>
       <c r="H106">
-        <v>1</v>
-      </c>
-      <c r="I106" t="s">
-        <v>364</v>
-      </c>
-      <c r="J106">
-        <v>405754</v>
+        <v>35587</v>
       </c>
       <c r="K106" t="s">
         <v>43</v>
@@ -6585,10 +6586,10 @@
         <v>365</v>
       </c>
       <c r="M106">
-        <v>11102722</v>
+        <v>42861409</v>
       </c>
       <c r="N106">
-        <v>11105864</v>
+        <v>42871367</v>
       </c>
     </row>
     <row r="107" spans="1:14" x14ac:dyDescent="0.2">
@@ -6602,13 +6603,13 @@
         <v>17</v>
       </c>
       <c r="D107" t="s">
-        <v>366</v>
+        <v>267</v>
       </c>
       <c r="G107" t="s">
         <v>19</v>
       </c>
       <c r="H107">
-        <v>69</v>
+        <v>23</v>
       </c>
       <c r="K107" t="s">
         <v>20</v>
@@ -6617,10 +6618,10 @@
         <v>365</v>
       </c>
       <c r="M107">
-        <v>28650367</v>
+        <v>57623896</v>
       </c>
       <c r="N107">
-        <v>28660735</v>
+        <v>57628704</v>
       </c>
     </row>
     <row r="108" spans="1:14" x14ac:dyDescent="0.2">
@@ -6634,31 +6635,37 @@
         <v>17</v>
       </c>
       <c r="D108" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="E108" t="s">
-        <v>368</v>
+        <v>372</v>
+      </c>
+      <c r="F108" t="s">
+        <v>373</v>
+      </c>
+      <c r="G108" t="s">
+        <v>76</v>
       </c>
       <c r="H108">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="I108" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="J108">
-        <v>105375011</v>
+        <v>100289683</v>
       </c>
       <c r="K108" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="L108" t="s">
         <v>365</v>
       </c>
       <c r="M108">
-        <v>29843501</v>
+        <v>68591209</v>
       </c>
       <c r="N108">
-        <v>29844033</v>
+        <v>68599037</v>
       </c>
     </row>
     <row r="109" spans="1:14" x14ac:dyDescent="0.2">
@@ -6672,13 +6679,22 @@
         <v>17</v>
       </c>
       <c r="D109" t="s">
-        <v>370</v>
-      </c>
-      <c r="G109" t="s">
-        <v>19</v>
+        <v>379</v>
+      </c>
+      <c r="E109" t="s">
+        <v>380</v>
+      </c>
+      <c r="F109" t="s">
+        <v>381</v>
       </c>
       <c r="H109">
-        <v>35587</v>
+        <v>109</v>
+      </c>
+      <c r="I109" t="s">
+        <v>382</v>
+      </c>
+      <c r="J109">
+        <v>110006328</v>
       </c>
       <c r="K109" t="s">
         <v>43</v>
@@ -6687,10 +6703,10 @@
         <v>365</v>
       </c>
       <c r="M109">
-        <v>42861409</v>
+        <v>78426662</v>
       </c>
       <c r="N109">
-        <v>42871367</v>
+        <v>78436083</v>
       </c>
     </row>
     <row r="110" spans="1:14" x14ac:dyDescent="0.2">
@@ -6704,25 +6720,37 @@
         <v>17</v>
       </c>
       <c r="D110" t="s">
-        <v>267</v>
+        <v>383</v>
+      </c>
+      <c r="E110" t="s">
+        <v>384</v>
+      </c>
+      <c r="F110" t="s">
+        <v>385</v>
       </c>
       <c r="G110" t="s">
         <v>19</v>
       </c>
       <c r="H110">
-        <v>23</v>
+        <v>19</v>
+      </c>
+      <c r="I110" t="s">
+        <v>386</v>
+      </c>
+      <c r="J110">
+        <v>105376906</v>
       </c>
       <c r="K110" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="L110" t="s">
         <v>365</v>
       </c>
       <c r="M110">
-        <v>57623896</v>
+        <v>78427019</v>
       </c>
       <c r="N110">
-        <v>57628704</v>
+        <v>78436083</v>
       </c>
     </row>
     <row r="111" spans="1:14" x14ac:dyDescent="0.2">
@@ -6736,25 +6764,19 @@
         <v>17</v>
       </c>
       <c r="D111" t="s">
-        <v>371</v>
+        <v>387</v>
       </c>
       <c r="E111" t="s">
-        <v>372</v>
-      </c>
-      <c r="F111" t="s">
-        <v>373</v>
-      </c>
-      <c r="G111" t="s">
-        <v>76</v>
+        <v>388</v>
       </c>
       <c r="H111">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="I111" t="s">
-        <v>374</v>
+        <v>389</v>
       </c>
       <c r="J111">
-        <v>100289683</v>
+        <v>100616102</v>
       </c>
       <c r="K111" t="s">
         <v>43</v>
@@ -6763,10 +6785,10 @@
         <v>365</v>
       </c>
       <c r="M111">
-        <v>68591209</v>
+        <v>78430450</v>
       </c>
       <c r="N111">
-        <v>68599037</v>
+        <v>78432161</v>
       </c>
     </row>
     <row r="112" spans="1:14" x14ac:dyDescent="0.2">
@@ -6780,22 +6802,22 @@
         <v>17</v>
       </c>
       <c r="D112" t="s">
-        <v>375</v>
+        <v>390</v>
       </c>
       <c r="E112" t="s">
-        <v>376</v>
-      </c>
-      <c r="F112" t="s">
-        <v>377</v>
+        <v>391</v>
+      </c>
+      <c r="G112" t="s">
+        <v>175</v>
       </c>
       <c r="H112">
-        <v>1610</v>
+        <v>4</v>
       </c>
       <c r="I112" t="s">
-        <v>378</v>
+        <v>392</v>
       </c>
       <c r="J112">
-        <v>101928353</v>
+        <v>100616105</v>
       </c>
       <c r="K112" t="s">
         <v>20</v>
@@ -6804,10 +6826,10 @@
         <v>365</v>
       </c>
       <c r="M112">
-        <v>71103905</v>
+        <v>89372192</v>
       </c>
       <c r="N112">
-        <v>71109120</v>
+        <v>89380624</v>
       </c>
     </row>
     <row r="113" spans="1:15" x14ac:dyDescent="0.2">
@@ -6821,34 +6843,34 @@
         <v>17</v>
       </c>
       <c r="D113" t="s">
-        <v>379</v>
+        <v>394</v>
       </c>
       <c r="E113" t="s">
-        <v>380</v>
-      </c>
-      <c r="F113" t="s">
-        <v>381</v>
+        <v>395</v>
+      </c>
+      <c r="G113" t="s">
+        <v>24</v>
       </c>
       <c r="H113">
-        <v>109</v>
+        <v>17</v>
       </c>
       <c r="I113" t="s">
-        <v>382</v>
+        <v>396</v>
       </c>
       <c r="J113">
-        <v>110006328</v>
+        <v>106144567</v>
       </c>
       <c r="K113" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="L113" t="s">
         <v>365</v>
       </c>
       <c r="M113">
-        <v>78426662</v>
+        <v>106676011</v>
       </c>
       <c r="N113">
-        <v>78436083</v>
+        <v>106683689</v>
       </c>
     </row>
     <row r="114" spans="1:15" x14ac:dyDescent="0.2">
@@ -6862,37 +6884,31 @@
         <v>17</v>
       </c>
       <c r="D114" t="s">
-        <v>383</v>
+        <v>397</v>
       </c>
       <c r="E114" t="s">
-        <v>384</v>
-      </c>
-      <c r="F114" t="s">
-        <v>385</v>
-      </c>
-      <c r="G114" t="s">
-        <v>19</v>
+        <v>398</v>
       </c>
       <c r="H114">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="I114" t="s">
-        <v>386</v>
+        <v>399</v>
       </c>
       <c r="J114">
-        <v>105376906</v>
+        <v>111188146</v>
       </c>
       <c r="K114" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="L114" t="s">
         <v>365</v>
       </c>
       <c r="M114">
-        <v>78427019</v>
+        <v>111242742</v>
       </c>
       <c r="N114">
-        <v>78436083</v>
+        <v>111243387</v>
       </c>
     </row>
     <row r="115" spans="1:15" x14ac:dyDescent="0.2">
@@ -6906,31 +6922,34 @@
         <v>17</v>
       </c>
       <c r="D115" t="s">
-        <v>387</v>
+        <v>400</v>
       </c>
       <c r="E115" t="s">
-        <v>388</v>
+        <v>401</v>
+      </c>
+      <c r="G115" t="s">
+        <v>24</v>
       </c>
       <c r="H115">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="I115" t="s">
-        <v>389</v>
+        <v>402</v>
       </c>
       <c r="J115">
-        <v>100616102</v>
+        <v>106144562</v>
       </c>
       <c r="K115" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="L115" t="s">
         <v>365</v>
       </c>
       <c r="M115">
-        <v>78430450</v>
+        <v>143400937</v>
       </c>
       <c r="N115">
-        <v>78432161</v>
+        <v>143408849</v>
       </c>
     </row>
     <row r="116" spans="1:15" x14ac:dyDescent="0.2">
@@ -6944,22 +6963,22 @@
         <v>17</v>
       </c>
       <c r="D116" t="s">
-        <v>390</v>
+        <v>403</v>
       </c>
       <c r="E116" t="s">
-        <v>391</v>
+        <v>404</v>
       </c>
       <c r="G116" t="s">
-        <v>175</v>
+        <v>24</v>
       </c>
       <c r="H116">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="I116" t="s">
-        <v>392</v>
+        <v>405</v>
       </c>
       <c r="J116">
-        <v>100616105</v>
+        <v>106144571</v>
       </c>
       <c r="K116" t="s">
         <v>20</v>
@@ -6968,10 +6987,10 @@
         <v>365</v>
       </c>
       <c r="M116">
-        <v>89372192</v>
+        <v>167304567</v>
       </c>
       <c r="N116">
-        <v>89380624</v>
+        <v>167311741</v>
       </c>
     </row>
     <row r="117" spans="1:15" x14ac:dyDescent="0.2">
@@ -6985,34 +7004,40 @@
         <v>17</v>
       </c>
       <c r="D117" t="s">
-        <v>394</v>
+        <v>406</v>
       </c>
       <c r="E117" t="s">
-        <v>395</v>
+        <v>407</v>
+      </c>
+      <c r="F117" t="s">
+        <v>408</v>
       </c>
       <c r="G117" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="H117">
-        <v>17</v>
+        <v>108</v>
       </c>
       <c r="I117" t="s">
-        <v>396</v>
+        <v>409</v>
       </c>
       <c r="J117">
-        <v>106144567</v>
+        <v>64006</v>
       </c>
       <c r="K117" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="L117" t="s">
-        <v>365</v>
+        <v>410</v>
       </c>
       <c r="M117">
-        <v>106676011</v>
+        <v>4620811</v>
       </c>
       <c r="N117">
-        <v>106683689</v>
+        <v>4631528</v>
+      </c>
+      <c r="O117" t="s">
+        <v>411</v>
       </c>
     </row>
     <row r="118" spans="1:15" x14ac:dyDescent="0.2">
@@ -7026,31 +7051,40 @@
         <v>17</v>
       </c>
       <c r="D118" t="s">
-        <v>397</v>
+        <v>412</v>
       </c>
       <c r="E118" t="s">
-        <v>398</v>
+        <v>407</v>
+      </c>
+      <c r="F118" t="s">
+        <v>408</v>
+      </c>
+      <c r="G118" t="s">
+        <v>19</v>
       </c>
       <c r="H118">
-        <v>6</v>
+        <v>108</v>
       </c>
       <c r="I118" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="J118">
-        <v>111188146</v>
+        <v>64006</v>
       </c>
       <c r="K118" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="L118" t="s">
-        <v>365</v>
+        <v>410</v>
       </c>
       <c r="M118">
-        <v>111242742</v>
+        <v>4630561</v>
       </c>
       <c r="N118">
-        <v>111243387</v>
+        <v>4640031</v>
+      </c>
+      <c r="O118" t="s">
+        <v>413</v>
       </c>
     </row>
     <row r="119" spans="1:15" x14ac:dyDescent="0.2">
@@ -7064,34 +7098,37 @@
         <v>17</v>
       </c>
       <c r="D119" t="s">
-        <v>400</v>
+        <v>414</v>
       </c>
       <c r="E119" t="s">
-        <v>401</v>
+        <v>415</v>
+      </c>
+      <c r="F119" t="s">
+        <v>416</v>
       </c>
       <c r="G119" t="s">
-        <v>24</v>
+        <v>417</v>
       </c>
       <c r="H119">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I119" t="s">
-        <v>402</v>
+        <v>418</v>
       </c>
       <c r="J119">
-        <v>106144562</v>
+        <v>100616104</v>
       </c>
       <c r="K119" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="L119" t="s">
-        <v>365</v>
+        <v>410</v>
       </c>
       <c r="M119">
-        <v>143400937</v>
+        <v>12628860</v>
       </c>
       <c r="N119">
-        <v>143408849</v>
+        <v>12633987</v>
       </c>
     </row>
     <row r="120" spans="1:15" x14ac:dyDescent="0.2">
@@ -7105,34 +7142,31 @@
         <v>17</v>
       </c>
       <c r="D120" t="s">
-        <v>403</v>
+        <v>419</v>
       </c>
       <c r="E120" t="s">
-        <v>404</v>
-      </c>
-      <c r="G120" t="s">
-        <v>24</v>
+        <v>420</v>
       </c>
       <c r="H120">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="I120" t="s">
-        <v>405</v>
+        <v>421</v>
       </c>
       <c r="J120">
-        <v>106144571</v>
+        <v>111188142</v>
       </c>
       <c r="K120" t="s">
         <v>20</v>
       </c>
       <c r="L120" t="s">
-        <v>365</v>
+        <v>410</v>
       </c>
       <c r="M120">
-        <v>167304567</v>
+        <v>35950680</v>
       </c>
       <c r="N120">
-        <v>167311741</v>
+        <v>35951312</v>
       </c>
     </row>
     <row r="121" spans="1:15" x14ac:dyDescent="0.2">
@@ -7146,25 +7180,25 @@
         <v>17</v>
       </c>
       <c r="D121" t="s">
-        <v>406</v>
+        <v>422</v>
       </c>
       <c r="E121" t="s">
-        <v>407</v>
+        <v>423</v>
       </c>
       <c r="F121" t="s">
-        <v>408</v>
+        <v>424</v>
       </c>
       <c r="G121" t="s">
-        <v>19</v>
+        <v>425</v>
       </c>
       <c r="H121">
-        <v>108</v>
+        <v>1</v>
       </c>
       <c r="I121" t="s">
-        <v>409</v>
+        <v>426</v>
       </c>
       <c r="J121">
-        <v>64006</v>
+        <v>2086</v>
       </c>
       <c r="K121" t="s">
         <v>43</v>
@@ -7173,13 +7207,10 @@
         <v>410</v>
       </c>
       <c r="M121">
-        <v>4620811</v>
+        <v>64450734</v>
       </c>
       <c r="N121">
-        <v>4631528</v>
-      </c>
-      <c r="O121" t="s">
-        <v>411</v>
+        <v>64467065</v>
       </c>
     </row>
     <row r="122" spans="1:15" x14ac:dyDescent="0.2">
@@ -7193,40 +7224,37 @@
         <v>17</v>
       </c>
       <c r="D122" t="s">
-        <v>412</v>
+        <v>427</v>
       </c>
       <c r="E122" t="s">
-        <v>407</v>
+        <v>428</v>
       </c>
       <c r="F122" t="s">
-        <v>408</v>
+        <v>429</v>
       </c>
       <c r="G122" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="H122">
-        <v>108</v>
+        <v>1</v>
       </c>
       <c r="I122" t="s">
-        <v>409</v>
+        <v>430</v>
       </c>
       <c r="J122">
-        <v>64006</v>
+        <v>30816</v>
       </c>
       <c r="K122" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="L122" t="s">
         <v>410</v>
       </c>
       <c r="M122">
-        <v>4630561</v>
+        <v>92097312</v>
       </c>
       <c r="N122">
-        <v>4640031</v>
-      </c>
-      <c r="O122" t="s">
-        <v>413</v>
+        <v>92107506</v>
       </c>
     </row>
     <row r="123" spans="1:15" x14ac:dyDescent="0.2">
@@ -7240,25 +7268,25 @@
         <v>17</v>
       </c>
       <c r="D123" t="s">
-        <v>414</v>
+        <v>431</v>
       </c>
       <c r="E123" t="s">
-        <v>415</v>
+        <v>432</v>
       </c>
       <c r="F123" t="s">
-        <v>416</v>
+        <v>433</v>
       </c>
       <c r="G123" t="s">
-        <v>417</v>
+        <v>19</v>
       </c>
       <c r="H123">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="I123" t="s">
-        <v>418</v>
+        <v>434</v>
       </c>
       <c r="J123">
-        <v>100616104</v>
+        <v>100862687</v>
       </c>
       <c r="K123" t="s">
         <v>43</v>
@@ -7267,10 +7295,10 @@
         <v>410</v>
       </c>
       <c r="M123">
-        <v>12628860</v>
+        <v>104388369</v>
       </c>
       <c r="N123">
-        <v>12633987</v>
+        <v>104393266</v>
       </c>
     </row>
     <row r="124" spans="1:15" x14ac:dyDescent="0.2">
@@ -7284,19 +7312,22 @@
         <v>17</v>
       </c>
       <c r="D124" t="s">
-        <v>419</v>
+        <v>435</v>
       </c>
       <c r="E124" t="s">
-        <v>420</v>
+        <v>436</v>
+      </c>
+      <c r="F124" t="s">
+        <v>437</v>
       </c>
       <c r="H124">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I124" t="s">
-        <v>421</v>
+        <v>438</v>
       </c>
       <c r="J124">
-        <v>111188142</v>
+        <v>57612</v>
       </c>
       <c r="K124" t="s">
         <v>20</v>
@@ -7305,10 +7336,10 @@
         <v>410</v>
       </c>
       <c r="M124">
-        <v>35950680</v>
+        <v>134862422</v>
       </c>
       <c r="N124">
-        <v>35951312</v>
+        <v>134866711</v>
       </c>
     </row>
     <row r="125" spans="1:15" x14ac:dyDescent="0.2">
@@ -7322,25 +7353,25 @@
         <v>17</v>
       </c>
       <c r="D125" t="s">
-        <v>422</v>
+        <v>439</v>
       </c>
       <c r="E125" t="s">
-        <v>423</v>
+        <v>440</v>
       </c>
       <c r="F125" t="s">
-        <v>424</v>
+        <v>441</v>
       </c>
       <c r="G125" t="s">
-        <v>425</v>
+        <v>19</v>
       </c>
       <c r="H125">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="I125" t="s">
-        <v>426</v>
+        <v>442</v>
       </c>
       <c r="J125">
-        <v>2086</v>
+        <v>100616443</v>
       </c>
       <c r="K125" t="s">
         <v>43</v>
@@ -7349,10 +7380,10 @@
         <v>410</v>
       </c>
       <c r="M125">
-        <v>64450734</v>
+        <v>141450926</v>
       </c>
       <c r="N125">
-        <v>64467065</v>
+        <v>141455903</v>
       </c>
     </row>
     <row r="126" spans="1:15" x14ac:dyDescent="0.2">
@@ -7366,37 +7397,37 @@
         <v>17</v>
       </c>
       <c r="D126" t="s">
-        <v>427</v>
+        <v>443</v>
       </c>
       <c r="E126" t="s">
-        <v>428</v>
+        <v>444</v>
       </c>
       <c r="F126" t="s">
-        <v>429</v>
+        <v>445</v>
       </c>
       <c r="G126" t="s">
-        <v>24</v>
+        <v>446</v>
       </c>
       <c r="H126">
         <v>1</v>
       </c>
       <c r="I126" t="s">
-        <v>430</v>
+        <v>447</v>
       </c>
       <c r="J126">
-        <v>30816</v>
+        <v>346547</v>
       </c>
       <c r="K126" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="L126" t="s">
         <v>410</v>
       </c>
       <c r="M126">
-        <v>92097312</v>
+        <v>153108319</v>
       </c>
       <c r="N126">
-        <v>92107506</v>
+        <v>153111048</v>
       </c>
     </row>
     <row r="127" spans="1:15" x14ac:dyDescent="0.2">
@@ -7410,37 +7441,37 @@
         <v>17</v>
       </c>
       <c r="D127" t="s">
-        <v>431</v>
+        <v>448</v>
       </c>
       <c r="E127" t="s">
-        <v>432</v>
+        <v>449</v>
       </c>
       <c r="F127" t="s">
-        <v>433</v>
+        <v>450</v>
       </c>
       <c r="G127" t="s">
         <v>19</v>
       </c>
       <c r="H127">
-        <v>14</v>
+        <v>115</v>
       </c>
       <c r="I127" t="s">
-        <v>434</v>
+        <v>451</v>
       </c>
       <c r="J127">
-        <v>100862687</v>
+        <v>619465</v>
       </c>
       <c r="K127" t="s">
         <v>43</v>
       </c>
       <c r="L127" t="s">
-        <v>410</v>
+        <v>452</v>
       </c>
       <c r="M127">
-        <v>104388369</v>
+        <v>7355397</v>
       </c>
       <c r="N127">
-        <v>104393266</v>
+        <v>7364859</v>
       </c>
     </row>
     <row r="128" spans="1:15" x14ac:dyDescent="0.2">
@@ -7454,34 +7485,25 @@
         <v>17</v>
       </c>
       <c r="D128" t="s">
-        <v>435</v>
-      </c>
-      <c r="E128" t="s">
-        <v>436</v>
-      </c>
-      <c r="F128" t="s">
-        <v>437</v>
+        <v>92</v>
+      </c>
+      <c r="G128" t="s">
+        <v>19</v>
       </c>
       <c r="H128">
-        <v>2</v>
-      </c>
-      <c r="I128" t="s">
-        <v>438</v>
-      </c>
-      <c r="J128">
-        <v>57612</v>
+        <v>27</v>
       </c>
       <c r="K128" t="s">
         <v>20</v>
       </c>
       <c r="L128" t="s">
-        <v>410</v>
+        <v>452</v>
       </c>
       <c r="M128">
-        <v>134862422</v>
+        <v>8054700</v>
       </c>
       <c r="N128">
-        <v>134866711</v>
+        <v>8055725</v>
       </c>
     </row>
     <row r="129" spans="1:14" x14ac:dyDescent="0.2">
@@ -7495,37 +7517,34 @@
         <v>17</v>
       </c>
       <c r="D129" t="s">
-        <v>439</v>
+        <v>453</v>
       </c>
       <c r="E129" t="s">
-        <v>440</v>
-      </c>
-      <c r="F129" t="s">
-        <v>441</v>
+        <v>454</v>
       </c>
       <c r="G129" t="s">
         <v>19</v>
       </c>
       <c r="H129">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="I129" t="s">
-        <v>442</v>
+        <v>455</v>
       </c>
       <c r="J129">
-        <v>100616443</v>
+        <v>103539957</v>
       </c>
       <c r="K129" t="s">
         <v>43</v>
       </c>
       <c r="L129" t="s">
-        <v>410</v>
+        <v>452</v>
       </c>
       <c r="M129">
-        <v>141450926</v>
+        <v>12081113</v>
       </c>
       <c r="N129">
-        <v>141455903</v>
+        <v>12081622</v>
       </c>
     </row>
     <row r="130" spans="1:14" x14ac:dyDescent="0.2">
@@ -7539,37 +7558,34 @@
         <v>17</v>
       </c>
       <c r="D130" t="s">
-        <v>443</v>
+        <v>458</v>
       </c>
       <c r="E130" t="s">
-        <v>444</v>
-      </c>
-      <c r="F130" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="G130" t="s">
-        <v>446</v>
+        <v>175</v>
       </c>
       <c r="H130">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I130" t="s">
-        <v>447</v>
+        <v>460</v>
       </c>
       <c r="J130">
-        <v>346547</v>
+        <v>100862700</v>
       </c>
       <c r="K130" t="s">
         <v>43</v>
       </c>
       <c r="L130" t="s">
-        <v>410</v>
+        <v>452</v>
       </c>
       <c r="M130">
-        <v>153108319</v>
+        <v>12343258</v>
       </c>
       <c r="N130">
-        <v>153111048</v>
+        <v>12350376</v>
       </c>
     </row>
     <row r="131" spans="1:14" x14ac:dyDescent="0.2">
@@ -7583,25 +7599,13 @@
         <v>17</v>
       </c>
       <c r="D131" t="s">
-        <v>448</v>
-      </c>
-      <c r="E131" t="s">
-        <v>449</v>
-      </c>
-      <c r="F131" t="s">
-        <v>450</v>
+        <v>461</v>
       </c>
       <c r="G131" t="s">
         <v>19</v>
       </c>
       <c r="H131">
-        <v>115</v>
-      </c>
-      <c r="I131" t="s">
-        <v>451</v>
-      </c>
-      <c r="J131">
-        <v>619465</v>
+        <v>70</v>
       </c>
       <c r="K131" t="s">
         <v>43</v>
@@ -7610,10 +7614,10 @@
         <v>452</v>
       </c>
       <c r="M131">
-        <v>7355397</v>
+        <v>47175650</v>
       </c>
       <c r="N131">
-        <v>7364859</v>
+        <v>47183661</v>
       </c>
     </row>
     <row r="132" spans="1:14" x14ac:dyDescent="0.2">
@@ -7627,13 +7631,19 @@
         <v>17</v>
       </c>
       <c r="D132" t="s">
-        <v>92</v>
-      </c>
-      <c r="G132" t="s">
-        <v>19</v>
+        <v>462</v>
+      </c>
+      <c r="E132" t="s">
+        <v>463</v>
       </c>
       <c r="H132">
-        <v>27</v>
+        <v>8</v>
+      </c>
+      <c r="I132" t="s">
+        <v>464</v>
+      </c>
+      <c r="J132">
+        <v>111188145</v>
       </c>
       <c r="K132" t="s">
         <v>20</v>
@@ -7642,10 +7652,10 @@
         <v>452</v>
       </c>
       <c r="M132">
-        <v>8054700</v>
+        <v>54988029</v>
       </c>
       <c r="N132">
-        <v>8055725</v>
+        <v>54988656</v>
       </c>
     </row>
     <row r="133" spans="1:14" x14ac:dyDescent="0.2">
@@ -7659,34 +7669,34 @@
         <v>17</v>
       </c>
       <c r="D133" t="s">
-        <v>453</v>
+        <v>468</v>
       </c>
       <c r="E133" t="s">
-        <v>454</v>
+        <v>469</v>
       </c>
       <c r="G133" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="H133">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="I133" t="s">
-        <v>455</v>
+        <v>470</v>
       </c>
       <c r="J133">
-        <v>103539957</v>
+        <v>106144587</v>
       </c>
       <c r="K133" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="L133" t="s">
         <v>452</v>
       </c>
       <c r="M133">
-        <v>12081113</v>
+        <v>81651950</v>
       </c>
       <c r="N133">
-        <v>12081622</v>
+        <v>81655427</v>
       </c>
     </row>
     <row r="134" spans="1:14" x14ac:dyDescent="0.2">
@@ -7700,22 +7710,13 @@
         <v>17</v>
       </c>
       <c r="D134" t="s">
-        <v>458</v>
-      </c>
-      <c r="E134" t="s">
-        <v>459</v>
+        <v>209</v>
       </c>
       <c r="G134" t="s">
-        <v>175</v>
+        <v>19</v>
       </c>
       <c r="H134">
-        <v>3</v>
-      </c>
-      <c r="I134" t="s">
-        <v>460</v>
-      </c>
-      <c r="J134">
-        <v>100862700</v>
+        <v>29</v>
       </c>
       <c r="K134" t="s">
         <v>43</v>
@@ -7724,10 +7725,10 @@
         <v>452</v>
       </c>
       <c r="M134">
-        <v>12343258</v>
+        <v>146246648</v>
       </c>
       <c r="N134">
-        <v>12350376</v>
+        <v>146254211</v>
       </c>
     </row>
     <row r="135" spans="1:14" x14ac:dyDescent="0.2">
@@ -7741,25 +7742,34 @@
         <v>17</v>
       </c>
       <c r="D135" t="s">
-        <v>461</v>
+        <v>471</v>
+      </c>
+      <c r="E135" t="s">
+        <v>472</v>
       </c>
       <c r="G135" t="s">
-        <v>19</v>
+        <v>222</v>
       </c>
       <c r="H135">
-        <v>70</v>
+        <v>3</v>
+      </c>
+      <c r="I135" t="s">
+        <v>473</v>
+      </c>
+      <c r="J135">
+        <v>100533725</v>
       </c>
       <c r="K135" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="L135" t="s">
-        <v>452</v>
+        <v>474</v>
       </c>
       <c r="M135">
-        <v>47175650</v>
+        <v>21930389</v>
       </c>
       <c r="N135">
-        <v>47183661</v>
+        <v>21932738</v>
       </c>
     </row>
     <row r="136" spans="1:14" x14ac:dyDescent="0.2">
@@ -7773,31 +7783,34 @@
         <v>17</v>
       </c>
       <c r="D136" t="s">
-        <v>462</v>
+        <v>475</v>
       </c>
       <c r="E136" t="s">
-        <v>463</v>
+        <v>476</v>
+      </c>
+      <c r="G136" t="s">
+        <v>24</v>
       </c>
       <c r="H136">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="I136" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="J136">
-        <v>111188145</v>
+        <v>106144563</v>
       </c>
       <c r="K136" t="s">
         <v>20</v>
       </c>
       <c r="L136" t="s">
-        <v>452</v>
+        <v>474</v>
       </c>
       <c r="M136">
-        <v>54988029</v>
+        <v>35640301</v>
       </c>
       <c r="N136">
-        <v>54988656</v>
+        <v>35642824</v>
       </c>
     </row>
     <row r="137" spans="1:14" x14ac:dyDescent="0.2">
@@ -7811,34 +7824,34 @@
         <v>17</v>
       </c>
       <c r="D137" t="s">
-        <v>465</v>
+        <v>478</v>
       </c>
       <c r="E137" t="s">
-        <v>466</v>
+        <v>479</v>
       </c>
       <c r="G137" t="s">
-        <v>24</v>
+        <v>480</v>
       </c>
       <c r="H137">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="I137" t="s">
-        <v>467</v>
+        <v>481</v>
       </c>
       <c r="J137">
-        <v>106144604</v>
+        <v>100131068</v>
       </c>
       <c r="K137" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="L137" t="s">
-        <v>452</v>
+        <v>474</v>
       </c>
       <c r="M137">
-        <v>74734099</v>
+        <v>90652790</v>
       </c>
       <c r="N137">
-        <v>74734838</v>
+        <v>90659200</v>
       </c>
     </row>
     <row r="138" spans="1:14" x14ac:dyDescent="0.2">
@@ -7852,34 +7865,25 @@
         <v>17</v>
       </c>
       <c r="D138" t="s">
-        <v>468</v>
-      </c>
-      <c r="E138" t="s">
-        <v>469</v>
+        <v>355</v>
       </c>
       <c r="G138" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="H138">
-        <v>21</v>
-      </c>
-      <c r="I138" t="s">
-        <v>470</v>
-      </c>
-      <c r="J138">
-        <v>106144587</v>
+        <v>31</v>
       </c>
       <c r="K138" t="s">
         <v>20</v>
       </c>
       <c r="L138" t="s">
-        <v>452</v>
+        <v>474</v>
       </c>
       <c r="M138">
-        <v>81651950</v>
+        <v>131612515</v>
       </c>
       <c r="N138">
-        <v>81655427</v>
+        <v>131619736</v>
       </c>
     </row>
     <row r="139" spans="1:14" x14ac:dyDescent="0.2">
@@ -7893,25 +7897,25 @@
         <v>17</v>
       </c>
       <c r="D139" t="s">
-        <v>209</v>
+        <v>259</v>
       </c>
       <c r="G139" t="s">
         <v>19</v>
       </c>
       <c r="H139">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K139" t="s">
         <v>43</v>
       </c>
       <c r="L139" t="s">
-        <v>452</v>
+        <v>474</v>
       </c>
       <c r="M139">
-        <v>146246648</v>
+        <v>139674766</v>
       </c>
       <c r="N139">
-        <v>146254211</v>
+        <v>139684228</v>
       </c>
     </row>
     <row r="140" spans="1:14" x14ac:dyDescent="0.2">
@@ -7925,34 +7929,37 @@
         <v>17</v>
       </c>
       <c r="D140" t="s">
-        <v>471</v>
+        <v>484</v>
       </c>
       <c r="E140" t="s">
-        <v>472</v>
+        <v>485</v>
+      </c>
+      <c r="F140" t="s">
+        <v>486</v>
       </c>
       <c r="G140" t="s">
-        <v>222</v>
+        <v>76</v>
       </c>
       <c r="H140">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I140" t="s">
-        <v>473</v>
+        <v>487</v>
       </c>
       <c r="J140">
-        <v>100533725</v>
+        <v>100616461</v>
       </c>
       <c r="K140" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="L140" t="s">
-        <v>474</v>
+        <v>488</v>
       </c>
       <c r="M140">
-        <v>21930389</v>
+        <v>4462210</v>
       </c>
       <c r="N140">
-        <v>21932738</v>
+        <v>4463549</v>
       </c>
     </row>
     <row r="141" spans="1:14" x14ac:dyDescent="0.2">
@@ -7966,34 +7973,37 @@
         <v>17</v>
       </c>
       <c r="D141" t="s">
-        <v>475</v>
+        <v>489</v>
       </c>
       <c r="E141" t="s">
-        <v>476</v>
+        <v>490</v>
+      </c>
+      <c r="F141" t="s">
+        <v>491</v>
       </c>
       <c r="G141" t="s">
         <v>24</v>
       </c>
       <c r="H141">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="I141" t="s">
-        <v>477</v>
+        <v>492</v>
       </c>
       <c r="J141">
-        <v>106144563</v>
+        <v>100379323</v>
       </c>
       <c r="K141" t="s">
         <v>20</v>
       </c>
       <c r="L141" t="s">
-        <v>474</v>
+        <v>488</v>
       </c>
       <c r="M141">
-        <v>35640301</v>
+        <v>106295360</v>
       </c>
       <c r="N141">
-        <v>35642824</v>
+        <v>106298101</v>
       </c>
     </row>
     <row r="142" spans="1:14" x14ac:dyDescent="0.2">
@@ -8007,34 +8017,25 @@
         <v>17</v>
       </c>
       <c r="D142" t="s">
-        <v>478</v>
-      </c>
-      <c r="E142" t="s">
-        <v>479</v>
+        <v>493</v>
       </c>
       <c r="G142" t="s">
-        <v>480</v>
+        <v>19</v>
       </c>
       <c r="H142">
-        <v>1</v>
-      </c>
-      <c r="I142" t="s">
-        <v>481</v>
-      </c>
-      <c r="J142">
-        <v>100131068</v>
+        <v>63</v>
       </c>
       <c r="K142" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="L142" t="s">
-        <v>474</v>
+        <v>488</v>
       </c>
       <c r="M142">
-        <v>90652790</v>
+        <v>153817163</v>
       </c>
       <c r="N142">
-        <v>90659200</v>
+        <v>153819562</v>
       </c>
     </row>
     <row r="143" spans="1:14" x14ac:dyDescent="0.2">
@@ -8048,249 +8049,33 @@
         <v>17</v>
       </c>
       <c r="D143" t="s">
-        <v>355</v>
+        <v>494</v>
+      </c>
+      <c r="E143" t="s">
+        <v>495</v>
       </c>
       <c r="G143" t="s">
-        <v>19</v>
+        <v>76</v>
       </c>
       <c r="H143">
-        <v>31</v>
+        <v>6</v>
+      </c>
+      <c r="I143" t="s">
+        <v>496</v>
+      </c>
+      <c r="J143">
+        <v>51581</v>
       </c>
       <c r="K143" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="L143" t="s">
-        <v>474</v>
+        <v>497</v>
       </c>
       <c r="M143">
-        <v>131612515</v>
+        <v>23200175</v>
       </c>
       <c r="N143">
-        <v>131619736</v>
-      </c>
-    </row>
-    <row r="144" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A144" t="s">
-        <v>15</v>
-      </c>
-      <c r="B144" t="s">
-        <v>16</v>
-      </c>
-      <c r="C144" t="s">
-        <v>17</v>
-      </c>
-      <c r="D144" t="s">
-        <v>259</v>
-      </c>
-      <c r="G144" t="s">
-        <v>19</v>
-      </c>
-      <c r="H144">
-        <v>30</v>
-      </c>
-      <c r="K144" t="s">
-        <v>43</v>
-      </c>
-      <c r="L144" t="s">
-        <v>474</v>
-      </c>
-      <c r="M144">
-        <v>139674766</v>
-      </c>
-      <c r="N144">
-        <v>139684228</v>
-      </c>
-    </row>
-    <row r="145" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A145" t="s">
-        <v>15</v>
-      </c>
-      <c r="B145" t="s">
-        <v>16</v>
-      </c>
-      <c r="C145" t="s">
-        <v>17</v>
-      </c>
-      <c r="D145" t="s">
-        <v>482</v>
-      </c>
-      <c r="G145" t="s">
-        <v>19</v>
-      </c>
-      <c r="H145">
-        <v>105</v>
-      </c>
-      <c r="K145" t="s">
-        <v>20</v>
-      </c>
-      <c r="L145" t="s">
-        <v>483</v>
-      </c>
-      <c r="M145">
-        <v>175210</v>
-      </c>
-      <c r="N145">
-        <v>176178</v>
-      </c>
-    </row>
-    <row r="146" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A146" t="s">
-        <v>15</v>
-      </c>
-      <c r="B146" t="s">
-        <v>16</v>
-      </c>
-      <c r="C146" t="s">
-        <v>17</v>
-      </c>
-      <c r="D146" t="s">
-        <v>484</v>
-      </c>
-      <c r="E146" t="s">
-        <v>485</v>
-      </c>
-      <c r="F146" t="s">
-        <v>486</v>
-      </c>
-      <c r="G146" t="s">
-        <v>76</v>
-      </c>
-      <c r="H146">
-        <v>2</v>
-      </c>
-      <c r="I146" t="s">
-        <v>487</v>
-      </c>
-      <c r="J146">
-        <v>100616461</v>
-      </c>
-      <c r="K146" t="s">
-        <v>43</v>
-      </c>
-      <c r="L146" t="s">
-        <v>488</v>
-      </c>
-      <c r="M146">
-        <v>4462210</v>
-      </c>
-      <c r="N146">
-        <v>4463549</v>
-      </c>
-    </row>
-    <row r="147" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A147" t="s">
-        <v>15</v>
-      </c>
-      <c r="B147" t="s">
-        <v>16</v>
-      </c>
-      <c r="C147" t="s">
-        <v>17</v>
-      </c>
-      <c r="D147" t="s">
-        <v>489</v>
-      </c>
-      <c r="E147" t="s">
-        <v>490</v>
-      </c>
-      <c r="F147" t="s">
-        <v>491</v>
-      </c>
-      <c r="G147" t="s">
-        <v>24</v>
-      </c>
-      <c r="H147">
-        <v>2</v>
-      </c>
-      <c r="I147" t="s">
-        <v>492</v>
-      </c>
-      <c r="J147">
-        <v>100379323</v>
-      </c>
-      <c r="K147" t="s">
-        <v>20</v>
-      </c>
-      <c r="L147" t="s">
-        <v>488</v>
-      </c>
-      <c r="M147">
-        <v>106295360</v>
-      </c>
-      <c r="N147">
-        <v>106298101</v>
-      </c>
-    </row>
-    <row r="148" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A148" t="s">
-        <v>15</v>
-      </c>
-      <c r="B148" t="s">
-        <v>16</v>
-      </c>
-      <c r="C148" t="s">
-        <v>17</v>
-      </c>
-      <c r="D148" t="s">
-        <v>493</v>
-      </c>
-      <c r="G148" t="s">
-        <v>19</v>
-      </c>
-      <c r="H148">
-        <v>63</v>
-      </c>
-      <c r="K148" t="s">
-        <v>20</v>
-      </c>
-      <c r="L148" t="s">
-        <v>488</v>
-      </c>
-      <c r="M148">
-        <v>153817163</v>
-      </c>
-      <c r="N148">
-        <v>153819562</v>
-      </c>
-    </row>
-    <row r="149" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A149" t="s">
-        <v>15</v>
-      </c>
-      <c r="B149" t="s">
-        <v>16</v>
-      </c>
-      <c r="C149" t="s">
-        <v>17</v>
-      </c>
-      <c r="D149" t="s">
-        <v>494</v>
-      </c>
-      <c r="E149" t="s">
-        <v>495</v>
-      </c>
-      <c r="G149" t="s">
-        <v>76</v>
-      </c>
-      <c r="H149">
-        <v>6</v>
-      </c>
-      <c r="I149" t="s">
-        <v>496</v>
-      </c>
-      <c r="J149">
-        <v>51581</v>
-      </c>
-      <c r="K149" t="s">
-        <v>43</v>
-      </c>
-      <c r="L149" t="s">
-        <v>497</v>
-      </c>
-      <c r="M149">
-        <v>23200175</v>
-      </c>
-      <c r="N149">
         <v>23206610</v>
       </c>
     </row>
@@ -8301,119 +8086,430 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCBE97ED-1BA3-824F-A08D-55E4843F8392}">
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:O10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="4" max="4" width="45.6640625" customWidth="1"/>
+    <col min="5" max="5" width="24.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1" t="s">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A2" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E2" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F2" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G2" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="I1" t="s">
+      <c r="H2" s="3"/>
+      <c r="I2" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="J1">
+      <c r="J2" s="3">
         <v>3272</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K2" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L2" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="M1">
+      <c r="M2" s="3">
         <v>229406344</v>
       </c>
-      <c r="N1">
+      <c r="N2" s="3">
         <v>229408495</v>
       </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="O2" s="3"/>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A3" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>390</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E3" s="3" t="s">
         <v>391</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F3" s="3" t="s">
         <v>393</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G3" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="H2">
+      <c r="H3" s="3">
         <v>4</v>
       </c>
-      <c r="K2" t="s">
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="L2" t="s">
+      <c r="L3" s="3" t="s">
         <v>365</v>
       </c>
-      <c r="M2">
+      <c r="M3" s="3">
         <v>89372203</v>
       </c>
-      <c r="N2">
+      <c r="N3" s="3">
         <v>89375974</v>
       </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="O3" s="3"/>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>456</v>
       </c>
-      <c r="F3" t="s">
+      <c r="E4" s="3"/>
+      <c r="F4" s="3" t="s">
         <v>457</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G4" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="K3" t="s">
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
+      <c r="K4" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="L3" t="s">
+      <c r="L4" s="3" t="s">
         <v>452</v>
       </c>
-      <c r="M3">
+      <c r="M4" s="3">
         <v>12316492</v>
       </c>
-      <c r="N3">
+      <c r="N4" s="3">
         <v>12326007</v>
       </c>
+      <c r="O4" s="3"/>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>465</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H5" s="3">
+        <v>20</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="J5" s="3">
+        <v>106144604</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>452</v>
+      </c>
+      <c r="M5" s="3">
+        <v>74734099</v>
+      </c>
+      <c r="N5" s="3">
+        <v>74734838</v>
+      </c>
+      <c r="O5" s="3"/>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A6" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3">
+        <v>1610</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="J6" s="3">
+        <v>101928353</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="M6" s="3">
+        <v>71103905</v>
+      </c>
+      <c r="N6" s="3">
+        <v>71109120</v>
+      </c>
+      <c r="O6" s="3"/>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A7" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H7" s="3">
+        <v>30</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="J7" s="3">
+        <v>106144591</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="M7" s="3">
+        <v>187385634</v>
+      </c>
+      <c r="N7" s="3">
+        <v>187387099</v>
+      </c>
+      <c r="O7" s="3"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A8" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3">
+        <v>1</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="J8" s="3">
+        <v>339476</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M8" s="3">
+        <v>187610358</v>
+      </c>
+      <c r="N8" s="3">
+        <v>187612992</v>
+      </c>
+      <c r="O8" s="3"/>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A9" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H9" s="3">
+        <v>105</v>
+      </c>
+      <c r="I9" s="3"/>
+      <c r="J9" s="3"/>
+      <c r="K9" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="M9" s="3">
+        <v>175210</v>
+      </c>
+      <c r="N9" s="3">
+        <v>176178</v>
+      </c>
+      <c r="O9" s="3"/>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A10" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3" t="s">
+        <v>499</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H10" s="3">
+        <v>113</v>
+      </c>
+      <c r="I10" s="3"/>
+      <c r="J10" s="3"/>
+      <c r="K10" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="M10" s="3">
+        <v>21841536</v>
+      </c>
+      <c r="N10" s="3">
+        <v>21841542</v>
+      </c>
+      <c r="O10" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/tabular/legacy-list.xlsx
+++ b/tabular/legacy-list.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rob/Projects/erv/ERVdb-HomoSapiens/tabular/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78FF3E04-AFE8-F84C-A0D0-FAAEBD36B583}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE81D4B9-E08D-2840-A2AB-18C582FF9BD2}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1280" yWindow="1000" windowWidth="27140" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1360" uniqueCount="500">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1370" uniqueCount="502">
   <si>
     <t>organism</t>
   </si>
@@ -1521,6 +1521,12 @@
   </si>
   <si>
     <t>HERV-K 113</t>
+  </si>
+  <si>
+    <t>no</t>
+  </si>
+  <si>
+    <t>found?</t>
   </si>
 </sst>
 </file>
@@ -2376,15 +2382,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O143"/>
+  <dimension ref="A1:P152"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="4" max="4" width="47.1640625" customWidth="1"/>
     <col min="5" max="5" width="34" customWidth="1"/>
     <col min="6" max="6" width="51.6640625" customWidth="1"/>
+    <col min="7" max="7" width="16.33203125" customWidth="1"/>
+    <col min="8" max="8" width="18.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2430,8 +2438,11 @@
       <c r="O1" s="2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P1" s="2" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -2463,7 +2474,7 @@
         <v>13467826</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -2504,7 +2515,7 @@
         <v>46856998</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -2548,7 +2559,7 @@
         <v>75849143</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -2589,7 +2600,7 @@
         <v>89397564</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -2627,7 +2638,7 @@
         <v>110252173</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>15</v>
       </c>
@@ -2665,7 +2676,7 @@
         <v>150631285</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>15</v>
       </c>
@@ -2709,7 +2720,7 @@
         <v>155605636</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>15</v>
       </c>
@@ -2753,7 +2764,7 @@
         <v>160669806</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -2785,7 +2796,7 @@
         <v>166580258</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>15</v>
       </c>
@@ -2826,7 +2837,7 @@
         <v>178112194</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>15</v>
       </c>
@@ -2867,7 +2878,7 @@
         <v>205844935</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>15</v>
       </c>
@@ -2908,7 +2919,7 @@
         <v>227821260</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>15</v>
       </c>
@@ -2952,7 +2963,7 @@
         <v>6875603</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>15</v>
       </c>
@@ -2987,7 +2998,7 @@
         <v>27183380</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -7506,7 +7517,7 @@
         <v>8055725</v>
       </c>
     </row>
-    <row r="129" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
         <v>15</v>
       </c>
@@ -7547,7 +7558,7 @@
         <v>12081622</v>
       </c>
     </row>
-    <row r="130" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
         <v>15</v>
       </c>
@@ -7588,7 +7599,7 @@
         <v>12350376</v>
       </c>
     </row>
-    <row r="131" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
         <v>15</v>
       </c>
@@ -7620,7 +7631,7 @@
         <v>47183661</v>
       </c>
     </row>
-    <row r="132" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
         <v>15</v>
       </c>
@@ -7658,7 +7669,7 @@
         <v>54988656</v>
       </c>
     </row>
-    <row r="133" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
         <v>15</v>
       </c>
@@ -7699,7 +7710,7 @@
         <v>81655427</v>
       </c>
     </row>
-    <row r="134" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
         <v>15</v>
       </c>
@@ -7731,7 +7742,7 @@
         <v>146254211</v>
       </c>
     </row>
-    <row r="135" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
         <v>15</v>
       </c>
@@ -7772,7 +7783,7 @@
         <v>21932738</v>
       </c>
     </row>
-    <row r="136" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
         <v>15</v>
       </c>
@@ -7813,7 +7824,7 @@
         <v>35642824</v>
       </c>
     </row>
-    <row r="137" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
         <v>15</v>
       </c>
@@ -7854,7 +7865,7 @@
         <v>90659200</v>
       </c>
     </row>
-    <row r="138" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
         <v>15</v>
       </c>
@@ -7886,7 +7897,7 @@
         <v>131619736</v>
       </c>
     </row>
-    <row r="139" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
         <v>15</v>
       </c>
@@ -7918,7 +7929,7 @@
         <v>139684228</v>
       </c>
     </row>
-    <row r="140" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
         <v>15</v>
       </c>
@@ -7962,7 +7973,7 @@
         <v>4463549</v>
       </c>
     </row>
-    <row r="141" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
         <v>15</v>
       </c>
@@ -8006,7 +8017,7 @@
         <v>106298101</v>
       </c>
     </row>
-    <row r="142" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
         <v>15</v>
       </c>
@@ -8038,7 +8049,7 @@
         <v>153819562</v>
       </c>
     </row>
-    <row r="143" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
         <v>15</v>
       </c>
@@ -8077,6 +8088,395 @@
       </c>
       <c r="N143">
         <v>23206610</v>
+      </c>
+    </row>
+    <row r="144" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A144" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B144" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C144" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D144" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E144" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F144" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="G144" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="H144" s="3"/>
+      <c r="I144" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="J144" s="3">
+        <v>3272</v>
+      </c>
+      <c r="K144" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="L144" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M144" s="3">
+        <v>229406344</v>
+      </c>
+      <c r="N144" s="3">
+        <v>229408495</v>
+      </c>
+      <c r="P144" s="3" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="145" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A145" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B145" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C145" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D145" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="E145" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="F145" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="G145" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H145" s="3">
+        <v>4</v>
+      </c>
+      <c r="I145" s="3"/>
+      <c r="J145" s="3"/>
+      <c r="K145" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L145" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="M145" s="3">
+        <v>89372203</v>
+      </c>
+      <c r="N145" s="3">
+        <v>89375974</v>
+      </c>
+      <c r="P145" s="3" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="146" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A146" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B146" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C146" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D146" s="3" t="s">
+        <v>456</v>
+      </c>
+      <c r="E146" s="3"/>
+      <c r="F146" s="3" t="s">
+        <v>457</v>
+      </c>
+      <c r="G146" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H146" s="3"/>
+      <c r="I146" s="3"/>
+      <c r="J146" s="3"/>
+      <c r="K146" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L146" s="3" t="s">
+        <v>452</v>
+      </c>
+      <c r="M146" s="3">
+        <v>12316492</v>
+      </c>
+      <c r="N146" s="3">
+        <v>12326007</v>
+      </c>
+      <c r="P146" s="3" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="147" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A147" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B147" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C147" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D147" s="3" t="s">
+        <v>465</v>
+      </c>
+      <c r="E147" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="F147" s="3"/>
+      <c r="G147" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H147" s="3">
+        <v>20</v>
+      </c>
+      <c r="I147" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="J147" s="3">
+        <v>106144604</v>
+      </c>
+      <c r="K147" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L147" s="3" t="s">
+        <v>452</v>
+      </c>
+      <c r="M147" s="3">
+        <v>74734099</v>
+      </c>
+      <c r="N147" s="3">
+        <v>74734838</v>
+      </c>
+      <c r="P147" s="3" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="148" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A148" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B148" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C148" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D148" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="E148" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="F148" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="G148" s="3"/>
+      <c r="H148" s="3">
+        <v>1610</v>
+      </c>
+      <c r="I148" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="J148" s="3">
+        <v>101928353</v>
+      </c>
+      <c r="K148" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L148" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="M148" s="3">
+        <v>71103905</v>
+      </c>
+      <c r="N148" s="3">
+        <v>71109120</v>
+      </c>
+      <c r="P148" s="3" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="149" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A149" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B149" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C149" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D149" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="E149" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="F149" s="3"/>
+      <c r="G149" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H149" s="3">
+        <v>30</v>
+      </c>
+      <c r="I149" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="J149" s="3">
+        <v>106144591</v>
+      </c>
+      <c r="K149" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L149" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="M149" s="3">
+        <v>187385634</v>
+      </c>
+      <c r="N149" s="3">
+        <v>187387099</v>
+      </c>
+      <c r="P149" s="3" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="150" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A150" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B150" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C150" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D150" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E150" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F150" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G150" s="3"/>
+      <c r="H150" s="3">
+        <v>1</v>
+      </c>
+      <c r="I150" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="J150" s="3">
+        <v>339476</v>
+      </c>
+      <c r="K150" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L150" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M150" s="3">
+        <v>187610358</v>
+      </c>
+      <c r="N150" s="3">
+        <v>187612992</v>
+      </c>
+      <c r="P150" s="3" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="151" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A151" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B151" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C151" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D151" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="E151" s="3"/>
+      <c r="F151" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="G151" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H151" s="3">
+        <v>105</v>
+      </c>
+      <c r="I151" s="3"/>
+      <c r="J151" s="3"/>
+      <c r="K151" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L151" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="M151" s="3">
+        <v>175210</v>
+      </c>
+      <c r="N151" s="3">
+        <v>176178</v>
+      </c>
+      <c r="P151" s="3" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="152" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A152" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B152" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C152" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D152" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="E152" s="3"/>
+      <c r="F152" s="3" t="s">
+        <v>499</v>
+      </c>
+      <c r="G152" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H152" s="3">
+        <v>113</v>
+      </c>
+      <c r="I152" s="3"/>
+      <c r="J152" s="3"/>
+      <c r="K152" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="L152" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="M152" s="3">
+        <v>21841536</v>
+      </c>
+      <c r="N152" s="3">
+        <v>21841542</v>
+      </c>
+      <c r="P152" s="3" t="s">
+        <v>500</v>
       </c>
     </row>
   </sheetData>
@@ -8086,7 +8486,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCBE97ED-1BA3-824F-A08D-55E4843F8392}">
-  <dimension ref="A1:O10"/>
+  <dimension ref="A1:O1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="4" max="4" width="45.6640625" customWidth="1"/>
@@ -8140,377 +8540,6 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A2" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="J2" s="3">
-        <v>3272</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M2" s="3">
-        <v>229406344</v>
-      </c>
-      <c r="N2" s="3">
-        <v>229408495</v>
-      </c>
-      <c r="O2" s="3"/>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A3" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>390</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>391</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>393</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H3" s="3">
-        <v>4</v>
-      </c>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>365</v>
-      </c>
-      <c r="M3" s="3">
-        <v>89372203</v>
-      </c>
-      <c r="N3" s="3">
-        <v>89375974</v>
-      </c>
-      <c r="O3" s="3"/>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A4" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>456</v>
-      </c>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3" t="s">
-        <v>457</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>452</v>
-      </c>
-      <c r="M4" s="3">
-        <v>12316492</v>
-      </c>
-      <c r="N4" s="3">
-        <v>12326007</v>
-      </c>
-      <c r="O4" s="3"/>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A5" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>465</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>466</v>
-      </c>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H5" s="3">
-        <v>20</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>467</v>
-      </c>
-      <c r="J5" s="3">
-        <v>106144604</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L5" s="3" t="s">
-        <v>452</v>
-      </c>
-      <c r="M5" s="3">
-        <v>74734099</v>
-      </c>
-      <c r="N5" s="3">
-        <v>74734838</v>
-      </c>
-      <c r="O5" s="3"/>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A6" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>375</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>376</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>377</v>
-      </c>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3">
-        <v>1610</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>378</v>
-      </c>
-      <c r="J6" s="3">
-        <v>101928353</v>
-      </c>
-      <c r="K6" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L6" s="3" t="s">
-        <v>365</v>
-      </c>
-      <c r="M6" s="3">
-        <v>71103905</v>
-      </c>
-      <c r="N6" s="3">
-        <v>71109120</v>
-      </c>
-      <c r="O6" s="3"/>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A7" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>259</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H7" s="3">
-        <v>30</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>261</v>
-      </c>
-      <c r="J7" s="3">
-        <v>106144591</v>
-      </c>
-      <c r="K7" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L7" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="M7" s="3">
-        <v>187385634</v>
-      </c>
-      <c r="N7" s="3">
-        <v>187387099</v>
-      </c>
-      <c r="O7" s="3"/>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A8" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3">
-        <v>1</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="J8" s="3">
-        <v>339476</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L8" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M8" s="3">
-        <v>187610358</v>
-      </c>
-      <c r="N8" s="3">
-        <v>187612992</v>
-      </c>
-      <c r="O8" s="3"/>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A9" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>482</v>
-      </c>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3" t="s">
-        <v>498</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H9" s="3">
-        <v>105</v>
-      </c>
-      <c r="I9" s="3"/>
-      <c r="J9" s="3"/>
-      <c r="K9" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L9" s="3" t="s">
-        <v>483</v>
-      </c>
-      <c r="M9" s="3">
-        <v>175210</v>
-      </c>
-      <c r="N9" s="3">
-        <v>176178</v>
-      </c>
-      <c r="O9" s="3"/>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A10" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3" t="s">
-        <v>499</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H10" s="3">
-        <v>113</v>
-      </c>
-      <c r="I10" s="3"/>
-      <c r="J10" s="3"/>
-      <c r="K10" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="L10" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="M10" s="3">
-        <v>21841536</v>
-      </c>
-      <c r="N10" s="3">
-        <v>21841542</v>
-      </c>
-      <c r="O10" s="3"/>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
